--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2898045.84</v>
+        <v>3081610.16</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1115840.41</v>
+        <v>1153188.29</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>771254.52</v>
+        <v>1035877.77</v>
       </c>
       <c r="P10" t="n">
         <v>1219699.56</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3102.62</v>
+        <v>20916.81</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2677638.29</v>
+        <v>4037641.2</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>337568.65</v>
+        <v>338689.58</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4443,19 +4443,19 @@
         <v>335600.91</v>
       </c>
       <c r="P29" t="n">
-        <v>238425.06</v>
+        <v>245380.32</v>
       </c>
       <c r="Q29" t="n">
         <v>9180</v>
       </c>
       <c r="R29" t="n">
-        <v>2080161.06</v>
+        <v>2087116.32</v>
       </c>
       <c r="S29" t="n">
-        <v>1553409.29</v>
+        <v>1557059.19</v>
       </c>
       <c r="T29" t="n">
-        <v>1666829.02</v>
+        <v>1670478.92</v>
       </c>
       <c r="U29" t="n">
         <v>1841736</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1981016.45</v>
+        <v>2247865.28</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>929768.28</v>
+        <v>1758052.47</v>
       </c>
       <c r="P31" t="n">
         <v>636049.5600000001</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>80183.86</v>
+        <v>80311.28999999999</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>729553.4399999999</v>
+        <v>1120449.02</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>542795.65</v>
+        <v>789686.7</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6540,7 +6540,7 @@
         <v>93886</v>
       </c>
       <c r="O44" t="n">
-        <v>400500.27</v>
+        <v>436445.38</v>
       </c>
       <c r="P44" t="n">
         <v>92469.78</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2870692.14</v>
+        <v>3336703.28</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2366800</v>
+        <v>3169600</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>9425812.26</v>
+        <v>13573576.06</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>775920.41</v>
+        <v>828090.79</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -18032,10 +18032,10 @@
         <v>3708073.53</v>
       </c>
       <c r="S126" t="n">
-        <v>1959433.84</v>
+        <v>1959769.84</v>
       </c>
       <c r="T126" t="n">
-        <v>1959433.84</v>
+        <v>1959769.84</v>
       </c>
       <c r="U126" t="n">
         <v>2964567.72</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>56822971.49</v>
+        <v>59453753.69</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -21100,7 +21100,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>53994268.94</v>
+        <v>54113151.78</v>
       </c>
       <c r="P148" t="n">
         <v>21043600.09</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -21511,7 +21511,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>22925479.8</v>
+        <v>26588094.6</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -21520,7 +21520,7 @@
         <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>19285095</v>
+        <v>20262325.8</v>
       </c>
       <c r="P151" t="n">
         <v>60670522</v>
@@ -21532,10 +21532,10 @@
         <v>197559544</v>
       </c>
       <c r="S151" t="n">
-        <v>106975031.2</v>
+        <v>107626518.4</v>
       </c>
       <c r="T151" t="n">
-        <v>106975031.2</v>
+        <v>107626518.4</v>
       </c>
       <c r="U151" t="n">
         <v>136889022</v>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>17305331.24</v>
+        <v>17383586.81</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21660,7 +21660,7 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>15040648.71</v>
+        <v>15283331.24</v>
       </c>
       <c r="P152" t="n">
         <v>49898263.91</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
         <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>20378876.76</v>
+        <v>21598368.26</v>
       </c>
       <c r="P159" t="n">
         <v>3068431.98</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>01/04/2026 10:15:18</t>
+          <t>02/04/2026 07:11:10</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1153188.29</v>
+        <v>1203805.09</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1035877.77</v>
+        <v>1037744.37</v>
       </c>
       <c r="P10" t="n">
         <v>1219699.56</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>466813.68</v>
+        <v>489495.63</v>
       </c>
       <c r="P20" t="n">
         <v>2751110</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -4440,28 +4440,28 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>335600.91</v>
+        <v>336638.89</v>
       </c>
       <c r="P29" t="n">
-        <v>245380.32</v>
+        <v>279460.96</v>
       </c>
       <c r="Q29" t="n">
         <v>9180</v>
       </c>
       <c r="R29" t="n">
-        <v>2087116.32</v>
+        <v>2120933</v>
       </c>
       <c r="S29" t="n">
-        <v>1557059.19</v>
+        <v>1556978.55</v>
       </c>
       <c r="T29" t="n">
         <v>1670478.92</v>
       </c>
       <c r="U29" t="n">
-        <v>1841736</v>
+        <v>1841472.04</v>
       </c>
       <c r="V29" t="n">
-        <v>113419.73</v>
+        <v>113500.37</v>
       </c>
       <c r="W29" t="n">
         <v>1841736</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1758052.47</v>
+        <v>1970622.07</v>
       </c>
       <c r="P31" t="n">
         <v>636049.5600000001</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>80311.28999999999</v>
+        <v>85144.78999999999</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>16149.87</v>
+        <v>26138.53</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -6540,22 +6540,22 @@
         <v>93886</v>
       </c>
       <c r="O44" t="n">
-        <v>436445.38</v>
+        <v>452696.78</v>
       </c>
       <c r="P44" t="n">
-        <v>92469.78</v>
+        <v>104469.78</v>
       </c>
       <c r="Q44" t="n">
         <v>1186346</v>
       </c>
       <c r="R44" t="n">
-        <v>15224152.51</v>
+        <v>15236152.51</v>
       </c>
       <c r="S44" t="n">
-        <v>3160777.22</v>
+        <v>3172777.22</v>
       </c>
       <c r="T44" t="n">
-        <v>3160777.22</v>
+        <v>3172777.22</v>
       </c>
       <c r="U44" t="n">
         <v>15131682.73</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>10095.09</v>
+        <v>19002.37</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1377.05</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>102275.25</v>
+        <v>109375.25</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2080380.53</v>
+        <v>3046970.4</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -16340,7 +16340,7 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>12920.34</v>
+        <v>20728.72</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16620,7 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>253907.52</v>
+        <v>416264.39</v>
       </c>
       <c r="P116" t="n">
         <v>1805879.62</v>
@@ -16629,7 +16629,7 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>5275194.58</v>
+        <v>5276694.58</v>
       </c>
       <c r="S116" t="n">
         <v>2659928.13</v>
@@ -16638,7 +16638,7 @@
         <v>2660248.13</v>
       </c>
       <c r="U116" t="n">
-        <v>3469314.96</v>
+        <v>3470814.96</v>
       </c>
       <c r="V116" t="n">
         <v>320</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>828090.79</v>
+        <v>848216.5699999999</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -18020,7 +18020,7 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>129347.58</v>
+        <v>184821.77</v>
       </c>
       <c r="P126" t="n">
         <v>743505.8100000001</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>40.27</v>
+        <v>352.53</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -19420,7 +19420,7 @@
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>36878.42</v>
+        <v>73722.28999999999</v>
       </c>
       <c r="P136" t="n">
         <v>551.08</v>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -20257,7 +20257,7 @@
         <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -20284,7 +20284,7 @@
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="X142" t="n">
         <v>0</v>
@@ -20296,7 +20296,7 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AB142" t="n">
         <v>5</v>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>59453753.69</v>
+        <v>59562897.36</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -21100,7 +21100,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>54113151.78</v>
+        <v>56085410.36</v>
       </c>
       <c r="P148" t="n">
         <v>21043600.09</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -21511,7 +21511,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>26588094.6</v>
+        <v>27984138.6</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>17383586.81</v>
+        <v>17531483.02</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21660,7 +21660,7 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>15283331.24</v>
+        <v>16363331.24</v>
       </c>
       <c r="P152" t="n">
         <v>49898263.91</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
         <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>21598368.26</v>
+        <v>22342656.61</v>
       </c>
       <c r="P159" t="n">
         <v>3068431.98</v>
@@ -22649,7 +22649,7 @@
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>38437471.45</v>
+        <v>38772651</v>
       </c>
       <c r="S159" t="n">
         <v>32116802.57</v>
@@ -22658,7 +22658,7 @@
         <v>33729566.67</v>
       </c>
       <c r="U159" t="n">
-        <v>35369039.47</v>
+        <v>35704219.02</v>
       </c>
       <c r="V159" t="n">
         <v>1612764.1</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>02/04/2026 07:11:10</t>
+          <t>03/04/2026 07:06:36</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>115966</v>
       </c>
       <c r="O8" t="n">
-        <v>21963.17</v>
+        <v>24432.42</v>
       </c>
       <c r="P8" t="n">
         <v>181083.4</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1037744.37</v>
+        <v>1080537.16</v>
       </c>
       <c r="P10" t="n">
         <v>1219699.56</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>336638.89</v>
+        <v>336898.45</v>
       </c>
       <c r="P29" t="n">
         <v>279460.96</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1970622.07</v>
+        <v>1980017.05</v>
       </c>
       <c r="P31" t="n">
         <v>636049.5600000001</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
         <v>93886</v>
       </c>
       <c r="O44" t="n">
-        <v>452696.78</v>
+        <v>530057.74</v>
       </c>
       <c r="P44" t="n">
         <v>104469.78</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>15390.74</v>
+        <v>15459.84</v>
       </c>
       <c r="P74" t="n">
         <v>1495.27</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>32062.85</v>
+        <v>33191.28</v>
       </c>
       <c r="P109" t="n">
         <v>218266.91</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -16340,7 +16340,7 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>20728.72</v>
+        <v>21056.72</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16620,7 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>416264.39</v>
+        <v>460740.76</v>
       </c>
       <c r="P116" t="n">
         <v>1805879.62</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18020,7 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>184821.77</v>
+        <v>209720.41</v>
       </c>
       <c r="P126" t="n">
         <v>743505.8100000001</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -19420,7 +19420,7 @@
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>73722.28999999999</v>
+        <v>73756.84</v>
       </c>
       <c r="P136" t="n">
         <v>551.08</v>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -21660,7 +21660,7 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>16363331.24</v>
+        <v>17305331.24</v>
       </c>
       <c r="P152" t="n">
         <v>49898263.91</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>03/04/2026 07:06:36</t>
+          <t>04/04/2026 06:55:10</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>04/04/2026 06:55:10</t>
+          <t>05/04/2026 06:56:40</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>05/04/2026 06:56:40</t>
+          <t>06/04/2026 07:21:15</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1203805.09</v>
+        <v>1328178.63</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1080537.16</v>
+        <v>1093082.16</v>
       </c>
       <c r="P10" t="n">
         <v>1219699.56</v>
@@ -1789,19 +1789,19 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>12720486.32</v>
+        <v>12735483.25</v>
       </c>
       <c r="S10" t="n">
-        <v>7843980.11</v>
+        <v>7788258.45</v>
       </c>
       <c r="T10" t="n">
-        <v>7869919</v>
+        <v>7882464</v>
       </c>
       <c r="U10" t="n">
-        <v>11500786.76</v>
+        <v>11515783.69</v>
       </c>
       <c r="V10" t="n">
-        <v>25938.89</v>
+        <v>94205.55</v>
       </c>
       <c r="W10" t="n">
         <v>12250650</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -3612,10 +3612,10 @@
         <v>17378.42</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="U23" t="n">
         <v>17378.42</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>5377087.17</v>
+        <v>9369099.67</v>
       </c>
       <c r="S30" t="n">
         <v>3212132.5</v>
@@ -4598,7 +4598,7 @@
         <v>3212132.5</v>
       </c>
       <c r="U30" t="n">
-        <v>3212132.5</v>
+        <v>7204145</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>789686.7</v>
+        <v>802280.38</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>156730.89</v>
+        <v>249936</v>
       </c>
       <c r="S50" t="n">
         <v>156730.89</v>
@@ -7398,7 +7398,7 @@
         <v>156730.89</v>
       </c>
       <c r="U50" t="n">
-        <v>156730.89</v>
+        <v>249936</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1391.52</v>
+        <v>4743.43</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -10603,13 +10603,13 @@
         <v>40961.43</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>12692.75</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>483609.93</v>
+        <v>538805.72</v>
       </c>
       <c r="S73" t="n">
         <v>483609.93</v>
@@ -10618,7 +10618,7 @@
         <v>483609.93</v>
       </c>
       <c r="U73" t="n">
-        <v>483609.93</v>
+        <v>526112.97</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>15459.84</v>
+        <v>30781.48</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -10749,7 +10749,7 @@
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>257689.93</v>
+        <v>258289.93</v>
       </c>
       <c r="S74" t="n">
         <v>132420.68</v>
@@ -10758,7 +10758,7 @@
         <v>132420.68</v>
       </c>
       <c r="U74" t="n">
-        <v>256194.66</v>
+        <v>256794.66</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>46118.97</v>
+        <v>130917</v>
       </c>
       <c r="S81" t="n">
         <v>46118.97</v>
@@ -11738,7 +11738,7 @@
         <v>46118.97</v>
       </c>
       <c r="U81" t="n">
-        <v>46118.97</v>
+        <v>130917</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -12012,10 +12012,10 @@
         <v>345.28</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>345.28</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>345.28</v>
       </c>
       <c r="U83" t="n">
         <v>345.28</v>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -15089,7 +15089,7 @@
         <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>7742964.08</v>
+        <v>7795800.02</v>
       </c>
       <c r="S105" t="n">
         <v>821264.08</v>
@@ -15098,7 +15098,7 @@
         <v>821264.08</v>
       </c>
       <c r="U105" t="n">
-        <v>7692964.08</v>
+        <v>7745800.02</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>286118.97</v>
+        <v>346118.97</v>
       </c>
       <c r="S107" t="n">
         <v>46118.97</v>
@@ -15378,7 +15378,7 @@
         <v>46118.97</v>
       </c>
       <c r="U107" t="n">
-        <v>286118.97</v>
+        <v>346118.97</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15509,7 @@
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>202849.86</v>
+        <v>321493</v>
       </c>
       <c r="S108" t="n">
         <v>202849.86</v>
@@ -15518,7 +15518,7 @@
         <v>202849.86</v>
       </c>
       <c r="U108" t="n">
-        <v>202849.86</v>
+        <v>321493</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>33191.28</v>
+        <v>55924.58</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>13573576.06</v>
+        <v>14008552.93</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>1074549.58</v>
+        <v>2537927</v>
       </c>
       <c r="S125" t="n">
         <v>1074549.58</v>
@@ -17898,7 +17898,7 @@
         <v>1131764.02</v>
       </c>
       <c r="U125" t="n">
-        <v>1074549.58</v>
+        <v>2537927</v>
       </c>
       <c r="V125" t="n">
         <v>57214.44</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>352.53</v>
+        <v>368.19</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -19429,7 +19429,7 @@
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>5032621.72</v>
+        <v>5040463.02</v>
       </c>
       <c r="S136" t="n">
         <v>570925.76</v>
@@ -19438,7 +19438,7 @@
         <v>570925.76</v>
       </c>
       <c r="U136" t="n">
-        <v>5032070.64</v>
+        <v>5039911.94</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -19569,7 +19569,7 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>525</v>
+        <v>1225</v>
       </c>
       <c r="S137" t="n">
         <v>300</v>
@@ -19578,7 +19578,7 @@
         <v>300</v>
       </c>
       <c r="U137" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>9705156.27</v>
+        <v>12940208.36</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>17531483.02</v>
+        <v>17774241.01</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21672,10 +21672,10 @@
         <v>129341289.91</v>
       </c>
       <c r="S152" t="n">
-        <v>32606672.28</v>
+        <v>38058584.37</v>
       </c>
       <c r="T152" t="n">
-        <v>33050672.28</v>
+        <v>38502584.37</v>
       </c>
       <c r="U152" t="n">
         <v>79443026</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>224000</v>
+        <v>336000</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>
@@ -22631,7 +22631,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>22399742.61</v>
+        <v>24296479.14</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>06/04/2026 07:21:15</t>
+          <t>07/04/2026 17:23:05</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2809167.78</v>
+        <v>2898045.84</v>
       </c>
       <c r="P3" t="n">
         <v>220570.58</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1328178.63</v>
+        <v>1505679.84</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1093082.16</v>
+        <v>1095382.55</v>
       </c>
       <c r="P10" t="n">
         <v>1219699.56</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -2784,13 +2784,13 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>300000</v>
+        <v>285000</v>
       </c>
       <c r="X17" t="n">
         <v>300000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>489495.63</v>
+        <v>490662.29</v>
       </c>
       <c r="P20" t="n">
         <v>2751110</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>338689.58</v>
+        <v>395483.01</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2247865.28</v>
+        <v>2267847.6</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>550207.78</v>
+        <v>550526.21</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>477352.94</v>
+        <v>1193382.32</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>109375.25</v>
+        <v>137775.25</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>14008552.93</v>
+        <v>16923298.94</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -17731,7 +17731,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>22225.6</v>
+        <v>33338.4</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>848216.5699999999</v>
+        <v>876799.9</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -18020,7 +18020,7 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>209720.41</v>
+        <v>775920.41</v>
       </c>
       <c r="P126" t="n">
         <v>743505.8100000001</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3935.7</v>
+        <v>5903.55</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -19846,7 +19846,7 @@
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
@@ -19864,7 +19864,7 @@
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>7143</v>
+        <v>22143</v>
       </c>
       <c r="X139" t="n">
         <v>46881</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>07/04/2026 17:23:05</t>
+          <t>08/04/2026 07:18:46</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>24432.42</v>
+        <v>31684.04</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1095382.55</v>
+        <v>1119125.1</v>
       </c>
       <c r="P10" t="n">
         <v>1219699.56</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>256416.04</v>
+        <v>393876.57</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>395483.01</v>
+        <v>419943.19</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4440,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>336898.45</v>
+        <v>337318.02</v>
       </c>
       <c r="P29" t="n">
         <v>279460.96</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>448751.2</v>
+        <v>458660.24</v>
       </c>
       <c r="P30" t="n">
         <v>2164954.67</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2267847.6</v>
+        <v>2392405.8</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>550526.21</v>
+        <v>551529.3100000001</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2380.39</v>
+        <v>3036.39</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>802280.38</v>
+        <v>828058.61</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6540,7 +6540,7 @@
         <v>93886</v>
       </c>
       <c r="O44" t="n">
-        <v>530057.74</v>
+        <v>540802.35</v>
       </c>
       <c r="P44" t="n">
         <v>104469.78</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>40961.43</v>
+        <v>50870.47</v>
       </c>
       <c r="P73" t="n">
         <v>12692.75</v>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>137775.25</v>
+        <v>247150.5</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16620,7 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>460740.76</v>
+        <v>477782.77</v>
       </c>
       <c r="P116" t="n">
         <v>1805879.62</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -17880,7 +17880,7 @@
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>123357.73</v>
+        <v>133266.77</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -20278,7 +20278,7 @@
         <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -21100,7 +21100,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>56085410.36</v>
+        <v>56792471.49</v>
       </c>
       <c r="P148" t="n">
         <v>21043600.09</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -21520,7 +21520,7 @@
         <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>20262325.8</v>
+        <v>22925479.8</v>
       </c>
       <c r="P151" t="n">
         <v>60670522</v>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>
@@ -22649,7 +22649,7 @@
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>38772651</v>
+        <v>38852167.98</v>
       </c>
       <c r="S159" t="n">
         <v>32116802.57</v>
@@ -22658,7 +22658,7 @@
         <v>33729566.67</v>
       </c>
       <c r="U159" t="n">
-        <v>35704219.02</v>
+        <v>35783736</v>
       </c>
       <c r="V159" t="n">
         <v>1612764.1</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>08/04/2026 07:18:46</t>
+          <t>09/04/2026 07:26:39</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1505679.84</v>
+        <v>1511187.25</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1119125.1</v>
+        <v>1123249.11</v>
       </c>
       <c r="P10" t="n">
         <v>1219699.56</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>17023.38</v>
+        <v>81465.10000000001</v>
       </c>
       <c r="S17" t="n">
         <v>5459</v>
@@ -2778,7 +2778,7 @@
         <v>5459</v>
       </c>
       <c r="U17" t="n">
-        <v>7014.46</v>
+        <v>71456.17999999999</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>490662.29</v>
+        <v>944836.8199999999</v>
       </c>
       <c r="P20" t="n">
         <v>2751110</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>419943.19</v>
+        <v>479209.32</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4443,13 +4443,13 @@
         <v>337318.02</v>
       </c>
       <c r="P29" t="n">
-        <v>279460.96</v>
+        <v>280141.13</v>
       </c>
       <c r="Q29" t="n">
         <v>9180</v>
       </c>
       <c r="R29" t="n">
-        <v>2120933</v>
+        <v>2121613.17</v>
       </c>
       <c r="S29" t="n">
         <v>1556978.55</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2392405.8</v>
+        <v>2404426.53</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4723,13 +4723,13 @@
         <v>1980017.05</v>
       </c>
       <c r="P31" t="n">
-        <v>636049.5600000001</v>
+        <v>800034.36</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>18461792.37</v>
+        <v>18625777.17</v>
       </c>
       <c r="S31" t="n">
         <v>16777817.19</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>551529.3100000001</v>
+        <v>552852</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>1441.7</v>
+        <v>2380.39</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>828058.61</v>
+        <v>830052.3100000001</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6540,16 +6540,16 @@
         <v>93886</v>
       </c>
       <c r="O44" t="n">
-        <v>540802.35</v>
+        <v>542795.65</v>
       </c>
       <c r="P44" t="n">
-        <v>104469.78</v>
+        <v>124469.78</v>
       </c>
       <c r="Q44" t="n">
         <v>1186346</v>
       </c>
       <c r="R44" t="n">
-        <v>15236152.51</v>
+        <v>15237352.51</v>
       </c>
       <c r="S44" t="n">
         <v>3172777.22</v>
@@ -6558,7 +6558,7 @@
         <v>3172777.22</v>
       </c>
       <c r="U44" t="n">
-        <v>15131682.73</v>
+        <v>15112882.73</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>796.3</v>
+        <v>946.3</v>
       </c>
       <c r="P75" t="n">
         <v>450</v>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2358168.48</v>
+        <v>2361402.78</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>6354.15</v>
+        <v>6804.15</v>
       </c>
       <c r="P110" t="n">
         <v>2250</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>642287.52</v>
+        <v>644342.13</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
@@ -16620,7 +16620,7 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>477782.77</v>
+        <v>479820.55</v>
       </c>
       <c r="P116" t="n">
         <v>1805879.62</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -17320,7 +17320,7 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>2366800</v>
+        <v>3169600</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
         <v>15000</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -19858,7 +19858,7 @@
         <v>0</v>
       </c>
       <c r="U139" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>59562897.36</v>
+        <v>59667250.81</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -21100,7 +21100,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>56792471.49</v>
+        <v>56932115.16</v>
       </c>
       <c r="P148" t="n">
         <v>21043600.09</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
         <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>22342656.61</v>
+        <v>22399742.61</v>
       </c>
       <c r="P159" t="n">
         <v>3068431.98</v>
@@ -22649,7 +22649,7 @@
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>38852167.98</v>
+        <v>39221984.38</v>
       </c>
       <c r="S159" t="n">
         <v>32116802.57</v>
@@ -22658,7 +22658,7 @@
         <v>33729566.67</v>
       </c>
       <c r="U159" t="n">
-        <v>35783736</v>
+        <v>36153552.4</v>
       </c>
       <c r="V159" t="n">
         <v>1612764.1</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>09/04/2026 07:26:39</t>
+          <t>10/04/2026 07:18:53</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2898045.84</v>
+        <v>2958116.16</v>
       </c>
       <c r="P3" t="n">
         <v>220570.58</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>21551</v>
+        <v>25823</v>
       </c>
       <c r="S6" t="n">
         <v>14351</v>
@@ -1238,7 +1238,7 @@
         <v>14351</v>
       </c>
       <c r="U6" t="n">
-        <v>14351</v>
+        <v>18623</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5272.92</v>
+        <v>25272.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>256866.38</v>
+        <v>276866.38</v>
       </c>
       <c r="S7" t="n">
         <v>17143.8</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>33633.63</v>
+        <v>57410.34</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1511187.25</v>
+        <v>1515012.25</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>20916.81</v>
+        <v>21527.07</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -3183,13 +3183,13 @@
         <v>944836.8199999999</v>
       </c>
       <c r="P20" t="n">
-        <v>2751110</v>
+        <v>3125692.73</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>8440644</v>
+        <v>8815226.73</v>
       </c>
       <c r="S20" t="n">
         <v>4831031.1</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>479209.32</v>
+        <v>488084.38</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4440,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>337318.02</v>
+        <v>338438.95</v>
       </c>
       <c r="P29" t="n">
         <v>280141.13</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>458660.24</v>
+        <v>897502.4</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2404426.53</v>
+        <v>2410709.86</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1980017.05</v>
+        <v>2246865.88</v>
       </c>
       <c r="P31" t="n">
         <v>800034.36</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>281044.11</v>
+        <v>507458</v>
       </c>
       <c r="S33" t="n">
         <v>281044.11</v>
@@ -5018,7 +5018,7 @@
         <v>281044.11</v>
       </c>
       <c r="U33" t="n">
-        <v>281044.11</v>
+        <v>507458</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>552852</v>
+        <v>555400.5699999999</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>114789.89</v>
+        <v>229579.78</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
         <v>93886</v>
       </c>
       <c r="O44" t="n">
-        <v>542795.65</v>
+        <v>777562.36</v>
       </c>
       <c r="P44" t="n">
         <v>124469.78</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>19209.02</v>
+        <v>31457.53</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>2870692.14</v>
+        <v>3336703.28</v>
       </c>
       <c r="P49" t="n">
         <v>4140329.7</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>22178.9</v>
+        <v>44357.8</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>50870.47</v>
+        <v>81922.86</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>6526.27</v>
+        <v>13052.54</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12271,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -15220,7 +15220,7 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>2080380.53</v>
+        <v>3046970.4</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -15351,7 +15351,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>6526.27</v>
+        <v>13052.54</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15491,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>28705.17</v>
+        <v>57410.34</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16471,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>80987.12</v>
+        <v>161974.24</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -17460,7 +17460,7 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>9425812.26</v>
+        <v>13573576.06</v>
       </c>
       <c r="P122" t="n">
         <v>1425517.51</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -17871,7 +17871,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>133266.77</v>
+        <v>246715.46</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18020,7 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>775920.41</v>
+        <v>848216.5699999999</v>
       </c>
       <c r="P126" t="n">
         <v>743505.8100000001</v>
@@ -18029,7 +18029,7 @@
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3708073.53</v>
+        <v>3716642.89</v>
       </c>
       <c r="S126" t="n">
         <v>1959769.84</v>
@@ -18038,7 +18038,7 @@
         <v>1959769.84</v>
       </c>
       <c r="U126" t="n">
-        <v>2964567.72</v>
+        <v>2973137.08</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -18160,7 +18160,7 @@
         <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>156.13</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>59667250.81</v>
+        <v>59682641.06</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -21100,7 +21100,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>56932115.16</v>
+        <v>59562897.36</v>
       </c>
       <c r="P148" t="n">
         <v>21043600.09</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>17774241.01</v>
+        <v>17924153.08</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21660,7 +21660,7 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>17305331.24</v>
+        <v>17531483.02</v>
       </c>
       <c r="P152" t="n">
         <v>49898263.91</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>
@@ -22652,10 +22652,10 @@
         <v>39221984.38</v>
       </c>
       <c r="S159" t="n">
-        <v>32116802.57</v>
+        <v>32377746.42</v>
       </c>
       <c r="T159" t="n">
-        <v>33729566.67</v>
+        <v>33990510.52</v>
       </c>
       <c r="U159" t="n">
         <v>36153552.4</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>10/04/2026 07:18:53</t>
+          <t>11/04/2026 06:58:22</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>11/04/2026 06:58:22</t>
+          <t>12/04/2026 06:58:16</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>12/04/2026 06:58:16</t>
+          <t>13/04/2026 07:57:59</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>25823</v>
+        <v>26713</v>
       </c>
       <c r="S6" t="n">
         <v>14351</v>
@@ -1238,7 +1238,7 @@
         <v>14351</v>
       </c>
       <c r="U6" t="n">
-        <v>18623</v>
+        <v>19513</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>25272.92</v>
+        <v>71272.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>276866.38</v>
+        <v>325087.88</v>
       </c>
       <c r="S7" t="n">
         <v>17143.8</v>
@@ -1378,7 +1378,7 @@
         <v>17143.8</v>
       </c>
       <c r="U7" t="n">
-        <v>251593.46</v>
+        <v>253814.96</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
         <v>5495750</v>
       </c>
       <c r="W54" t="n">
-        <v>18778855</v>
+        <v>18758759</v>
       </c>
       <c r="X54" t="n">
         <v>22965724</v>
@@ -7973,10 +7973,10 @@
         <v>4186869</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>20096</v>
       </c>
       <c r="AA54" t="n">
-        <v>22965724</v>
+        <v>22945628</v>
       </c>
       <c r="AB54" t="n">
         <v>5</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>20096</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8104,7 +8104,7 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>20096</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
@@ -8116,7 +8116,7 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>20096</v>
       </c>
       <c r="AB55" t="n">
         <v>5</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -9769,16 +9769,16 @@
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>20000</v>
+        <v>21050</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="U67" t="n">
-        <v>20000</v>
+        <v>21050</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -10743,13 +10743,13 @@
         <v>15459.84</v>
       </c>
       <c r="P74" t="n">
-        <v>1495.27</v>
+        <v>2221.59</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>258289.93</v>
+        <v>259016.25</v>
       </c>
       <c r="S74" t="n">
         <v>132420.68</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>247150.5</v>
+        <v>254250.5</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -15643,13 +15643,13 @@
         <v>33191.28</v>
       </c>
       <c r="P109" t="n">
-        <v>218266.91</v>
+        <v>219666.91</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>454774.15</v>
+        <v>456174.15</v>
       </c>
       <c r="S109" t="n">
         <v>230854</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -16623,13 +16623,13 @@
         <v>479820.55</v>
       </c>
       <c r="P116" t="n">
-        <v>1805879.62</v>
+        <v>1806052.42</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>5276694.58</v>
+        <v>5277014.58</v>
       </c>
       <c r="S116" t="n">
         <v>2659928.13</v>
@@ -16638,7 +16638,7 @@
         <v>2660248.13</v>
       </c>
       <c r="U116" t="n">
-        <v>3470814.96</v>
+        <v>3470962.16</v>
       </c>
       <c r="V116" t="n">
         <v>320</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>13/04/2026 07:57:59</t>
+          <t>14/04/2026 07:27:11</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>14351</v>
+        <v>19513</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1232,10 +1232,10 @@
         <v>26713</v>
       </c>
       <c r="S6" t="n">
-        <v>14351</v>
+        <v>19513</v>
       </c>
       <c r="T6" t="n">
-        <v>14351</v>
+        <v>19513</v>
       </c>
       <c r="U6" t="n">
         <v>19513</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1515012.25</v>
+        <v>1503067.25</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1123249.11</v>
+        <v>1122558.91</v>
       </c>
       <c r="P10" t="n">
-        <v>1219699.56</v>
+        <v>1231644.56</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1792,16 +1792,16 @@
         <v>12735483.25</v>
       </c>
       <c r="S10" t="n">
-        <v>7788258.45</v>
+        <v>7776313.45</v>
       </c>
       <c r="T10" t="n">
         <v>7882464</v>
       </c>
       <c r="U10" t="n">
-        <v>11515783.69</v>
+        <v>11503838.69</v>
       </c>
       <c r="V10" t="n">
-        <v>94205.55</v>
+        <v>106150.55</v>
       </c>
       <c r="W10" t="n">
         <v>12250650</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>555400.5699999999</v>
+        <v>832062.6</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
         <v>93886</v>
       </c>
       <c r="O44" t="n">
-        <v>777562.36</v>
+        <v>778720.6899999999</v>
       </c>
       <c r="P44" t="n">
         <v>124469.78</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>20096</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -8098,7 +8098,7 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>20096</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -10752,10 +10752,10 @@
         <v>259016.25</v>
       </c>
       <c r="S74" t="n">
-        <v>132420.68</v>
+        <v>133147</v>
       </c>
       <c r="T74" t="n">
-        <v>132420.68</v>
+        <v>133147</v>
       </c>
       <c r="U74" t="n">
         <v>256794.66</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -13811,16 +13811,16 @@
         </is>
       </c>
       <c r="L96" t="n">
+        <v>2363104.83</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
         <v>2361402.78</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="n">
-        <v>2358168.48</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -15643,7 +15643,7 @@
         <v>33191.28</v>
       </c>
       <c r="P109" t="n">
-        <v>219666.91</v>
+        <v>223266.91</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -15652,13 +15652,13 @@
         <v>456174.15</v>
       </c>
       <c r="S109" t="n">
-        <v>230854</v>
+        <v>232254</v>
       </c>
       <c r="T109" t="n">
-        <v>230854</v>
+        <v>232254</v>
       </c>
       <c r="U109" t="n">
-        <v>236507.24</v>
+        <v>232907.24</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -16620,25 +16620,25 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>479820.55</v>
+        <v>642287.52</v>
       </c>
       <c r="P116" t="n">
-        <v>1806052.42</v>
+        <v>2060687.58</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>5277014.58</v>
+        <v>5677014.58</v>
       </c>
       <c r="S116" t="n">
-        <v>2659928.13</v>
+        <v>2660248.13</v>
       </c>
       <c r="T116" t="n">
-        <v>2660248.13</v>
+        <v>2660568.13</v>
       </c>
       <c r="U116" t="n">
-        <v>3470962.16</v>
+        <v>3616327</v>
       </c>
       <c r="V116" t="n">
         <v>320</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -17460,7 +17460,7 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>13573576.06</v>
+        <v>14008552.93</v>
       </c>
       <c r="P122" t="n">
         <v>1425517.51</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -20272,10 +20272,10 @@
         <v>150000</v>
       </c>
       <c r="S142" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U142" t="n">
         <v>150000</v>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -20540,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>9705156.27</v>
+        <v>12940208.36</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -21660,7 +21660,7 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>17531483.02</v>
+        <v>17621483.02</v>
       </c>
       <c r="P152" t="n">
         <v>49898263.91</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
         <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>22399742.61</v>
+        <v>24296479.14</v>
       </c>
       <c r="P159" t="n">
         <v>3068431.98</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>14/04/2026 07:27:11</t>
+          <t>15/04/2026 07:28:15</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="P7" t="n">
         <v>71272.92</v>
@@ -1369,16 +1369,16 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>325087.88</v>
+        <v>326423.03</v>
       </c>
       <c r="S7" t="n">
-        <v>17143.8</v>
+        <v>65365.3</v>
       </c>
       <c r="T7" t="n">
-        <v>17143.8</v>
+        <v>65365.3</v>
       </c>
       <c r="U7" t="n">
-        <v>253814.96</v>
+        <v>255150.11</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1122558.91</v>
+        <v>1234387.45</v>
       </c>
       <c r="P10" t="n">
         <v>1231644.56</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -3603,13 +3603,13 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6496</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="R23" t="n">
-        <v>17378.42</v>
+        <v>75842.42</v>
       </c>
       <c r="S23" t="n">
         <v>1440</v>
@@ -3618,13 +3618,13 @@
         <v>1440</v>
       </c>
       <c r="U23" t="n">
-        <v>17378.42</v>
+        <v>69346.42</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>30306</v>
+        <v>80306</v>
       </c>
       <c r="X23" t="n">
         <v>200000</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -4440,25 +4440,25 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>338438.95</v>
+        <v>338939.23</v>
       </c>
       <c r="P29" t="n">
-        <v>280141.13</v>
+        <v>315775.36</v>
       </c>
       <c r="Q29" t="n">
         <v>9180</v>
       </c>
       <c r="R29" t="n">
-        <v>2121613.17</v>
+        <v>2157447.4</v>
       </c>
       <c r="S29" t="n">
-        <v>1556978.55</v>
+        <v>1634271.47</v>
       </c>
       <c r="T29" t="n">
-        <v>1670478.92</v>
+        <v>1747771.84</v>
       </c>
       <c r="U29" t="n">
-        <v>1841472.04</v>
+        <v>1841672.04</v>
       </c>
       <c r="V29" t="n">
         <v>113500.37</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>830052.3100000001</v>
+        <v>845852.3100000001</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6540,10 +6540,10 @@
         <v>93886</v>
       </c>
       <c r="O44" t="n">
-        <v>778720.6899999999</v>
+        <v>788997.71</v>
       </c>
       <c r="P44" t="n">
-        <v>124469.78</v>
+        <v>374469.78</v>
       </c>
       <c r="Q44" t="n">
         <v>1186346</v>
@@ -6558,7 +6558,7 @@
         <v>3172777.22</v>
       </c>
       <c r="U44" t="n">
-        <v>15112882.73</v>
+        <v>14862882.73</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>367350</v>
+        <v>492900</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -10052,10 +10052,10 @@
         <v>921519</v>
       </c>
       <c r="S69" t="n">
-        <v>367350</v>
+        <v>492900</v>
       </c>
       <c r="T69" t="n">
-        <v>367350</v>
+        <v>492900</v>
       </c>
       <c r="U69" t="n">
         <v>921519</v>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10320,7 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>477352.94</v>
+        <v>1193382.32</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>15459.84</v>
+        <v>30781.48</v>
       </c>
       <c r="P74" t="n">
         <v>2221.59</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2363104.83</v>
+        <v>3410465.43</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>33191.28</v>
+        <v>55924.58</v>
       </c>
       <c r="P109" t="n">
         <v>223266.91</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>644342.13</v>
+        <v>664800.21</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
@@ -16644,13 +16644,13 @@
         <v>320</v>
       </c>
       <c r="W116" t="n">
-        <v>4701261</v>
+        <v>4651261</v>
       </c>
       <c r="X116" t="n">
         <v>4953156</v>
       </c>
       <c r="Y116" t="n">
-        <v>251895</v>
+        <v>301895</v>
       </c>
       <c r="Z116" t="n">
         <v>0</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3169600</v>
+        <v>3132800</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -17320,7 +17320,7 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>3169600</v>
+        <v>3132800</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -17460,7 +17460,7 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>14008552.93</v>
+        <v>16923298.94</v>
       </c>
       <c r="P122" t="n">
         <v>1425517.51</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -18011,16 +18011,16 @@
         </is>
       </c>
       <c r="L126" t="n">
+        <v>903570.96</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
         <v>876799.9</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" t="n">
-        <v>848216.5699999999</v>
       </c>
       <c r="P126" t="n">
         <v>743505.8100000001</v>
@@ -18029,7 +18029,7 @@
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3716642.89</v>
+        <v>3802648.2</v>
       </c>
       <c r="S126" t="n">
         <v>1959769.84</v>
@@ -18038,7 +18038,7 @@
         <v>1959769.84</v>
       </c>
       <c r="U126" t="n">
-        <v>2973137.08</v>
+        <v>3059142.39</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>73756.84</v>
+        <v>110421.01</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -21100,7 +21100,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>59562897.36</v>
+        <v>59582064.28</v>
       </c>
       <c r="P148" t="n">
         <v>21043600.09</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -21511,7 +21511,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>27984138.6</v>
+        <v>29380182.6</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -21520,7 +21520,7 @@
         <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>22925479.8</v>
+        <v>26588094.6</v>
       </c>
       <c r="P151" t="n">
         <v>60670522</v>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>17924153.08</v>
+        <v>18074598.76</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21660,7 +21660,7 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>17621483.02</v>
+        <v>17774241.01</v>
       </c>
       <c r="P152" t="n">
         <v>49898263.91</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>
@@ -22631,7 +22631,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>24296479.14</v>
+        <v>24479179.14</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -22649,7 +22649,7 @@
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>39221984.38</v>
+        <v>39529119.98</v>
       </c>
       <c r="S159" t="n">
         <v>32377746.42</v>
@@ -22658,7 +22658,7 @@
         <v>33990510.52</v>
       </c>
       <c r="U159" t="n">
-        <v>36153552.4</v>
+        <v>36460688</v>
       </c>
       <c r="V159" t="n">
         <v>1612764.1</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>15/04/2026 07:28:15</t>
+          <t>16/04/2026 07:27:49</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -1363,22 +1363,22 @@
         <v>490</v>
       </c>
       <c r="P7" t="n">
-        <v>71272.92</v>
+        <v>74385.42</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>326423.03</v>
+        <v>332768.03</v>
       </c>
       <c r="S7" t="n">
-        <v>65365.3</v>
+        <v>128004.85</v>
       </c>
       <c r="T7" t="n">
-        <v>65365.3</v>
+        <v>128004.85</v>
       </c>
       <c r="U7" t="n">
-        <v>255150.11</v>
+        <v>258382.61</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>33633.63</v>
+        <v>57410.34</v>
       </c>
       <c r="P9" t="n">
         <v>106.92</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1503067.25</v>
+        <v>1506178.6</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1783,13 +1783,13 @@
         <v>1234387.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1231644.56</v>
+        <v>1234134.56</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>12735483.25</v>
+        <v>12736833.25</v>
       </c>
       <c r="S10" t="n">
         <v>7776313.45</v>
@@ -1798,7 +1798,7 @@
         <v>7882464</v>
       </c>
       <c r="U10" t="n">
-        <v>11503838.69</v>
+        <v>11502698.69</v>
       </c>
       <c r="V10" t="n">
         <v>106150.55</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>5459</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>256416.04</v>
+        <v>393876.57</v>
       </c>
       <c r="P18" t="n">
         <v>14849.99</v>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>944836.8199999999</v>
+        <v>956587.76</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -4163,22 +4163,22 @@
         <v>13158.64</v>
       </c>
       <c r="P27" t="n">
-        <v>26530.2</v>
+        <v>42067.8</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>351236.74</v>
+        <v>382910.98</v>
       </c>
       <c r="S27" t="n">
-        <v>262903.94</v>
+        <v>312903.94</v>
       </c>
       <c r="T27" t="n">
-        <v>262903.94</v>
+        <v>312903.94</v>
       </c>
       <c r="U27" t="n">
-        <v>324706.54</v>
+        <v>340843.18</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -4452,10 +4452,10 @@
         <v>2157447.4</v>
       </c>
       <c r="S29" t="n">
-        <v>1634271.47</v>
+        <v>1634951.64</v>
       </c>
       <c r="T29" t="n">
-        <v>1747771.84</v>
+        <v>1748452.01</v>
       </c>
       <c r="U29" t="n">
         <v>1841672.04</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>458660.24</v>
+        <v>897502.4</v>
       </c>
       <c r="P30" t="n">
         <v>2164954.67</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2410709.86</v>
+        <v>2459996.15</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2246865.88</v>
+        <v>2272907.97</v>
       </c>
       <c r="P31" t="n">
         <v>800034.36</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2380.39</v>
+        <v>2708.39</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -6272,10 +6272,10 @@
         <v>51525.12</v>
       </c>
       <c r="S42" t="n">
-        <v>20187</v>
+        <v>50187</v>
       </c>
       <c r="T42" t="n">
-        <v>24123</v>
+        <v>54123</v>
       </c>
       <c r="U42" t="n">
         <v>51525.12</v>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>845852.3100000001</v>
+        <v>846303.71</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>22178.9</v>
+        <v>44357.8</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>11245942.1</v>
+        <v>18253327.1</v>
       </c>
       <c r="S54" t="n">
         <v>11054942.1</v>
@@ -7958,7 +7958,7 @@
         <v>16550692.1</v>
       </c>
       <c r="U54" t="n">
-        <v>11245942.1</v>
+        <v>18253327.1</v>
       </c>
       <c r="V54" t="n">
         <v>5495750</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -9772,10 +9772,10 @@
         <v>21050</v>
       </c>
       <c r="S67" t="n">
-        <v>1050</v>
+        <v>21050</v>
       </c>
       <c r="T67" t="n">
-        <v>1050</v>
+        <v>21050</v>
       </c>
       <c r="U67" t="n">
         <v>21050</v>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -10463,22 +10463,22 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1124.65</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
+        <v>52292.66</v>
+      </c>
+      <c r="S72" t="n">
         <v>50000</v>
       </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U72" t="n">
-        <v>50000</v>
+        <v>51168.01</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>259016.25</v>
+        <v>260366.25</v>
       </c>
       <c r="S74" t="n">
         <v>133147</v>
@@ -10758,7 +10758,7 @@
         <v>133147</v>
       </c>
       <c r="U74" t="n">
-        <v>256794.66</v>
+        <v>258144.66</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -11592,10 +11592,10 @@
         <v>30000</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="U80" t="n">
         <v>30000</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>6526.27</v>
+        <v>13052.54</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -13272,10 +13272,10 @@
         <v>30000</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="U92" t="n">
         <v>30000</v>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
         <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>2361402.78</v>
+        <v>2363104.83</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -15080,7 +15080,7 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>102275.25</v>
+        <v>204550.5</v>
       </c>
       <c r="P105" t="n">
         <v>50000</v>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -15360,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>6526.27</v>
+        <v>13052.54</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -15500,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>28705.17</v>
+        <v>57410.34</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -15649,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>456174.15</v>
+        <v>460224.15</v>
       </c>
       <c r="S109" t="n">
         <v>232254</v>
@@ -15658,7 +15658,7 @@
         <v>232254</v>
       </c>
       <c r="U109" t="n">
-        <v>232907.24</v>
+        <v>236957.24</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>664800.21</v>
+        <v>665756.61</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -17603,22 +17603,22 @@
         <v>62133</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2075</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>177419.82</v>
+        <v>181649.82</v>
       </c>
       <c r="S123" t="n">
-        <v>73323</v>
+        <v>133323</v>
       </c>
       <c r="T123" t="n">
-        <v>75117</v>
+        <v>135117</v>
       </c>
       <c r="U123" t="n">
-        <v>177419.82</v>
+        <v>179574.82</v>
       </c>
       <c r="V123" t="n">
         <v>1794</v>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -17880,7 +17880,7 @@
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>133266.77</v>
+        <v>218108.24</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -19563,13 +19563,13 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>225</v>
+        <v>925</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>1225</v>
+        <v>1900</v>
       </c>
       <c r="S137" t="n">
         <v>300</v>
@@ -19578,7 +19578,7 @@
         <v>300</v>
       </c>
       <c r="U137" t="n">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -21100,7 +21100,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>59582064.28</v>
+        <v>59682641.06</v>
       </c>
       <c r="P148" t="n">
         <v>21043600.09</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>
@@ -22649,7 +22649,7 @@
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>39529119.98</v>
+        <v>39837366.69</v>
       </c>
       <c r="S159" t="n">
         <v>32377746.42</v>
@@ -22658,7 +22658,7 @@
         <v>33990510.52</v>
       </c>
       <c r="U159" t="n">
-        <v>36460688</v>
+        <v>36768934.71</v>
       </c>
       <c r="V159" t="n">
         <v>1612764.1</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>16/04/2026 07:27:49</t>
+          <t>17/04/2026 07:27:32</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>14351</v>
+        <v>18623</v>
       </c>
       <c r="P6" t="n">
         <v>7200</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -1363,22 +1363,22 @@
         <v>490</v>
       </c>
       <c r="P7" t="n">
-        <v>74385.42</v>
+        <v>96530.67999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>332768.03</v>
+        <v>355018.03</v>
       </c>
       <c r="S7" t="n">
-        <v>128004.85</v>
+        <v>150254.85</v>
       </c>
       <c r="T7" t="n">
-        <v>128004.85</v>
+        <v>150254.85</v>
       </c>
       <c r="U7" t="n">
-        <v>258382.61</v>
+        <v>258487.35</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1234387.45</v>
+        <v>1411888.66</v>
       </c>
       <c r="P10" t="n">
         <v>1234134.56</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>956587.76</v>
+        <v>1227268.72</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6496</v>
+        <v>10000.06</v>
       </c>
       <c r="Q23" t="n">
         <v>50000</v>
@@ -3612,13 +3612,13 @@
         <v>75842.42</v>
       </c>
       <c r="S23" t="n">
-        <v>1440</v>
+        <v>6040.6</v>
       </c>
       <c r="T23" t="n">
-        <v>1440</v>
+        <v>6040.6</v>
       </c>
       <c r="U23" t="n">
-        <v>69346.42</v>
+        <v>65842.36</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>338939.23</v>
+        <v>487833.75</v>
       </c>
       <c r="P29" t="n">
         <v>315775.36</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2272907.97</v>
+        <v>2321926.53</v>
       </c>
       <c r="P31" t="n">
         <v>800034.36</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>85144.78999999999</v>
+        <v>85560.27</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>550207.78</v>
+        <v>552868.79</v>
       </c>
       <c r="P35" t="n">
         <v>2931914.44</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
         <v>650000</v>
       </c>
       <c r="O43" t="n">
-        <v>114789.89</v>
+        <v>229579.78</v>
       </c>
       <c r="P43" t="n">
         <v>406043.22</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -6540,10 +6540,10 @@
         <v>93886</v>
       </c>
       <c r="O44" t="n">
-        <v>788997.71</v>
+        <v>814775.9399999999</v>
       </c>
       <c r="P44" t="n">
-        <v>374469.78</v>
+        <v>380793.78</v>
       </c>
       <c r="Q44" t="n">
         <v>1186346</v>
@@ -6552,13 +6552,13 @@
         <v>15237352.51</v>
       </c>
       <c r="S44" t="n">
-        <v>3172777.22</v>
+        <v>3177330.5</v>
       </c>
       <c r="T44" t="n">
-        <v>3172777.22</v>
+        <v>3177330.5</v>
       </c>
       <c r="U44" t="n">
-        <v>14862882.73</v>
+        <v>14856558.73</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>492900</v>
+        <v>486700</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -10040,7 +10040,7 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>367350</v>
+        <v>361150</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -10469,16 +10469,16 @@
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>52292.66</v>
+        <v>60292.66</v>
       </c>
       <c r="S72" t="n">
-        <v>50000</v>
+        <v>58000</v>
       </c>
       <c r="T72" t="n">
-        <v>50000</v>
+        <v>58000</v>
       </c>
       <c r="U72" t="n">
-        <v>51168.01</v>
+        <v>59168.01</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>50870.47</v>
+        <v>81922.86</v>
       </c>
       <c r="P73" t="n">
         <v>12692.75</v>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12280,7 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="P85" t="n">
         <v>2000</v>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>4551281.7</v>
+        <v>7383237.78</v>
       </c>
       <c r="S96" t="n">
         <v>4551281.7</v>
@@ -13838,7 +13838,7 @@
         <v>4551281.7</v>
       </c>
       <c r="U96" t="n">
-        <v>4551281.7</v>
+        <v>7383237.78</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -16480,7 +16480,7 @@
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>80987.12</v>
+        <v>161974.24</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -17609,16 +17609,16 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>181649.82</v>
+        <v>190072.94</v>
       </c>
       <c r="S123" t="n">
-        <v>133323</v>
+        <v>141746.12</v>
       </c>
       <c r="T123" t="n">
-        <v>135117</v>
+        <v>143540.12</v>
       </c>
       <c r="U123" t="n">
-        <v>179574.82</v>
+        <v>187997.94</v>
       </c>
       <c r="V123" t="n">
         <v>1794</v>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>22225.6</v>
+        <v>33338.4</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -17880,7 +17880,7 @@
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>218108.24</v>
+        <v>246715.46</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -18300,7 +18300,7 @@
         <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>3935.7</v>
+        <v>5903.55</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -19843,22 +19843,22 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="Q139" t="n">
         <v>15000</v>
       </c>
       <c r="R139" t="n">
-        <v>10800</v>
+        <v>21600</v>
       </c>
       <c r="S139" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="U139" t="n">
-        <v>10800</v>
+        <v>10200</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -20549,7 +20549,7 @@
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>38820625.08</v>
+        <v>40835555</v>
       </c>
       <c r="S144" t="n">
         <v>38820625.08</v>
@@ -20558,7 +20558,7 @@
         <v>38820625.08</v>
       </c>
       <c r="U144" t="n">
-        <v>38820625.08</v>
+        <v>40835555</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>59682641.06</v>
+        <v>59791184.99</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -21511,7 +21511,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>29380182.6</v>
+        <v>29431997.31</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>18074598.76</v>
+        <v>22994007.34</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21672,10 +21672,10 @@
         <v>129341289.91</v>
       </c>
       <c r="S152" t="n">
-        <v>38058584.37</v>
+        <v>73158584.37</v>
       </c>
       <c r="T152" t="n">
-        <v>38502584.37</v>
+        <v>73602584.37</v>
       </c>
       <c r="U152" t="n">
         <v>79443026</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -21940,7 +21940,7 @@
         <v>1406720</v>
       </c>
       <c r="O154" t="n">
-        <v>224000</v>
+        <v>336000</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>17/04/2026 07:27:32</t>
+          <t>18/04/2026 07:00:38</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ159"/>
+  <dimension ref="A1:AJ160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -17307,11 +17307,11 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3132800</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -17320,43 +17320,43 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>3132800</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>3169600</v>
+        <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>3949200</v>
+        <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="X121" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1421600</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>8705439.67</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
         <v>5</v>
@@ -17379,22 +17379,22 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Kenji Ito</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>16923298.94</v>
+        <v>3132800</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -17460,43 +17460,43 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>16923298.94</v>
+        <v>3132800</v>
       </c>
       <c r="P122" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="R122" t="n">
-        <v>23851875.51</v>
+        <v>8578400</v>
       </c>
       <c r="S122" t="n">
-        <v>21926109.23</v>
+        <v>3169600</v>
       </c>
       <c r="T122" t="n">
-        <v>22593123.43</v>
+        <v>3949200</v>
       </c>
       <c r="U122" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="V122" t="n">
-        <v>667014.2</v>
+        <v>779600</v>
       </c>
       <c r="W122" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="X122" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="AA122" t="n">
-        <v>22426358</v>
+        <v>8705439.67</v>
       </c>
       <c r="AB122" t="n">
         <v>5</v>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -17591,7 +17591,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>64653</v>
+        <v>16923298.94</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
@@ -17600,34 +17600,34 @@
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>62133</v>
+        <v>16923298.94</v>
       </c>
       <c r="P123" t="n">
-        <v>2075</v>
+        <v>1425517.51</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>190072.94</v>
+        <v>23851875.51</v>
       </c>
       <c r="S123" t="n">
-        <v>141746.12</v>
+        <v>21926109.23</v>
       </c>
       <c r="T123" t="n">
-        <v>143540.12</v>
+        <v>22593123.43</v>
       </c>
       <c r="U123" t="n">
-        <v>187997.94</v>
+        <v>22426358</v>
       </c>
       <c r="V123" t="n">
-        <v>1794</v>
+        <v>667014.2</v>
       </c>
       <c r="W123" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="X123" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="Y123" t="n">
         <v>0</v>
@@ -17636,7 +17636,7 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="AB123" t="n">
         <v>5</v>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH123" t="inlineStr">
@@ -17669,12 +17669,12 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -17731,7 +17731,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>33338.4</v>
+        <v>64653</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -17740,34 +17740,34 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>33338.4</v>
+        <v>62133</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2075</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>95531.96000000001</v>
+        <v>190072.94</v>
       </c>
       <c r="S124" t="n">
-        <v>95531.96000000001</v>
+        <v>141746.12</v>
       </c>
       <c r="T124" t="n">
-        <v>95531.96000000001</v>
+        <v>143540.12</v>
       </c>
       <c r="U124" t="n">
-        <v>95531.96000000001</v>
+        <v>187997.94</v>
       </c>
       <c r="V124" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="W124" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="X124" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="AB124" t="n">
         <v>5</v>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
@@ -17809,12 +17809,12 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -17857,7 +17857,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -17871,7 +17871,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>246715.46</v>
+        <v>33338.4</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -17880,7 +17880,7 @@
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>246715.46</v>
+        <v>33338.4</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -17889,25 +17889,25 @@
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>2537927</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="S125" t="n">
-        <v>1074549.58</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="T125" t="n">
-        <v>1131764.02</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="U125" t="n">
-        <v>2537927</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="V125" t="n">
-        <v>57214.44</v>
+        <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="X125" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
@@ -17916,7 +17916,7 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="AB125" t="n">
         <v>5</v>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
@@ -17949,12 +17949,12 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>903570.96</v>
+        <v>246715.46</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -18020,34 +18020,34 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>876799.9</v>
+        <v>246715.46</v>
       </c>
       <c r="P126" t="n">
-        <v>743505.8100000001</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3802648.2</v>
+        <v>2537927</v>
       </c>
       <c r="S126" t="n">
-        <v>1959769.84</v>
+        <v>1074549.58</v>
       </c>
       <c r="T126" t="n">
-        <v>1959769.84</v>
+        <v>1131764.02</v>
       </c>
       <c r="U126" t="n">
-        <v>3059142.39</v>
+        <v>2537927</v>
       </c>
       <c r="V126" t="n">
-        <v>0</v>
+        <v>57214.44</v>
       </c>
       <c r="W126" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="X126" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="Y126" t="n">
         <v>0</v>
@@ -18056,7 +18056,7 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="AB126" t="n">
         <v>5</v>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -18147,11 +18147,11 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>368.19</v>
+        <v>903570.96</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -18160,34 +18160,34 @@
         <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>156.13</v>
+        <v>876799.9</v>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>743505.8100000001</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>80100</v>
+        <v>3802648.2</v>
       </c>
       <c r="S127" t="n">
-        <v>80100</v>
+        <v>1959769.84</v>
       </c>
       <c r="T127" t="n">
-        <v>80100</v>
+        <v>1959769.84</v>
       </c>
       <c r="U127" t="n">
-        <v>80100</v>
+        <v>3059142.39</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="X127" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="Y127" t="n">
         <v>0</v>
@@ -18196,7 +18196,7 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="AB127" t="n">
         <v>5</v>
@@ -18224,17 +18224,17 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -18287,11 +18287,11 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>5903.55</v>
+        <v>368.19</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
@@ -18300,7 +18300,7 @@
         <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>5903.55</v>
+        <v>156.13</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -18309,25 +18309,25 @@
         <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="S128" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="T128" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="U128" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="X128" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
@@ -18336,7 +18336,7 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="AB128" t="n">
         <v>5</v>
@@ -18359,22 +18359,22 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -18407,17 +18407,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>5903.55</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
@@ -18440,43 +18440,43 @@
         <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>5903.55</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T129" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U129" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="X129" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="Y129" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="Z129" t="n">
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="AB129" t="n">
         <v>5</v>
@@ -18484,12 +18484,12 @@
       <c r="AC129" t="inlineStr"/>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -18499,7 +18499,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
@@ -18509,12 +18509,12 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -18547,7 +18547,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -18586,7 +18586,7 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>200000</v>
+        <v>220000</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -18604,19 +18604,19 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="X130" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Y130" t="n">
-        <v>200000</v>
+        <v>220000</v>
       </c>
       <c r="Z130" t="n">
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="AB130" t="n">
         <v>5</v>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
+          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -18649,12 +18649,12 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -18726,7 +18726,7 @@
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>75000</v>
+        <v>200000</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
@@ -18744,19 +18744,19 @@
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="X131" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y131" t="n">
-        <v>75000</v>
+        <v>200000</v>
       </c>
       <c r="Z131" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AB131" t="n">
         <v>5</v>
@@ -18769,7 +18769,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
+          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -18789,12 +18789,12 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -18823,21 +18823,21 @@
         <v>422</v>
       </c>
       <c r="F132" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -18866,7 +18866,7 @@
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -18884,19 +18884,19 @@
         <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="X132" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA132" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
         <v>5</v>
@@ -18904,12 +18904,12 @@
       <c r="AC132" t="inlineStr"/>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -18919,7 +18919,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
@@ -19000,43 +19000,43 @@
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>127000</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="U133" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>3596273</v>
+        <v>11949</v>
       </c>
       <c r="X133" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="Y133" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="AB133" t="n">
         <v>5</v>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -19059,7 +19059,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH133" t="inlineStr">
@@ -19069,12 +19069,12 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -19131,7 +19131,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
@@ -19140,43 +19140,43 @@
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="S134" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="T134" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="U134" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
       </c>
       <c r="W134" t="n">
-        <v>5374</v>
+        <v>3596273</v>
       </c>
       <c r="X134" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="Y134" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="Z134" t="n">
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="AB134" t="n">
         <v>5</v>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH134" t="inlineStr">
@@ -19209,12 +19209,12 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -19304,19 +19304,19 @@
         <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>80612</v>
+        <v>5374</v>
       </c>
       <c r="X135" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="Y135" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="AB135" t="n">
         <v>5</v>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AH135" t="inlineStr">
@@ -19349,12 +19349,12 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -19411,7 +19411,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>110421.01</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -19420,43 +19420,43 @@
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>73756.84</v>
+        <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>551.08</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>5040463.02</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>570925.76</v>
+        <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>570925.76</v>
+        <v>0</v>
       </c>
       <c r="U136" t="n">
-        <v>5039911.94</v>
+        <v>0</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>5870981</v>
+        <v>80612</v>
       </c>
       <c r="X136" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="Y136" t="n">
-        <v>5054381</v>
+        <v>69388</v>
       </c>
       <c r="Z136" t="n">
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="AB136" t="n">
         <v>5</v>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH136" t="inlineStr">
@@ -19489,12 +19489,12 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -19547,11 +19547,11 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>110421.01</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -19560,43 +19560,43 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>73756.84</v>
       </c>
       <c r="P137" t="n">
-        <v>925</v>
+        <v>551.08</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>1900</v>
+        <v>5040463.02</v>
       </c>
       <c r="S137" t="n">
-        <v>300</v>
+        <v>570925.76</v>
       </c>
       <c r="T137" t="n">
-        <v>300</v>
+        <v>570925.76</v>
       </c>
       <c r="U137" t="n">
-        <v>975</v>
+        <v>5039911.94</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>1000</v>
+        <v>5870981</v>
       </c>
       <c r="X137" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="Y137" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="Z137" t="n">
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="AB137" t="n">
         <v>5</v>
@@ -19624,17 +19624,17 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -19667,17 +19667,17 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -19703,40 +19703,40 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="Q138" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U138" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
       </c>
       <c r="W138" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X138" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="Y138" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB138" t="n">
         <v>5</v>
@@ -19744,12 +19744,12 @@
       <c r="AC138" t="inlineStr"/>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -19759,22 +19759,22 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -19800,24 +19800,24 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F139" t="n">
         <v>4026</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -19843,40 +19843,40 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>11400</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>15000</v>
+        <v>75000</v>
       </c>
       <c r="R139" t="n">
-        <v>21600</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="U139" t="n">
-        <v>10200</v>
+        <v>0</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>22143</v>
+        <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="Y139" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="Z139" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA139" t="n">
-        <v>46881</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
         <v>5</v>
@@ -19884,12 +19884,12 @@
       <c r="AC139" t="inlineStr"/>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -19899,7 +19899,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH139" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -19983,40 +19983,40 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R140" t="n">
-        <v>33669</v>
+        <v>21600</v>
       </c>
       <c r="S140" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="U140" t="n">
-        <v>33669</v>
+        <v>10200</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
       </c>
       <c r="W140" t="n">
-        <v>33669</v>
+        <v>22143</v>
       </c>
       <c r="X140" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="Y140" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="Z140" t="n">
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="AB140" t="n">
         <v>5</v>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH140" t="inlineStr">
@@ -20049,12 +20049,12 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -20087,17 +20087,17 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -20126,10 +20126,10 @@
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>127873.65</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -20138,25 +20138,25 @@
         <v>0</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>27873.65</v>
+        <v>33669</v>
       </c>
       <c r="X141" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="Y141" t="n">
-        <v>127873.65</v>
+        <v>187297</v>
       </c>
       <c r="Z141" t="n">
-        <v>72126.35000000001</v>
+        <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>27873.65</v>
+        <v>220966</v>
       </c>
       <c r="AB141" t="n">
         <v>5</v>
@@ -20164,12 +20164,12 @@
       <c r="AC141" t="inlineStr"/>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH141" t="inlineStr">
@@ -20189,12 +20189,12 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -20206,12 +20206,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20220,19 +20220,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F142" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L142" t="n">
@@ -20257,7 +20257,7 @@
         <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -20266,37 +20266,37 @@
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>127873.65</v>
       </c>
       <c r="R142" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>150000</v>
+        <v>27873.65</v>
       </c>
       <c r="X142" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>127873.65</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>72126.35000000001</v>
       </c>
       <c r="AA142" t="n">
-        <v>150000</v>
+        <v>27873.65</v>
       </c>
       <c r="AB142" t="n">
         <v>5</v>
@@ -20304,12 +20304,12 @@
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -20324,17 +20324,17 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
+          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -20387,7 +20387,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -20397,7 +20397,7 @@
         <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -20409,34 +20409,34 @@
         <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U143" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="X143" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>589773</v>
+        <v>150000</v>
       </c>
       <c r="AB143" t="n">
         <v>5</v>
@@ -20459,65 +20459,65 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F144" t="n">
         <v>4010</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -20531,7 +20531,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>12940208.36</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -20540,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>12940208.36</v>
+        <v>0</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
@@ -20549,34 +20549,34 @@
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
       </c>
       <c r="W144" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="X144" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Z144" t="n">
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="AB144" t="n">
         <v>5</v>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -20599,7 +20599,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH144" t="inlineStr">
@@ -20609,12 +20609,12 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -20671,7 +20671,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>12940208.36</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -20680,7 +20680,7 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>12940208.36</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -20689,34 +20689,34 @@
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="S145" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>600437</v>
+        <v>40835555</v>
       </c>
       <c r="X145" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="Y145" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Z145" t="n">
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="AB145" t="n">
         <v>5</v>
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
@@ -20749,12 +20749,12 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -20776,23 +20776,23 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F146" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -20844,19 +20844,19 @@
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="X146" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Z146" t="n">
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="AB146" t="n">
         <v>5</v>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -20889,12 +20889,12 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>44906100</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -20957,7 +20957,7 @@
         <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -20969,7 +20969,7 @@
         <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -20978,16 +20978,16 @@
         <v>0</v>
       </c>
       <c r="U147" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>361510</v>
+        <v>1000</v>
       </c>
       <c r="X147" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y147" t="n">
         <v>0</v>
@@ -20996,7 +20996,7 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>361510</v>
+        <v>1000</v>
       </c>
       <c r="AB147" t="n">
         <v>5</v>
@@ -21019,7 +21019,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>Aquisição de Imóveis</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH147" t="inlineStr">
@@ -21029,12 +21029,12 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -21060,14 +21060,14 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F148" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -21077,7 +21077,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44906100</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -21091,52 +21091,52 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>59791184.99</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="O148" t="n">
-        <v>59682641.06</v>
+        <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>21043600.09</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>158978189.3</v>
+        <v>361510</v>
       </c>
       <c r="S148" t="n">
-        <v>135266690.42</v>
+        <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>140706402.81</v>
+        <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>137934589.21</v>
+        <v>361510</v>
       </c>
       <c r="V148" t="n">
-        <v>5439712.39</v>
+        <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>165715582</v>
+        <v>361510</v>
       </c>
       <c r="X148" t="n">
-        <v>171813039</v>
+        <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA148" t="n">
         <v>361510</v>
-      </c>
-      <c r="AA148" t="n">
-        <v>171451529</v>
       </c>
       <c r="AB148" t="n">
         <v>5</v>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Aquisição de Imóveis</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
@@ -21169,12 +21169,12 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -21217,21 +21217,21 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>59791184.99</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -21240,43 +21240,43 @@
         <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
+        <v>59682641.06</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>21043600.09</v>
       </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>158978189.3</v>
       </c>
       <c r="S149" t="n">
-        <v>0</v>
+        <v>135266690.42</v>
       </c>
       <c r="T149" t="n">
-        <v>0</v>
+        <v>140706402.81</v>
       </c>
       <c r="U149" t="n">
-        <v>0</v>
+        <v>137934589.21</v>
       </c>
       <c r="V149" t="n">
-        <v>0</v>
+        <v>5439712.39</v>
       </c>
       <c r="W149" t="n">
-        <v>2000</v>
+        <v>165715582</v>
       </c>
       <c r="X149" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="Y149" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Z149" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="AA149" t="n">
-        <v>2000</v>
+        <v>171451529</v>
       </c>
       <c r="AB149" t="n">
         <v>5</v>
@@ -21294,27 +21294,27 @@
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
+          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -21362,12 +21362,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -21404,10 +21404,10 @@
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X150" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="Y150" t="n">
         <v>0</v>
@@ -21416,7 +21416,7 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AB150" t="n">
         <v>5</v>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AF150" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG150" t="inlineStr">
@@ -21444,17 +21444,17 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
+          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -21497,21 +21497,21 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>29431997.31</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -21520,43 +21520,43 @@
         <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>26588094.6</v>
+        <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>60670522</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>197559544</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>107626518.4</v>
+        <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>107626518.4</v>
+        <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>136889022</v>
+        <v>0</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="X151" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="Y151" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Z151" t="n">
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AB151" t="n">
         <v>5</v>
@@ -21574,27 +21574,27 @@
       </c>
       <c r="AF151" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>22994007.34</v>
+        <v>29431997.31</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21660,43 +21660,43 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>17774241.01</v>
+        <v>26588094.6</v>
       </c>
       <c r="P152" t="n">
-        <v>49898263.91</v>
+        <v>60670522</v>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>129341289.91</v>
+        <v>197559544</v>
       </c>
       <c r="S152" t="n">
-        <v>73158584.37</v>
+        <v>107626518.4</v>
       </c>
       <c r="T152" t="n">
-        <v>73602584.37</v>
+        <v>107626518.4</v>
       </c>
       <c r="U152" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="V152" t="n">
-        <v>444000</v>
+        <v>0</v>
       </c>
       <c r="W152" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="X152" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="Y152" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Z152" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>82235403</v>
+        <v>141616875</v>
       </c>
       <c r="AB152" t="n">
         <v>5</v>
@@ -21719,7 +21719,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
@@ -21729,12 +21729,12 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -21782,16 +21782,16 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>22994007.34</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -21800,43 +21800,43 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>0</v>
+        <v>17774241.01</v>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>49898263.91</v>
       </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>129341289.91</v>
       </c>
       <c r="S153" t="n">
-        <v>0</v>
+        <v>73158584.37</v>
       </c>
       <c r="T153" t="n">
-        <v>0</v>
+        <v>73602584.37</v>
       </c>
       <c r="U153" t="n">
-        <v>0</v>
+        <v>79443026</v>
       </c>
       <c r="V153" t="n">
-        <v>0</v>
+        <v>444000</v>
       </c>
       <c r="W153" t="n">
-        <v>2000</v>
+        <v>79443026</v>
       </c>
       <c r="X153" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="Y153" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Z153" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="AA153" t="n">
-        <v>2000</v>
+        <v>82235403</v>
       </c>
       <c r="AB153" t="n">
         <v>5</v>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="AF153" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG153" t="inlineStr">
@@ -21864,17 +21864,17 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
+          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -21917,30 +21917,30 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>33913900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>336000</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>336000</v>
+        <v>0</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -21949,25 +21949,25 @@
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="U154" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="X154" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y154" t="n">
         <v>0</v>
@@ -21976,7 +21976,7 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="AB154" t="n">
         <v>5</v>
@@ -21994,39 +21994,39 @@
       </c>
       <c r="AF154" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>Transferência entre Órgãos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -22040,24 +22040,24 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F155" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -22071,16 +22071,16 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>336000</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
+        <v>336000</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -22089,25 +22089,25 @@
         <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S155" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="T155" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U155" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="X155" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y155" t="n">
         <v>0</v>
@@ -22116,7 +22116,7 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="AB155" t="n">
         <v>5</v>
@@ -22124,12 +22124,12 @@
       <c r="AC155" t="inlineStr"/>
       <c r="AD155" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -22139,7 +22139,7 @@
       </c>
       <c r="AG155" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AH155" t="inlineStr">
@@ -22149,12 +22149,12 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -22197,7 +22197,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -22244,10 +22244,10 @@
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X156" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="Y156" t="n">
         <v>0</v>
@@ -22256,7 +22256,7 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AB156" t="n">
         <v>5</v>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH156" t="inlineStr">
@@ -22289,12 +22289,12 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -22320,24 +22320,24 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F157" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>DTIC</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -22384,10 +22384,10 @@
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X157" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="Y157" t="n">
         <v>0</v>
@@ -22396,7 +22396,7 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AB157" t="n">
         <v>5</v>
@@ -22404,12 +22404,12 @@
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>DTIC - Desenvolvimento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -22419,7 +22419,7 @@
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
@@ -22429,12 +22429,12 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -22460,24 +22460,24 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F158" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -22524,10 +22524,10 @@
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X158" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y158" t="n">
         <v>0</v>
@@ -22536,7 +22536,7 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB158" t="n">
         <v>5</v>
@@ -22544,12 +22544,12 @@
       <c r="AC158" t="inlineStr"/>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC - Desenvolvimento</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -22559,22 +22559,22 @@
       </c>
       <c r="AG158" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
         </is>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>18/04/2026 07:00:38</t>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>
@@ -22622,16 +22622,16 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>24479179.14</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -22640,34 +22640,34 @@
         <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>24296479.14</v>
+        <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>3068431.98</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>39837366.69</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
-        <v>32377746.42</v>
+        <v>0</v>
       </c>
       <c r="T159" t="n">
-        <v>33990510.52</v>
+        <v>0</v>
       </c>
       <c r="U159" t="n">
-        <v>36768934.71</v>
+        <v>0</v>
       </c>
       <c r="V159" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X159" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="Y159" t="n">
         <v>0</v>
@@ -22676,7 +22676,7 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
         <v>5</v>
@@ -22694,27 +22694,167 @@
       </c>
       <c r="AF159" t="inlineStr">
         <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>19/04/2026 07:03:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>422</v>
+      </c>
+      <c r="F160" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>24479179.14</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>24296479.14</v>
+      </c>
+      <c r="P160" t="n">
+        <v>3068431.98</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>39837366.69</v>
+      </c>
+      <c r="S160" t="n">
+        <v>32377746.42</v>
+      </c>
+      <c r="T160" t="n">
+        <v>33990510.52</v>
+      </c>
+      <c r="U160" t="n">
+        <v>36768934.71</v>
+      </c>
+      <c r="V160" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="W160" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X160" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC160" t="inlineStr"/>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
           <t>08 - Recusos Vinculados</t>
         </is>
       </c>
-      <c r="AG159" t="inlineStr">
+      <c r="AG160" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AH159" t="inlineStr">
+      <c r="AH160" t="inlineStr">
         <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AI159" t="inlineStr">
+      <c r="AI160" t="inlineStr">
         <is>
           <t>90.10.14.422.4019.6160.33503900.08.1.759.0958</t>
         </is>
       </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>18/04/2026 07:00:38</t>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>19/04/2026 07:03:01</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>19/04/2026 07:03:01</t>
+          <t>20/04/2026 08:00:50</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>20/04/2026 08:00:50</t>
+          <t>21/04/2026 07:31:08</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2958116.16</v>
+        <v>3081610.16</v>
       </c>
       <c r="P3" t="n">
         <v>220570.58</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>18623</v>
+        <v>19513</v>
       </c>
       <c r="P6" t="n">
         <v>7200</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2321926.53</v>
+        <v>2328209.86</v>
       </c>
       <c r="P31" t="n">
         <v>800034.36</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>21/04/2026 07:31:08</t>
+          <t>22/04/2026 07:30:16</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8220.799999999999</v>
+        <v>11982.8</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>31684.04</v>
+        <v>34331.79</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1506178.6</v>
+        <v>1591106.18</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1783,13 +1783,13 @@
         <v>1411888.66</v>
       </c>
       <c r="P10" t="n">
-        <v>1234134.56</v>
+        <v>1253945.22</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>12736833.25</v>
+        <v>12796283.42</v>
       </c>
       <c r="S10" t="n">
         <v>7776313.45</v>
@@ -1798,7 +1798,7 @@
         <v>7882464</v>
       </c>
       <c r="U10" t="n">
-        <v>11502698.69</v>
+        <v>11542338.2</v>
       </c>
       <c r="V10" t="n">
         <v>106150.55</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>21527.07</v>
+        <v>21602.07</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1227268.72</v>
+        <v>1414911.08</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>488084.38</v>
+        <v>488880.75</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2459996.15</v>
+        <v>2585245.06</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>86945.48</v>
+        <v>107359.77</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>26138.53</v>
+        <v>42156.29</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -5271,16 +5271,16 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>832228.22</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>832062.6</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>552868.79</v>
       </c>
       <c r="P35" t="n">
         <v>2931914.44</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>846303.71</v>
+        <v>855872.8100000001</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6543,22 +6543,22 @@
         <v>814775.9399999999</v>
       </c>
       <c r="P44" t="n">
-        <v>380793.78</v>
+        <v>465163.56</v>
       </c>
       <c r="Q44" t="n">
         <v>1186346</v>
       </c>
       <c r="R44" t="n">
-        <v>15237352.51</v>
+        <v>15333661.41</v>
       </c>
       <c r="S44" t="n">
-        <v>3177330.5</v>
+        <v>3273639.4</v>
       </c>
       <c r="T44" t="n">
-        <v>3177330.5</v>
+        <v>3273639.4</v>
       </c>
       <c r="U44" t="n">
-        <v>14856558.73</v>
+        <v>14868497.85</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
         <v>5495750</v>
       </c>
       <c r="W54" t="n">
-        <v>18758759</v>
+        <v>18568759</v>
       </c>
       <c r="X54" t="n">
         <v>22965724</v>
@@ -7973,10 +7973,10 @@
         <v>4186869</v>
       </c>
       <c r="Z54" t="n">
-        <v>20096</v>
+        <v>210096</v>
       </c>
       <c r="AA54" t="n">
-        <v>22945628</v>
+        <v>22755628</v>
       </c>
       <c r="AB54" t="n">
         <v>5</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>30781.48</v>
+        <v>30850.58</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>55924.58</v>
+        <v>55993.68</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="O109" t="n">
         <v>55924.58</v>
@@ -15664,7 +15664,7 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>237085</v>
+        <v>427085</v>
       </c>
       <c r="X109" t="n">
         <v>237085</v>
@@ -15676,7 +15676,7 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>237085</v>
+        <v>427085</v>
       </c>
       <c r="AB109" t="n">
         <v>5</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>6869.89</v>
+        <v>6998.62</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -16331,7 +16331,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>21056.72</v>
+        <v>21384.72</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16477,7 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>564000</v>
       </c>
       <c r="O115" t="n">
         <v>161974.24</v>
@@ -16504,7 +16504,7 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>519437</v>
+        <v>1083437</v>
       </c>
       <c r="X115" t="n">
         <v>547269</v>
@@ -16516,7 +16516,7 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>547269</v>
+        <v>1111269</v>
       </c>
       <c r="AB115" t="n">
         <v>5</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>665756.61</v>
+        <v>666215.36</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
@@ -16623,28 +16623,28 @@
         <v>642287.52</v>
       </c>
       <c r="P116" t="n">
-        <v>2060687.58</v>
+        <v>2102872.47</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>5677014.58</v>
+        <v>5725169.27</v>
       </c>
       <c r="S116" t="n">
-        <v>2660248.13</v>
+        <v>2708402.82</v>
       </c>
       <c r="T116" t="n">
-        <v>2660568.13</v>
+        <v>2708722.82</v>
       </c>
       <c r="U116" t="n">
-        <v>3616327</v>
+        <v>3622296.8</v>
       </c>
       <c r="V116" t="n">
         <v>320</v>
       </c>
       <c r="W116" t="n">
-        <v>4651261</v>
+        <v>4087261</v>
       </c>
       <c r="X116" t="n">
         <v>4953156</v>
@@ -16653,10 +16653,10 @@
         <v>301895</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>564000</v>
       </c>
       <c r="AA116" t="n">
-        <v>4953156</v>
+        <v>4389156</v>
       </c>
       <c r="AB116" t="n">
         <v>5</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -19551,7 +19551,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>110421.01</v>
+        <v>110455.56</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -21231,7 +21231,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>59791184.99</v>
+        <v>59803761.71</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -21791,7 +21791,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>22994007.34</v>
+        <v>23174007.34</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -21812,10 +21812,10 @@
         <v>129341289.91</v>
       </c>
       <c r="S153" t="n">
-        <v>73158584.37</v>
+        <v>78558584.37</v>
       </c>
       <c r="T153" t="n">
-        <v>73602584.37</v>
+        <v>79002584.37</v>
       </c>
       <c r="U153" t="n">
         <v>79443026</v>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>22/04/2026 07:30:16</t>
+          <t>23/04/2026 07:34:36</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ160"/>
+  <dimension ref="A1:AJ161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>115966</v>
       </c>
       <c r="O8" t="n">
-        <v>24432.42</v>
+        <v>31684.04</v>
       </c>
       <c r="P8" t="n">
         <v>181083.4</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1591106.18</v>
+        <v>1820051.18</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1411888.66</v>
+        <v>1455848.66</v>
       </c>
       <c r="P10" t="n">
         <v>1253945.22</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2165.67</v>
+        <v>2775.93</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>488880.75</v>
+        <v>489255.05</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2585245.06</v>
+        <v>3285707.39</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4732,10 +4732,10 @@
         <v>18625777.17</v>
       </c>
       <c r="S31" t="n">
-        <v>16777817.19</v>
+        <v>16941801.99</v>
       </c>
       <c r="T31" t="n">
-        <v>16784389.84</v>
+        <v>16948374.64</v>
       </c>
       <c r="U31" t="n">
         <v>17825742.81</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>832062.6</v>
+        <v>832228.22</v>
       </c>
       <c r="P35" t="n">
         <v>2931914.44</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2708.39</v>
+        <v>3036.39</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>855872.8100000001</v>
+        <v>896173.73</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -8524,13 +8524,13 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
         <v>200000</v>
       </c>
       <c r="Y58" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -8804,13 +8804,13 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
         <v>100000</v>
       </c>
       <c r="Y60" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -8944,13 +8944,13 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
         <v>100000</v>
       </c>
       <c r="Y61" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -9084,13 +9084,13 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
         <v>350000</v>
       </c>
       <c r="Y62" t="n">
-        <v>700000</v>
+        <v>1050000</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -9364,13 +9364,13 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
         <v>200000</v>
       </c>
       <c r="Y64" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -9504,13 +9504,13 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>2300000</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
         <v>2300000</v>
       </c>
       <c r="Y65" t="n">
-        <v>4600000</v>
+        <v>6900000</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -10204,10 +10204,10 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
         <v>0</v>
@@ -10216,7 +10216,7 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
         <v>5</v>
@@ -10239,22 +10239,22 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Marina Bragante</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>34.10.14.422.4023.4320.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4023.4320.33503900.00.1.500.7079</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1193382.32</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -10320,7 +10320,7 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>1193382.32</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -10329,34 +10329,34 @@
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1193451</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>1193451</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>1548270.03</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>1193451</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>354819.03</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>1193451</v>
+        <v>3000</v>
       </c>
       <c r="X71" t="n">
-        <v>1671844</v>
+        <v>3000</v>
       </c>
       <c r="Y71" t="n">
-        <v>478393</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1671844</v>
+        <v>3000</v>
       </c>
       <c r="AB71" t="n">
         <v>5</v>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>CPPI - Equipamentos</t>
+          <t>CPPI - Políticas</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>34.10.14.422.4023.4330.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4023.4320.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1193382.32</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -10460,43 +10460,43 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>1193382.32</v>
       </c>
       <c r="P72" t="n">
-        <v>1124.65</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>60292.66</v>
+        <v>1193451</v>
       </c>
       <c r="S72" t="n">
-        <v>58000</v>
+        <v>1193451</v>
       </c>
       <c r="T72" t="n">
-        <v>58000</v>
+        <v>1548270.03</v>
       </c>
       <c r="U72" t="n">
-        <v>59168.01</v>
+        <v>1193451</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>354819.03</v>
       </c>
       <c r="W72" t="n">
-        <v>74955</v>
+        <v>1193451</v>
       </c>
       <c r="X72" t="n">
-        <v>105000</v>
+        <v>1671844</v>
       </c>
       <c r="Y72" t="n">
-        <v>30045</v>
+        <v>478393</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>105000</v>
+        <v>1671844</v>
       </c>
       <c r="AB72" t="n">
         <v>5</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>34.10.14.422.4023.4330.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4023.4330.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10577,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -10591,7 +10591,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>81922.86</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -10600,43 +10600,43 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>81922.86</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>12692.75</v>
+        <v>1124.65</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>538805.72</v>
+        <v>60292.66</v>
       </c>
       <c r="S73" t="n">
-        <v>483609.93</v>
+        <v>58000</v>
       </c>
       <c r="T73" t="n">
-        <v>483609.93</v>
+        <v>58000</v>
       </c>
       <c r="U73" t="n">
-        <v>526112.97</v>
+        <v>59168.01</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>616055</v>
+        <v>74955</v>
       </c>
       <c r="X73" t="n">
-        <v>863000</v>
+        <v>105000</v>
       </c>
       <c r="Y73" t="n">
-        <v>246945</v>
+        <v>30045</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>863000</v>
+        <v>105000</v>
       </c>
       <c r="AB73" t="n">
         <v>5</v>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH73" t="inlineStr">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>34.10.14.422.4023.4330.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4023.4330.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -10717,7 +10717,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>30850.58</v>
+        <v>81922.86</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -10740,43 +10740,43 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>30781.48</v>
+        <v>81922.86</v>
       </c>
       <c r="P74" t="n">
-        <v>2221.59</v>
+        <v>12692.75</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>260366.25</v>
+        <v>538805.72</v>
       </c>
       <c r="S74" t="n">
-        <v>133147</v>
+        <v>483609.93</v>
       </c>
       <c r="T74" t="n">
-        <v>133147</v>
+        <v>483609.93</v>
       </c>
       <c r="U74" t="n">
-        <v>258144.66</v>
+        <v>526112.97</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>938683</v>
+        <v>616055</v>
       </c>
       <c r="X74" t="n">
-        <v>1314953</v>
+        <v>863000</v>
       </c>
       <c r="Y74" t="n">
-        <v>376270</v>
+        <v>246945</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1314953</v>
+        <v>863000</v>
       </c>
       <c r="AB74" t="n">
         <v>5</v>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH74" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>34.10.14.422.4023.4330.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4023.4330.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -10867,11 +10867,11 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>953.49</v>
+        <v>30850.58</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -10880,43 +10880,43 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>946.3</v>
+        <v>30781.48</v>
       </c>
       <c r="P75" t="n">
-        <v>450</v>
+        <v>2221.59</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>21720</v>
+        <v>260366.25</v>
       </c>
       <c r="S75" t="n">
-        <v>21270</v>
+        <v>133147</v>
       </c>
       <c r="T75" t="n">
-        <v>21720</v>
+        <v>133147</v>
       </c>
       <c r="U75" t="n">
-        <v>21270</v>
+        <v>258144.66</v>
       </c>
       <c r="V75" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>21270</v>
+        <v>938683</v>
       </c>
       <c r="X75" t="n">
-        <v>21270</v>
+        <v>1314953</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>376270</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>21270</v>
+        <v>1314953</v>
       </c>
       <c r="AB75" t="n">
         <v>5</v>
@@ -10944,17 +10944,17 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>34.10.14.422.4023.4330.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4023.4330.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -10987,17 +10987,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPPI</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -11007,11 +11007,11 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>953.49</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -11020,43 +11020,43 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>946.3</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="Q76" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>21720</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>21720</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="X76" t="n">
-        <v>100000</v>
+        <v>21270</v>
       </c>
       <c r="Y76" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="AB76" t="n">
         <v>5</v>
@@ -11064,12 +11064,12 @@
       <c r="AC76" t="inlineStr"/>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Idoso</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>E2902 - Realização do projeto "Sábios em Ação". Organização: Instituto Mario Américo – IMA</t>
+          <t>CPPI - Equipamentos</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -11079,22 +11079,22 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>34.10.14.422.4023.9028.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4023.4330.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11166,7 +11166,7 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -11184,19 +11184,19 @@
         <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
         <v>100000</v>
       </c>
       <c r="Y77" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AA77" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
         <v>5</v>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>E302 - Formação para Grupos de Terceira Idade em Práticas Artísticas, Educacionais, Esportivas - UNI</t>
+          <t>E2902 - Realização do projeto "Sábios em Ação". Organização: Instituto Mario Américo – IMA</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>34.10.14.422.4023.9038.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4023.9028.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11306,7 +11306,7 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>75000</v>
+        <v>200000</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -11327,16 +11327,16 @@
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y78" t="n">
-        <v>75000</v>
+        <v>300000</v>
       </c>
       <c r="Z78" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AB78" t="n">
         <v>5</v>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>E318 - Formação para Grupos de Terceira Idade em Práticas Artísticas, Educacionais, Esportivas - GAR</t>
+          <t>E302 - Formação para Grupos de Terceira Idade em Práticas Artísticas, Educacionais, Esportivas - UNI</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -11369,12 +11369,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>34.10.14.422.4023.9050.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4023.9038.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -11403,16 +11403,16 @@
         <v>422</v>
       </c>
       <c r="F79" t="n">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -11440,43 +11440,43 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R79" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>1838981</v>
+        <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>2107032</v>
+        <v>75000</v>
       </c>
       <c r="Y79" t="n">
-        <v>268051</v>
+        <v>75000</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA79" t="n">
-        <v>2107032</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
         <v>5</v>
@@ -11484,12 +11484,12 @@
       <c r="AC79" t="inlineStr"/>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>CPIPTD - Equipamentos</t>
+          <t>E318 - Formação para Grupos de Terceira Idade em Práticas Artísticas, Educacionais, Esportivas - GAR</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.2051.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4023.9050.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -11571,7 +11571,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -11580,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
@@ -11589,34 +11589,34 @@
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>30000</v>
+        <v>679177.12</v>
       </c>
       <c r="S80" t="n">
-        <v>30000</v>
+        <v>679177.12</v>
       </c>
       <c r="T80" t="n">
-        <v>30000</v>
+        <v>679177.12</v>
       </c>
       <c r="U80" t="n">
-        <v>30000</v>
+        <v>679177.12</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>69823</v>
+        <v>1838981</v>
       </c>
       <c r="X80" t="n">
-        <v>80000</v>
+        <v>2107032</v>
       </c>
       <c r="Y80" t="n">
-        <v>10177</v>
+        <v>268051</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>80000</v>
+        <v>2107032</v>
       </c>
       <c r="AB80" t="n">
         <v>5</v>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.2051.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4024.2051.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>13052.54</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -11720,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>13052.54</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -11729,34 +11729,34 @@
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>130917</v>
+        <v>30000</v>
       </c>
       <c r="S81" t="n">
-        <v>46118.97</v>
+        <v>30000</v>
       </c>
       <c r="T81" t="n">
-        <v>46118.97</v>
+        <v>30000</v>
       </c>
       <c r="U81" t="n">
-        <v>130917</v>
+        <v>30000</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>130917</v>
+        <v>69823</v>
       </c>
       <c r="X81" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="Y81" t="n">
-        <v>19083</v>
+        <v>10177</v>
       </c>
       <c r="Z81" t="n">
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="AB81" t="n">
         <v>5</v>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.2051.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4024.2051.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -11851,7 +11851,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>13052.54</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -11860,43 +11860,43 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>13052.54</v>
       </c>
       <c r="P82" t="n">
-        <v>23843.36</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>416595.36</v>
+        <v>130917</v>
       </c>
       <c r="S82" t="n">
-        <v>363452.83</v>
+        <v>46118.97</v>
       </c>
       <c r="T82" t="n">
-        <v>363452.83</v>
+        <v>46118.97</v>
       </c>
       <c r="U82" t="n">
-        <v>392752</v>
+        <v>130917</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>392752</v>
+        <v>130917</v>
       </c>
       <c r="X82" t="n">
-        <v>450000</v>
+        <v>150000</v>
       </c>
       <c r="Y82" t="n">
-        <v>57248</v>
+        <v>19083</v>
       </c>
       <c r="Z82" t="n">
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>450000</v>
+        <v>150000</v>
       </c>
       <c r="AB82" t="n">
         <v>5</v>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.2051.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.2051.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>EDH</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -12003,40 +12003,40 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>23843.36</v>
       </c>
       <c r="Q83" t="n">
-        <v>49471</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>345.28</v>
+        <v>416595.36</v>
       </c>
       <c r="S83" t="n">
-        <v>345.28</v>
+        <v>363452.83</v>
       </c>
       <c r="T83" t="n">
-        <v>345.28</v>
+        <v>363452.83</v>
       </c>
       <c r="U83" t="n">
-        <v>345.28</v>
+        <v>392752</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>50000</v>
+        <v>392752</v>
       </c>
       <c r="X83" t="n">
-        <v>50000</v>
+        <v>450000</v>
       </c>
       <c r="Y83" t="n">
-        <v>49471</v>
+        <v>57248</v>
       </c>
       <c r="Z83" t="n">
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>50000</v>
+        <v>450000</v>
       </c>
       <c r="AB83" t="n">
         <v>5</v>
@@ -12044,12 +12044,12 @@
       <c r="AC83" t="inlineStr"/>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Educação em Direitos Humanos</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>EDH</t>
+          <t>CPIPTD - Equipamentos</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.2142.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4024.2051.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -12146,37 +12146,37 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>49471</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>345.28</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>345.28</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>345.28</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>345.28</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>1058</v>
+        <v>50000</v>
       </c>
       <c r="X84" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="Y84" t="n">
-        <v>98942</v>
+        <v>49471</v>
       </c>
       <c r="Z84" t="n">
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="AB84" t="n">
         <v>5</v>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH84" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.2142.33903100.00.1.500.9001</t>
+          <t>34.10.14.422.4024.2142.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -12257,7 +12257,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -12271,7 +12271,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -12280,43 +12280,43 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>49471</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>50000</v>
+        <v>1058</v>
       </c>
       <c r="X85" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="Y85" t="n">
-        <v>49471</v>
+        <v>98942</v>
       </c>
       <c r="Z85" t="n">
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="AB85" t="n">
         <v>5</v>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -12349,12 +12349,12 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.2142.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4024.2142.33903100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12397,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -12420,43 +12420,43 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="P86" t="n">
         <v>2000</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>49471</v>
       </c>
       <c r="R86" t="n">
+        <v>4000</v>
+      </c>
+      <c r="S86" t="n">
         <v>2000</v>
       </c>
-      <c r="S86" t="n">
-        <v>0</v>
-      </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>13341</v>
+        <v>50000</v>
       </c>
       <c r="X86" t="n">
-        <v>1261000</v>
+        <v>50000</v>
       </c>
       <c r="Y86" t="n">
-        <v>1247659</v>
+        <v>49471</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1261000</v>
+        <v>50000</v>
       </c>
       <c r="AB86" t="n">
         <v>5</v>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.2142.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.2142.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -12527,17 +12527,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Selo DH</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>44903900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -12563,13 +12563,13 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -12584,19 +12584,19 @@
         <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>1000</v>
+        <v>13341</v>
       </c>
       <c r="X87" t="n">
-        <v>1000</v>
+        <v>1261000</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1247659</v>
       </c>
       <c r="Z87" t="n">
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1000</v>
+        <v>1261000</v>
       </c>
       <c r="AB87" t="n">
         <v>5</v>
@@ -12604,12 +12604,12 @@
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>Selo Direitos Humanos</t>
+          <t>Educação em Direitos Humanos</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>Selo DH</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.3406.44903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.2142.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -12667,17 +12667,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>Selo DH</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44903900</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -12724,19 +12724,19 @@
         <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X88" t="n">
-        <v>550500</v>
+        <v>1000</v>
       </c>
       <c r="Y88" t="n">
-        <v>550500</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>550500</v>
+        <v>1000</v>
       </c>
       <c r="AB88" t="n">
         <v>5</v>
@@ -12744,12 +12744,12 @@
       <c r="AC88" t="inlineStr"/>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>Desaparecidos</t>
+          <t>Selo Direitos Humanos</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>CLFD - Políticas</t>
+          <t>Selo DH</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Material Permanente</t>
         </is>
       </c>
       <c r="AH88" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4314.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.3406.44903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -12807,17 +12807,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>DMV</t>
+          <t>CLFD</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -12864,19 +12864,19 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>1000</v>
+        <v>550500</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>550500</v>
       </c>
       <c r="Z89" t="n">
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1000</v>
+        <v>550500</v>
       </c>
       <c r="AB89" t="n">
         <v>5</v>
@@ -12884,12 +12884,12 @@
       <c r="AC89" t="inlineStr"/>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>Direito à Memória e Verdade</t>
+          <t>Desaparecidos</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>DMV</t>
+          <t>CLFD - Políticas</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
@@ -12909,12 +12909,12 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4317.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4314.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -12947,17 +12947,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>CPJ</t>
+          <t>DMV</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -13004,10 +13004,10 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y90" t="n">
         <v>0</v>
@@ -13016,7 +13016,7 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB90" t="n">
         <v>5</v>
@@ -13024,12 +13024,12 @@
       <c r="AC90" t="inlineStr"/>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Direito à Memória e Verdade</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>CPJ - Políticas</t>
+          <t>DMV</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -13039,22 +13039,22 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Ricardo Teixeira</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4318.33503900.00.1.500.7061</t>
+          <t>34.10.14.422.4024.4317.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -13107,11 +13107,11 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -13120,7 +13120,7 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -13129,25 +13129,25 @@
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>10919153.01</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>10919153.01</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
@@ -13156,7 +13156,7 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
         <v>5</v>
@@ -13184,17 +13184,17 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Ricardo Teixeira</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4318.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33503900.00.1.500.7061</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -13251,7 +13251,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -13260,7 +13260,7 @@
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
@@ -13269,25 +13269,25 @@
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>30000</v>
+        <v>10919153.01</v>
       </c>
       <c r="S92" t="n">
-        <v>30000</v>
+        <v>2861229.41</v>
       </c>
       <c r="T92" t="n">
-        <v>30000</v>
+        <v>2861229.41</v>
       </c>
       <c r="U92" t="n">
-        <v>30000</v>
+        <v>10919153.01</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="X92" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
@@ -13296,7 +13296,7 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="AB92" t="n">
         <v>5</v>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4318.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -13409,25 +13409,25 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="X93" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
@@ -13436,7 +13436,7 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="AB93" t="n">
         <v>5</v>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH93" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4318.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -13507,17 +13507,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>33804100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -13564,19 +13564,19 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>8373</v>
+        <v>378632</v>
       </c>
       <c r="X94" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="Y94" t="n">
-        <v>2225</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="AB94" t="n">
         <v>5</v>
@@ -13584,12 +13584,12 @@
       <c r="AC94" t="inlineStr"/>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>CPLGBTI - Políticas</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -13599,7 +13599,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>Taxa Rainbow</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH94" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4319.33804100.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -13657,17 +13657,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33804100</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -13704,19 +13704,19 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>4000</v>
+        <v>8373</v>
       </c>
       <c r="X95" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2225</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="AB95" t="n">
         <v>5</v>
@@ -13734,27 +13734,27 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Taxa Rainbow</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4319.33903900.05.1.703.0000</t>
+          <t>34.10.14.422.4024.4319.33804100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -13797,21 +13797,21 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3410465.43</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -13820,7 +13820,7 @@
         <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>2363104.83</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -13829,34 +13829,34 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>7383237.78</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>7383237.78</v>
+        <v>0</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>9813947</v>
+        <v>4000</v>
       </c>
       <c r="X96" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="Y96" t="n">
-        <v>2607835</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="AB96" t="n">
         <v>5</v>
@@ -13874,27 +13874,27 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4319.33904800.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4319.33903900.05.1.703.0000</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -13927,17 +13927,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -13951,7 +13951,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3410465.43</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -13960,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2363104.83</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -13969,34 +13969,34 @@
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>7383237.78</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>7383237.78</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>9813947</v>
       </c>
       <c r="X97" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="Y97" t="n">
-        <v>56000</v>
+        <v>2607835</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="AB97" t="n">
         <v>5</v>
@@ -14004,12 +14004,12 @@
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>CPIPTD - Políticas</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4319.33904800.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -14127,16 +14127,16 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>40000</v>
+        <v>56000</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="Z98" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="AB98" t="n">
         <v>5</v>
@@ -14164,17 +14164,17 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9005</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -14227,7 +14227,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -14237,7 +14237,7 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -14264,19 +14264,19 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="Y99" t="n">
         <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AA99" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
         <v>5</v>
@@ -14304,17 +14304,17 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
+          <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9567</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9005</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -14367,7 +14367,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -14444,17 +14444,17 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
         </is>
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9570</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9567</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -14517,7 +14517,7 @@
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14544,7 +14544,7 @@
         <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="X101" t="n">
         <v>0</v>
@@ -14556,7 +14556,7 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AB101" t="n">
         <v>5</v>
@@ -14584,17 +14584,17 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
         </is>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9571</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9570</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -14627,12 +14627,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="L102" t="n">
@@ -14657,7 +14657,7 @@
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="X102" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
         <v>0</v>
@@ -14696,7 +14696,7 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AB102" t="n">
         <v>5</v>
@@ -14704,12 +14704,12 @@
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>Drogas</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>CPD - Políticas</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -14724,17 +14724,17 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4325.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9571</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -14767,17 +14767,17 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -14791,7 +14791,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3487177.25</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -14800,7 +14800,7 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>3487177.25</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
@@ -14809,25 +14809,25 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="X103" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="Y103" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="AB103" t="n">
         <v>5</v>
@@ -14844,12 +14844,12 @@
       <c r="AC103" t="inlineStr"/>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Drogas</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>CPLGBTI - Equipamentos</t>
+          <t>CPD - Políticas</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH103" t="inlineStr">
@@ -14869,12 +14869,12 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4326.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4325.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -14917,7 +14917,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -14931,7 +14931,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>3487177.25</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -14940,7 +14940,7 @@
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>3487177.25</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
@@ -14949,25 +14949,25 @@
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="U104" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="X104" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="Y104" t="n">
         <v>0</v>
@@ -14976,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="AB104" t="n">
         <v>5</v>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
@@ -15009,12 +15009,12 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4326.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4326.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -15057,7 +15057,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -15071,7 +15071,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>254250.5</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -15080,34 +15080,34 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>204550.5</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>7795800.02</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>821264.08</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>821264.08</v>
+        <v>0</v>
       </c>
       <c r="U105" t="n">
-        <v>7745800.02</v>
+        <v>0</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="X105" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="Y105" t="n">
         <v>0</v>
@@ -15116,7 +15116,7 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="AB105" t="n">
         <v>5</v>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH105" t="inlineStr">
@@ -15149,12 +15149,12 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4326.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4326.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -15187,17 +15187,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3046970.4</v>
+        <v>254250.5</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -15220,34 +15220,34 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>3046970.4</v>
+        <v>204550.5</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>5238691</v>
+        <v>7795800.02</v>
       </c>
       <c r="S106" t="n">
-        <v>5238691</v>
+        <v>821264.08</v>
       </c>
       <c r="T106" t="n">
-        <v>8823589.4</v>
+        <v>821264.08</v>
       </c>
       <c r="U106" t="n">
-        <v>5238691</v>
+        <v>7745800.02</v>
       </c>
       <c r="V106" t="n">
-        <v>3584898.4</v>
+        <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="X106" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="Y106" t="n">
         <v>0</v>
@@ -15256,7 +15256,7 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="AB106" t="n">
         <v>5</v>
@@ -15264,12 +15264,12 @@
       <c r="AC106" t="inlineStr"/>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>Ouvidoria</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>ODH - Manutenção</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4332.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4326.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -15337,7 +15337,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -15351,7 +15351,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>13052.54</v>
+        <v>3046970.4</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
@@ -15360,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>13052.54</v>
+        <v>3046970.4</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -15369,25 +15369,25 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>346118.97</v>
+        <v>5238691</v>
       </c>
       <c r="S107" t="n">
-        <v>46118.97</v>
+        <v>5238691</v>
       </c>
       <c r="T107" t="n">
-        <v>46118.97</v>
+        <v>8823589.4</v>
       </c>
       <c r="U107" t="n">
-        <v>346118.97</v>
+        <v>5238691</v>
       </c>
       <c r="V107" t="n">
-        <v>0</v>
+        <v>3584898.4</v>
       </c>
       <c r="W107" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="X107" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="Y107" t="n">
         <v>0</v>
@@ -15396,7 +15396,7 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="AB107" t="n">
         <v>5</v>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4332.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4332.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -15467,17 +15467,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -15491,7 +15491,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>57410.34</v>
+        <v>13052.54</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
@@ -15500,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>57410.34</v>
+        <v>13052.54</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
@@ -15509,25 +15509,25 @@
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>321493</v>
+        <v>346118.97</v>
       </c>
       <c r="S108" t="n">
-        <v>202849.86</v>
+        <v>46118.97</v>
       </c>
       <c r="T108" t="n">
-        <v>202849.86</v>
+        <v>46118.97</v>
       </c>
       <c r="U108" t="n">
-        <v>321493</v>
+        <v>346118.97</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="X108" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="AB108" t="n">
         <v>5</v>
@@ -15544,12 +15544,12 @@
       <c r="AC108" t="inlineStr"/>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Centro Público</t>
+          <t>Ouvidoria</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH - Manutenção</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH108" t="inlineStr">
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4333.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4332.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -15631,43 +15631,43 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>55993.68</v>
+        <v>57410.34</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>55924.58</v>
+        <v>57410.34</v>
       </c>
       <c r="P109" t="n">
-        <v>223266.91</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>460224.15</v>
+        <v>321493</v>
       </c>
       <c r="S109" t="n">
-        <v>232254</v>
+        <v>202849.86</v>
       </c>
       <c r="T109" t="n">
-        <v>232254</v>
+        <v>202849.86</v>
       </c>
       <c r="U109" t="n">
-        <v>236957.24</v>
+        <v>321493</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>427085</v>
+        <v>321493</v>
       </c>
       <c r="X109" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="Y109" t="n">
         <v>0</v>
@@ -15676,7 +15676,7 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>427085</v>
+        <v>321493</v>
       </c>
       <c r="AB109" t="n">
         <v>5</v>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4333.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4333.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -15767,47 +15767,47 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>6998.62</v>
+        <v>55993.68</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="O110" t="n">
-        <v>6804.15</v>
+        <v>55924.58</v>
       </c>
       <c r="P110" t="n">
-        <v>2250</v>
+        <v>223266.91</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>47920</v>
+        <v>460224.15</v>
       </c>
       <c r="S110" t="n">
-        <v>45670</v>
+        <v>232254</v>
       </c>
       <c r="T110" t="n">
-        <v>47470</v>
+        <v>232254</v>
       </c>
       <c r="U110" t="n">
-        <v>45670</v>
+        <v>236957.24</v>
       </c>
       <c r="V110" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>45670</v>
+        <v>427085</v>
       </c>
       <c r="X110" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
@@ -15816,7 +15816,7 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>45670</v>
+        <v>427085</v>
       </c>
       <c r="AB110" t="n">
         <v>5</v>
@@ -15844,17 +15844,17 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4333.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4024.4333.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -15887,17 +15887,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>CPEF</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -15907,11 +15907,11 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>6998.62</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -15920,34 +15920,34 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>6804.15</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>47920</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>45670</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>47470</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>45670</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="W111" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="X111" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
@@ -15956,7 +15956,7 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="AB111" t="n">
         <v>5</v>
@@ -15964,12 +15964,12 @@
       <c r="AC111" t="inlineStr"/>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>Egressos e Familiares</t>
+          <t>Centro Público</t>
         </is>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>CPEF - Políticas</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -15979,22 +15979,22 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4335.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4333.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -16023,16 +16023,16 @@
         <v>422</v>
       </c>
       <c r="F112" t="n">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPEF</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -16051,52 +16051,52 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2414424.98</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2294560.33</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>2414424.98</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>393733.59</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>261863</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>7837448.92</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>5281025.59</v>
+        <v>0</v>
       </c>
       <c r="U112" t="n">
-        <v>7443715.33</v>
+        <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>393733.59</v>
+        <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>7443715.33</v>
+        <v>50000</v>
       </c>
       <c r="X112" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="Y112" t="n">
-        <v>261863</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>7443715.33</v>
+        <v>50000</v>
       </c>
       <c r="AB112" t="n">
         <v>5</v>
@@ -16104,12 +16104,12 @@
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Mulheres</t>
+          <t>Egressos e Familiares</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>CPM - Casa da Mulher Brasileira</t>
+          <t>CPEF - Políticas</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4335.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -16182,61 +16182,61 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2414424.98</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2294560.33</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>2414424.98</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>393733.59</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>261863</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>7837448.92</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>5281025.59</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>7443715.33</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>393733.59</v>
       </c>
       <c r="W113" t="n">
-        <v>0</v>
+        <v>7443715.33</v>
       </c>
       <c r="X113" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="Y113" t="n">
-        <v>2000</v>
+        <v>261863</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>2000</v>
+        <v>7443715.33</v>
       </c>
       <c r="AB113" t="n">
         <v>5</v>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>02 - Transferências Federais</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG113" t="inlineStr">
@@ -16264,17 +16264,17 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33503900.02.1.700.0000</t>
+          <t>34.10.14.422.4025.2053.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -16317,21 +16317,21 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>21384.72</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
@@ -16340,7 +16340,7 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>21056.72</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
@@ -16349,34 +16349,34 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>143942.4</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>33311.56</v>
+        <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>33311.56</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>143942.4</v>
+        <v>0</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>150755</v>
+        <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="Y114" t="n">
-        <v>8077</v>
+        <v>2000</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="AB114" t="n">
         <v>5</v>
@@ -16394,27 +16394,27 @@
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>02 - Transferências Federais</t>
         </is>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33503900.02.1.700.0000</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -16471,16 +16471,16 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>161974.24</v>
+        <v>21384.72</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>564000</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>161974.24</v>
+        <v>21056.72</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
@@ -16489,34 +16489,34 @@
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>519437</v>
+        <v>143942.4</v>
       </c>
       <c r="S115" t="n">
-        <v>485922.72</v>
+        <v>33311.56</v>
       </c>
       <c r="T115" t="n">
-        <v>485922.72</v>
+        <v>33311.56</v>
       </c>
       <c r="U115" t="n">
-        <v>519437</v>
+        <v>143942.4</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>1083437</v>
+        <v>150755</v>
       </c>
       <c r="X115" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="Y115" t="n">
-        <v>27832</v>
+        <v>8077</v>
       </c>
       <c r="Z115" t="n">
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1111269</v>
+        <v>158832</v>
       </c>
       <c r="AB115" t="n">
         <v>5</v>
@@ -16539,7 +16539,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH115" t="inlineStr">
@@ -16549,12 +16549,12 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -16611,52 +16611,52 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>666215.36</v>
+        <v>161974.24</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>564000</v>
       </c>
       <c r="O116" t="n">
-        <v>642287.52</v>
+        <v>161974.24</v>
       </c>
       <c r="P116" t="n">
-        <v>2102872.47</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>5725169.27</v>
+        <v>519437</v>
       </c>
       <c r="S116" t="n">
-        <v>2708402.82</v>
+        <v>485922.72</v>
       </c>
       <c r="T116" t="n">
-        <v>2708722.82</v>
+        <v>485922.72</v>
       </c>
       <c r="U116" t="n">
-        <v>3622296.8</v>
+        <v>519437</v>
       </c>
       <c r="V116" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>4087261</v>
+        <v>1083437</v>
       </c>
       <c r="X116" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="Y116" t="n">
-        <v>301895</v>
+        <v>27832</v>
       </c>
       <c r="Z116" t="n">
-        <v>564000</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>4389156</v>
+        <v>1111269</v>
       </c>
       <c r="AB116" t="n">
         <v>5</v>
@@ -16679,7 +16679,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH116" t="inlineStr">
@@ -16689,12 +16689,12 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -16747,11 +16747,11 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>22963.84</v>
+        <v>666215.36</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -16760,43 +16760,43 @@
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>22702.49</v>
+        <v>642287.52</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2102872.47</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>282533</v>
+        <v>5725169.27</v>
       </c>
       <c r="S117" t="n">
-        <v>282533</v>
+        <v>2708402.82</v>
       </c>
       <c r="T117" t="n">
-        <v>282533</v>
+        <v>2708722.82</v>
       </c>
       <c r="U117" t="n">
-        <v>282533</v>
+        <v>3622296.8</v>
       </c>
       <c r="V117" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="W117" t="n">
-        <v>282533</v>
+        <v>4087261</v>
       </c>
       <c r="X117" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>301895</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>564000</v>
       </c>
       <c r="AA117" t="n">
-        <v>282533</v>
+        <v>4389156</v>
       </c>
       <c r="AB117" t="n">
         <v>5</v>
@@ -16824,17 +16824,17 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4025.2053.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -16882,16 +16882,16 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>22963.84</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>22702.49</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -16909,25 +16909,25 @@
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="X118" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="Y118" t="n">
         <v>0</v>
@@ -16936,7 +16936,7 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="AB118" t="n">
         <v>5</v>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="AF118" t="inlineStr">
         <is>
-          <t>02 - Transferências Federais</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG118" t="inlineStr">
@@ -16964,17 +16964,17 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903900.02.1.700.0000</t>
+          <t>34.10.14.422.4025.2053.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -17017,7 +17017,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>33909300</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>Indenizações e Restituições</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33909300.02.1.700.0000</t>
+          <t>34.10.14.422.4025.2053.33903900.02.1.700.0000</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -17157,17 +17157,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33909300</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -17207,16 +17207,16 @@
         <v>0</v>
       </c>
       <c r="X120" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
         <v>5</v>
@@ -17234,27 +17234,27 @@
       </c>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>02 - Transferências Federais</t>
         </is>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Indenizações e Restituições</t>
         </is>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.44905200.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33909300.02.1.700.0000</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -17297,7 +17297,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -17347,16 +17347,16 @@
         <v>0</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z121" t="n">
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB121" t="n">
         <v>5</v>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>CPM - Políticas</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -17379,22 +17379,22 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Kenji Ito</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
+          <t>34.10.14.422.4025.2053.44905200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -17437,7 +17437,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -17447,11 +17447,11 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3132800</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -17460,43 +17460,43 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>3132800</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>3169600</v>
+        <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>3949200</v>
+        <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="X122" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1421600</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>8705439.67</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
         <v>5</v>
@@ -17519,22 +17519,22 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Kenji Ito</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -17577,7 +17577,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -17591,7 +17591,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>16923298.94</v>
+        <v>3132800</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
@@ -17600,43 +17600,43 @@
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>16923298.94</v>
+        <v>3132800</v>
       </c>
       <c r="P123" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="R123" t="n">
-        <v>23851875.51</v>
+        <v>8578400</v>
       </c>
       <c r="S123" t="n">
-        <v>21926109.23</v>
+        <v>3169600</v>
       </c>
       <c r="T123" t="n">
-        <v>22593123.43</v>
+        <v>3949200</v>
       </c>
       <c r="U123" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="V123" t="n">
-        <v>667014.2</v>
+        <v>779600</v>
       </c>
       <c r="W123" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="X123" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="AA123" t="n">
-        <v>22426358</v>
+        <v>8705439.67</v>
       </c>
       <c r="AB123" t="n">
         <v>5</v>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AH123" t="inlineStr">
@@ -17669,12 +17669,12 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -17731,7 +17731,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>64653</v>
+        <v>17238520.48</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -17740,34 +17740,34 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>62133</v>
+        <v>16923298.94</v>
       </c>
       <c r="P124" t="n">
-        <v>2075</v>
+        <v>1425517.51</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>190072.94</v>
+        <v>23851875.51</v>
       </c>
       <c r="S124" t="n">
-        <v>141746.12</v>
+        <v>21926109.23</v>
       </c>
       <c r="T124" t="n">
-        <v>143540.12</v>
+        <v>22593123.43</v>
       </c>
       <c r="U124" t="n">
-        <v>187997.94</v>
+        <v>22426358</v>
       </c>
       <c r="V124" t="n">
-        <v>1794</v>
+        <v>667014.2</v>
       </c>
       <c r="W124" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="X124" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="AB124" t="n">
         <v>5</v>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
@@ -17809,12 +17809,12 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -17857,7 +17857,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -17871,7 +17871,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>33338.4</v>
+        <v>64653</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -17880,34 +17880,34 @@
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>33338.4</v>
+        <v>64653</v>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2075</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>95531.96000000001</v>
+        <v>190072.94</v>
       </c>
       <c r="S125" t="n">
-        <v>95531.96000000001</v>
+        <v>141746.12</v>
       </c>
       <c r="T125" t="n">
-        <v>95531.96000000001</v>
+        <v>143540.12</v>
       </c>
       <c r="U125" t="n">
-        <v>95531.96000000001</v>
+        <v>187997.94</v>
       </c>
       <c r="V125" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="W125" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="X125" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
@@ -17916,7 +17916,7 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="AB125" t="n">
         <v>5</v>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
@@ -17949,12 +17949,12 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>246715.46</v>
+        <v>33338.4</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -18020,7 +18020,7 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>246715.46</v>
+        <v>33338.4</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
@@ -18029,25 +18029,25 @@
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2537927</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="S126" t="n">
-        <v>1074549.58</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="T126" t="n">
-        <v>1131764.02</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="U126" t="n">
-        <v>2537927</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="V126" t="n">
-        <v>57214.44</v>
+        <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="X126" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="Y126" t="n">
         <v>0</v>
@@ -18056,7 +18056,7 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="AB126" t="n">
         <v>5</v>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -18137,7 +18137,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>903570.96</v>
+        <v>246715.46</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -18160,34 +18160,34 @@
         <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>876799.9</v>
+        <v>246715.46</v>
       </c>
       <c r="P127" t="n">
-        <v>743505.8100000001</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3802648.2</v>
+        <v>2537927</v>
       </c>
       <c r="S127" t="n">
-        <v>1959769.84</v>
+        <v>1074549.58</v>
       </c>
       <c r="T127" t="n">
-        <v>1959769.84</v>
+        <v>1131764.02</v>
       </c>
       <c r="U127" t="n">
-        <v>3059142.39</v>
+        <v>2537927</v>
       </c>
       <c r="V127" t="n">
-        <v>0</v>
+        <v>57214.44</v>
       </c>
       <c r="W127" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="X127" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="Y127" t="n">
         <v>0</v>
@@ -18196,7 +18196,7 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="AB127" t="n">
         <v>5</v>
@@ -18219,7 +18219,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
@@ -18229,12 +18229,12 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -18287,11 +18287,11 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>368.19</v>
+        <v>903570.96</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
@@ -18300,34 +18300,34 @@
         <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>156.13</v>
+        <v>876799.9</v>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>743505.8100000001</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>80100</v>
+        <v>3802648.2</v>
       </c>
       <c r="S128" t="n">
-        <v>80100</v>
+        <v>1959769.84</v>
       </c>
       <c r="T128" t="n">
-        <v>80100</v>
+        <v>1959769.84</v>
       </c>
       <c r="U128" t="n">
-        <v>80100</v>
+        <v>3059142.39</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="X128" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
@@ -18336,7 +18336,7 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="AB128" t="n">
         <v>5</v>
@@ -18364,17 +18364,17 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -18417,7 +18417,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -18427,11 +18427,11 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>5903.55</v>
+        <v>368.19</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
@@ -18440,7 +18440,7 @@
         <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>5903.55</v>
+        <v>156.13</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -18449,25 +18449,25 @@
         <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="S129" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="T129" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="U129" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="X129" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="Y129" t="n">
         <v>0</v>
@@ -18476,7 +18476,7 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="AB129" t="n">
         <v>5</v>
@@ -18499,22 +18499,22 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -18547,17 +18547,17 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -18571,7 +18571,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>5903.55</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
@@ -18580,43 +18580,43 @@
         <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>5903.55</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S130" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U130" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="V130" t="n">
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="X130" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="Y130" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="AB130" t="n">
         <v>5</v>
@@ -18624,12 +18624,12 @@
       <c r="AC130" t="inlineStr"/>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AH130" t="inlineStr">
@@ -18649,12 +18649,12 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -18726,7 +18726,7 @@
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>200000</v>
+        <v>220000</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
@@ -18744,19 +18744,19 @@
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="X131" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Y131" t="n">
-        <v>200000</v>
+        <v>330000</v>
       </c>
       <c r="Z131" t="n">
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="AB131" t="n">
         <v>5</v>
@@ -18769,7 +18769,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
+          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -18789,12 +18789,12 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -18866,7 +18866,7 @@
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>75000</v>
+        <v>200000</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -18887,16 +18887,16 @@
         <v>0</v>
       </c>
       <c r="X132" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y132" t="n">
-        <v>75000</v>
+        <v>300000</v>
       </c>
       <c r="Z132" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AB132" t="n">
         <v>5</v>
@@ -18909,7 +18909,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
+          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -18963,21 +18963,21 @@
         <v>422</v>
       </c>
       <c r="F133" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -19006,7 +19006,7 @@
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -19024,19 +19024,19 @@
         <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="X133" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA133" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
         <v>5</v>
@@ -19044,12 +19044,12 @@
       <c r="AC133" t="inlineStr"/>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -19059,7 +19059,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH133" t="inlineStr">
@@ -19069,12 +19069,12 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -19107,7 +19107,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -19131,7 +19131,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
@@ -19140,43 +19140,43 @@
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>127000</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="U134" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
       </c>
       <c r="W134" t="n">
-        <v>3596273</v>
+        <v>11949</v>
       </c>
       <c r="X134" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="Y134" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="AB134" t="n">
         <v>5</v>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH134" t="inlineStr">
@@ -19209,12 +19209,12 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -19271,7 +19271,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -19280,43 +19280,43 @@
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="S135" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="U135" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>5374</v>
+        <v>3596273</v>
       </c>
       <c r="X135" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="Y135" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="Z135" t="n">
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="AB135" t="n">
         <v>5</v>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH135" t="inlineStr">
@@ -19349,12 +19349,12 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -19444,19 +19444,19 @@
         <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>80612</v>
+        <v>5374</v>
       </c>
       <c r="X136" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="Y136" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="Z136" t="n">
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="AB136" t="n">
         <v>5</v>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AH136" t="inlineStr">
@@ -19489,12 +19489,12 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -19551,7 +19551,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>110455.56</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -19560,43 +19560,43 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>73756.84</v>
+        <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>551.08</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>5040463.02</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>570925.76</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>570925.76</v>
+        <v>0</v>
       </c>
       <c r="U137" t="n">
-        <v>5039911.94</v>
+        <v>0</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>5870981</v>
+        <v>80612</v>
       </c>
       <c r="X137" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="Y137" t="n">
-        <v>5054381</v>
+        <v>69388</v>
       </c>
       <c r="Z137" t="n">
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="AB137" t="n">
         <v>5</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH137" t="inlineStr">
@@ -19629,12 +19629,12 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -19687,11 +19687,11 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>110455.56</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -19700,43 +19700,43 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>73756.84</v>
       </c>
       <c r="P138" t="n">
-        <v>925</v>
+        <v>551.08</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>1900</v>
+        <v>5040463.02</v>
       </c>
       <c r="S138" t="n">
-        <v>300</v>
+        <v>570925.76</v>
       </c>
       <c r="T138" t="n">
-        <v>300</v>
+        <v>570925.76</v>
       </c>
       <c r="U138" t="n">
-        <v>975</v>
+        <v>5039911.94</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
       </c>
       <c r="W138" t="n">
-        <v>1000</v>
+        <v>5870981</v>
       </c>
       <c r="X138" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="Y138" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="Z138" t="n">
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="AB138" t="n">
         <v>5</v>
@@ -19764,17 +19764,17 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -19807,17 +19807,17 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L139" t="n">
@@ -19843,40 +19843,40 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="Q139" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="S139" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U139" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X139" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="Y139" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB139" t="n">
         <v>5</v>
@@ -19884,12 +19884,12 @@
       <c r="AC139" t="inlineStr"/>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -19899,22 +19899,22 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -19940,24 +19940,24 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F140" t="n">
         <v>4026</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -19983,40 +19983,40 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>11400</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>15000</v>
+        <v>75000</v>
       </c>
       <c r="R140" t="n">
-        <v>21600</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="U140" t="n">
-        <v>10200</v>
+        <v>0</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
       </c>
       <c r="W140" t="n">
-        <v>22143</v>
+        <v>0</v>
       </c>
       <c r="X140" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="Y140" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="Z140" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA140" t="n">
-        <v>46881</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
         <v>5</v>
@@ -20024,12 +20024,12 @@
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH140" t="inlineStr">
@@ -20049,12 +20049,12 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -20123,40 +20123,40 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R141" t="n">
-        <v>33669</v>
+        <v>21600</v>
       </c>
       <c r="S141" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="U141" t="n">
-        <v>33669</v>
+        <v>10200</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>33669</v>
+        <v>22143</v>
       </c>
       <c r="X141" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="Y141" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="Z141" t="n">
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="AB141" t="n">
         <v>5</v>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH141" t="inlineStr">
@@ -20189,12 +20189,12 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -20227,17 +20227,17 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -20266,10 +20266,10 @@
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>127873.65</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -20278,25 +20278,25 @@
         <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>27873.65</v>
+        <v>33669</v>
       </c>
       <c r="X142" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="Y142" t="n">
-        <v>127873.65</v>
+        <v>187297</v>
       </c>
       <c r="Z142" t="n">
-        <v>72126.35000000001</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>27873.65</v>
+        <v>220966</v>
       </c>
       <c r="AB142" t="n">
         <v>5</v>
@@ -20304,12 +20304,12 @@
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -20319,7 +20319,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
@@ -20329,12 +20329,12 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -20346,12 +20346,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20360,19 +20360,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F143" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -20387,7 +20387,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -20397,7 +20397,7 @@
         <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -20406,37 +20406,37 @@
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>127873.65</v>
       </c>
       <c r="R143" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>155747.3</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>72126.35000000001</v>
       </c>
       <c r="AA143" t="n">
-        <v>150000</v>
+        <v>27873.65</v>
       </c>
       <c r="AB143" t="n">
         <v>5</v>
@@ -20444,12 +20444,12 @@
       <c r="AC143" t="inlineStr"/>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -20464,17 +20464,17 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
+          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -20517,7 +20517,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -20527,7 +20527,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -20537,7 +20537,7 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -20549,34 +20549,34 @@
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S144" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U144" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
       </c>
       <c r="W144" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="X144" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>589773</v>
+        <v>150000</v>
       </c>
       <c r="AB144" t="n">
         <v>5</v>
@@ -20599,65 +20599,65 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
         </is>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F145" t="n">
         <v>4010</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -20671,7 +20671,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>12940208.36</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -20680,7 +20680,7 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>12940208.36</v>
+        <v>0</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -20689,34 +20689,34 @@
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="X145" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="Y145" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Z145" t="n">
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="AB145" t="n">
         <v>5</v>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
@@ -20749,12 +20749,12 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -20811,7 +20811,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>12940208.36</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -20820,7 +20820,7 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>12940208.36</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -20829,34 +20829,34 @@
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="S146" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="T146" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="U146" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>600437</v>
+        <v>40835555</v>
       </c>
       <c r="X146" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="Y146" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Z146" t="n">
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="AB146" t="n">
         <v>5</v>
@@ -20879,7 +20879,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH146" t="inlineStr">
@@ -20889,12 +20889,12 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -20916,23 +20916,23 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F147" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -20984,19 +20984,19 @@
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="X147" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Z147" t="n">
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="AB147" t="n">
         <v>5</v>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -21029,12 +21029,12 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>44906100</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -21097,7 +21097,7 @@
         <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -21109,7 +21109,7 @@
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -21118,16 +21118,16 @@
         <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>361510</v>
+        <v>1000</v>
       </c>
       <c r="X148" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y148" t="n">
         <v>0</v>
@@ -21136,7 +21136,7 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>361510</v>
+        <v>1000</v>
       </c>
       <c r="AB148" t="n">
         <v>5</v>
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>Aquisição de Imóveis</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
@@ -21169,12 +21169,12 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -21200,14 +21200,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F149" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44906100</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -21231,52 +21231,52 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>59803761.71</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="O149" t="n">
-        <v>59682641.06</v>
+        <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>21043600.09</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>158978189.3</v>
+        <v>361510</v>
       </c>
       <c r="S149" t="n">
-        <v>135266690.42</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>140706402.81</v>
+        <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>137934589.21</v>
+        <v>361510</v>
       </c>
       <c r="V149" t="n">
-        <v>5439712.39</v>
+        <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>165715582</v>
+        <v>361510</v>
       </c>
       <c r="X149" t="n">
-        <v>171813039</v>
+        <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Z149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA149" t="n">
         <v>361510</v>
-      </c>
-      <c r="AA149" t="n">
-        <v>171451529</v>
       </c>
       <c r="AB149" t="n">
         <v>5</v>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Aquisição de Imóveis</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
@@ -21309,12 +21309,12 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -21357,21 +21357,21 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>59803761.71</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -21380,43 +21380,43 @@
         <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>0</v>
+        <v>59682641.06</v>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>21043600.09</v>
       </c>
       <c r="Q150" t="n">
         <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>158978189.3</v>
       </c>
       <c r="S150" t="n">
-        <v>0</v>
+        <v>135266690.42</v>
       </c>
       <c r="T150" t="n">
-        <v>0</v>
+        <v>140706402.81</v>
       </c>
       <c r="U150" t="n">
-        <v>0</v>
+        <v>137934589.21</v>
       </c>
       <c r="V150" t="n">
-        <v>0</v>
+        <v>5439712.39</v>
       </c>
       <c r="W150" t="n">
-        <v>2000</v>
+        <v>165715582</v>
       </c>
       <c r="X150" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="Y150" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Z150" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="AA150" t="n">
-        <v>2000</v>
+        <v>171451529</v>
       </c>
       <c r="AB150" t="n">
         <v>5</v>
@@ -21434,27 +21434,27 @@
       </c>
       <c r="AF150" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
+          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -21502,12 +21502,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -21544,10 +21544,10 @@
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X151" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="Y151" t="n">
         <v>0</v>
@@ -21556,7 +21556,7 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AB151" t="n">
         <v>5</v>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="AF151" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG151" t="inlineStr">
@@ -21584,17 +21584,17 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
+          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -21637,21 +21637,21 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>29431997.31</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21660,43 +21660,43 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>26588094.6</v>
+        <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>60670522</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>197559544</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>107626518.4</v>
+        <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>107626518.4</v>
+        <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>136889022</v>
+        <v>0</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
       </c>
       <c r="W152" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="X152" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="Y152" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Z152" t="n">
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AB152" t="n">
         <v>5</v>
@@ -21714,27 +21714,27 @@
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -21777,7 +21777,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -21791,7 +21791,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>23174007.34</v>
+        <v>29431997.31</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -21800,43 +21800,43 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>17774241.01</v>
+        <v>27984138.6</v>
       </c>
       <c r="P153" t="n">
-        <v>49898263.91</v>
+        <v>60670522</v>
       </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>129341289.91</v>
+        <v>197559544</v>
       </c>
       <c r="S153" t="n">
-        <v>78558584.37</v>
+        <v>107626518.4</v>
       </c>
       <c r="T153" t="n">
-        <v>79002584.37</v>
+        <v>107626518.4</v>
       </c>
       <c r="U153" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="V153" t="n">
-        <v>444000</v>
+        <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="X153" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="Y153" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Z153" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>82235403</v>
+        <v>141616875</v>
       </c>
       <c r="AB153" t="n">
         <v>5</v>
@@ -21859,7 +21859,7 @@
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AH153" t="inlineStr">
@@ -21869,12 +21869,12 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -21922,16 +21922,16 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>24074007.34</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -21940,43 +21940,43 @@
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>17924153.08</v>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>49898263.91</v>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>129341289.91</v>
       </c>
       <c r="S154" t="n">
-        <v>0</v>
+        <v>78558584.37</v>
       </c>
       <c r="T154" t="n">
-        <v>0</v>
+        <v>79002584.37</v>
       </c>
       <c r="U154" t="n">
-        <v>0</v>
+        <v>79443026</v>
       </c>
       <c r="V154" t="n">
-        <v>0</v>
+        <v>444000</v>
       </c>
       <c r="W154" t="n">
-        <v>2000</v>
+        <v>79443026</v>
       </c>
       <c r="X154" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="Y154" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Z154" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="AA154" t="n">
-        <v>2000</v>
+        <v>82235403</v>
       </c>
       <c r="AB154" t="n">
         <v>5</v>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="AF154" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG154" t="inlineStr">
@@ -22004,17 +22004,17 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
+          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -22057,30 +22057,30 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>33913900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>336000</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>336000</v>
+        <v>0</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -22089,25 +22089,25 @@
         <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="U155" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="X155" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y155" t="n">
         <v>0</v>
@@ -22116,7 +22116,7 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="AB155" t="n">
         <v>5</v>
@@ -22134,39 +22134,39 @@
       </c>
       <c r="AF155" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG155" t="inlineStr">
         <is>
-          <t>Transferência entre Órgãos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -22180,24 +22180,24 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F156" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -22211,16 +22211,16 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>336000</v>
       </c>
       <c r="M156" t="n">
         <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>336000</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -22229,25 +22229,25 @@
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="X156" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y156" t="n">
         <v>0</v>
@@ -22256,7 +22256,7 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="AB156" t="n">
         <v>5</v>
@@ -22264,12 +22264,12 @@
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -22279,7 +22279,7 @@
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AH156" t="inlineStr">
@@ -22289,12 +22289,12 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -22384,10 +22384,10 @@
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X157" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="Y157" t="n">
         <v>0</v>
@@ -22396,7 +22396,7 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AB157" t="n">
         <v>5</v>
@@ -22419,7 +22419,7 @@
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
@@ -22429,12 +22429,12 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -22460,24 +22460,24 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F158" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>DTIC</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -22524,10 +22524,10 @@
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X158" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="Y158" t="n">
         <v>0</v>
@@ -22536,7 +22536,7 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AB158" t="n">
         <v>5</v>
@@ -22544,12 +22544,12 @@
       <c r="AC158" t="inlineStr"/>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>DTIC - Desenvolvimento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="AG158" t="inlineStr">
         <is>
-          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH158" t="inlineStr">
@@ -22569,12 +22569,12 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -22600,24 +22600,24 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F159" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -22627,7 +22627,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -22664,10 +22664,10 @@
         <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X159" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y159" t="n">
         <v>0</v>
@@ -22676,7 +22676,7 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB159" t="n">
         <v>5</v>
@@ -22684,12 +22684,12 @@
       <c r="AC159" t="inlineStr"/>
       <c r="AD159" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC - Desenvolvimento</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -22699,22 +22699,22 @@
       </c>
       <c r="AG159" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
         </is>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>23/04/2026 07:34:36</t>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>
@@ -22762,16 +22762,16 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>24479179.14</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -22780,34 +22780,34 @@
         <v>0</v>
       </c>
       <c r="O160" t="n">
-        <v>24296479.14</v>
+        <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>3068431.98</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>39837366.69</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>32377746.42</v>
+        <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>33990510.52</v>
+        <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>36768934.71</v>
+        <v>0</v>
       </c>
       <c r="V160" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X160" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="Y160" t="n">
         <v>0</v>
@@ -22816,7 +22816,7 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AB160" t="n">
         <v>5</v>
@@ -22834,27 +22834,167 @@
       </c>
       <c r="AF160" t="inlineStr">
         <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>24/04/2026 07:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>422</v>
+      </c>
+      <c r="F161" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>24479179.14</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>24479179.14</v>
+      </c>
+      <c r="P161" t="n">
+        <v>3068431.98</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>39837366.69</v>
+      </c>
+      <c r="S161" t="n">
+        <v>32377746.42</v>
+      </c>
+      <c r="T161" t="n">
+        <v>33990510.52</v>
+      </c>
+      <c r="U161" t="n">
+        <v>36768934.71</v>
+      </c>
+      <c r="V161" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="W161" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X161" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
           <t>08 - Recusos Vinculados</t>
         </is>
       </c>
-      <c r="AG160" t="inlineStr">
+      <c r="AG161" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AH160" t="inlineStr">
+      <c r="AH161" t="inlineStr">
         <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AI160" t="inlineStr">
+      <c r="AI161" t="inlineStr">
         <is>
           <t>90.10.14.422.4019.6160.33503900.08.1.759.0958</t>
         </is>
       </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>23/04/2026 07:34:36</t>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>24/04/2026 07:32:16</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3081610.16</v>
+        <v>3838685.61</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1820051.18</v>
+        <v>1825007.65</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1455848.66</v>
+        <v>1492154.79</v>
       </c>
       <c r="P10" t="n">
         <v>1253945.22</v>
@@ -1792,10 +1792,10 @@
         <v>12796283.42</v>
       </c>
       <c r="S10" t="n">
-        <v>7776313.45</v>
+        <v>7777663.45</v>
       </c>
       <c r="T10" t="n">
-        <v>7882464</v>
+        <v>7883814</v>
       </c>
       <c r="U10" t="n">
         <v>11542338.2</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>21602.07</v>
+        <v>22056.08</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1414911.08</v>
+        <v>1418100.68</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4037641.2</v>
+        <v>5351497.79</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3889,16 +3889,16 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4037641.2</v>
+        <v>5351497.79</v>
       </c>
       <c r="S25" t="n">
-        <v>4037641.2</v>
+        <v>5351497.79</v>
       </c>
       <c r="T25" t="n">
-        <v>4037641.2</v>
+        <v>5351497.79</v>
       </c>
       <c r="U25" t="n">
-        <v>4037641.2</v>
+        <v>5351497.79</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>489255.05</v>
+        <v>491130.66</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3285707.39</v>
+        <v>3286386.22</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4732,10 +4732,10 @@
         <v>18625777.17</v>
       </c>
       <c r="S31" t="n">
-        <v>16941801.99</v>
+        <v>16983877.06</v>
       </c>
       <c r="T31" t="n">
-        <v>16948374.64</v>
+        <v>16990449.71</v>
       </c>
       <c r="U31" t="n">
         <v>17825742.81</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1120449.02</v>
+        <v>1471182.28</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -5149,16 +5149,16 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1120449.02</v>
+        <v>1471182.28</v>
       </c>
       <c r="S34" t="n">
-        <v>1120449.02</v>
+        <v>1471182.28</v>
       </c>
       <c r="T34" t="n">
-        <v>1120449.02</v>
+        <v>1471182.28</v>
       </c>
       <c r="U34" t="n">
-        <v>1120449.02</v>
+        <v>1471182.28</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
         <v>5916961.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2985047</v>
+        <v>2983887.66</v>
       </c>
       <c r="T35" t="n">
         <v>2985047</v>
@@ -5301,7 +5301,7 @@
         <v>2985047</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1159.34</v>
       </c>
       <c r="W35" t="n">
         <v>2985047</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3036.39</v>
+        <v>3115.08</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
         <v>93886</v>
       </c>
       <c r="O44" t="n">
-        <v>814775.9399999999</v>
+        <v>826900.28</v>
       </c>
       <c r="P44" t="n">
         <v>465163.56</v>
@@ -6552,16 +6552,16 @@
         <v>15333661.41</v>
       </c>
       <c r="S44" t="n">
-        <v>3273639.4</v>
+        <v>5295350.24</v>
       </c>
       <c r="T44" t="n">
-        <v>3273639.4</v>
+        <v>5717985.82</v>
       </c>
       <c r="U44" t="n">
         <v>14868497.85</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>422635.58</v>
       </c>
       <c r="W44" t="n">
         <v>15225568.73</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4743.43</v>
+        <v>6180.06</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -10892,10 +10892,10 @@
         <v>260366.25</v>
       </c>
       <c r="S75" t="n">
-        <v>133147</v>
+        <v>134497</v>
       </c>
       <c r="T75" t="n">
-        <v>133147</v>
+        <v>134497</v>
       </c>
       <c r="U75" t="n">
         <v>258144.66</v>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>953.49</v>
+        <v>1731.85</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -13972,10 +13972,10 @@
         <v>7383237.78</v>
       </c>
       <c r="S97" t="n">
-        <v>4551281.7</v>
+        <v>7383237.78</v>
       </c>
       <c r="T97" t="n">
-        <v>4551281.7</v>
+        <v>7383237.78</v>
       </c>
       <c r="U97" t="n">
         <v>7383237.78</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -15789,16 +15789,16 @@
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>460224.15</v>
+        <v>507656.93</v>
       </c>
       <c r="S110" t="n">
-        <v>232254</v>
+        <v>236304</v>
       </c>
       <c r="T110" t="n">
-        <v>232254</v>
+        <v>236304</v>
       </c>
       <c r="U110" t="n">
-        <v>236957.24</v>
+        <v>284390.02</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15911,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>6998.62</v>
+        <v>11293.18</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -16212,10 +16212,10 @@
         <v>7837448.92</v>
       </c>
       <c r="S113" t="n">
-        <v>4887292</v>
+        <v>7375465.34</v>
       </c>
       <c r="T113" t="n">
-        <v>5281025.59</v>
+        <v>7769198.93</v>
       </c>
       <c r="U113" t="n">
         <v>7443715.33</v>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>666215.36</v>
+        <v>780215.36</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -17731,7 +17731,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>17238520.48</v>
+        <v>19041664.7</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>33338.4</v>
+        <v>40338.4</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>903570.96</v>
+        <v>903690.76</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
@@ -18312,16 +18312,16 @@
         <v>3802648.2</v>
       </c>
       <c r="S128" t="n">
-        <v>1959769.84</v>
+        <v>2409038.89</v>
       </c>
       <c r="T128" t="n">
-        <v>1959769.84</v>
+        <v>2502957.88</v>
       </c>
       <c r="U128" t="n">
         <v>3059142.39</v>
       </c>
       <c r="V128" t="n">
-        <v>0</v>
+        <v>93918.99000000001</v>
       </c>
       <c r="W128" t="n">
         <v>4806049</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -19691,7 +19691,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>110455.56</v>
+        <v>110635.26</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>76.61</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -19852,10 +19852,10 @@
         <v>1900</v>
       </c>
       <c r="S139" t="n">
-        <v>300</v>
+        <v>975</v>
       </c>
       <c r="T139" t="n">
-        <v>300</v>
+        <v>975</v>
       </c>
       <c r="U139" t="n">
         <v>975</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -20832,10 +20832,10 @@
         <v>40835555</v>
       </c>
       <c r="S146" t="n">
-        <v>38820625.08</v>
+        <v>40835555</v>
       </c>
       <c r="T146" t="n">
-        <v>38820625.08</v>
+        <v>40835555</v>
       </c>
       <c r="U146" t="n">
         <v>40835555</v>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>59803761.71</v>
+        <v>59869982.53</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -21380,7 +21380,7 @@
         <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>59682641.06</v>
+        <v>59791184.99</v>
       </c>
       <c r="P150" t="n">
         <v>21043600.09</v>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>24074007.34</v>
+        <v>24164007.34</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -21952,10 +21952,10 @@
         <v>129341289.91</v>
       </c>
       <c r="S154" t="n">
-        <v>78558584.37</v>
+        <v>79232487.98999999</v>
       </c>
       <c r="T154" t="n">
-        <v>79002584.37</v>
+        <v>79676487.98999999</v>
       </c>
       <c r="U154" t="n">
         <v>79443026</v>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -22923,7 +22923,7 @@
         <v>24479179.14</v>
       </c>
       <c r="P161" t="n">
-        <v>3068431.98</v>
+        <v>3158618.88</v>
       </c>
       <c r="Q161" t="n">
         <v>0</v>
@@ -22932,13 +22932,13 @@
         <v>39837366.69</v>
       </c>
       <c r="S161" t="n">
-        <v>32377746.42</v>
+        <v>32622739.07</v>
       </c>
       <c r="T161" t="n">
-        <v>33990510.52</v>
+        <v>34235503.17</v>
       </c>
       <c r="U161" t="n">
-        <v>36768934.71</v>
+        <v>36678747.81</v>
       </c>
       <c r="V161" t="n">
         <v>1612764.1</v>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>24/04/2026 07:32:16</t>
+          <t>25/04/2026 07:06:57</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ161"/>
+  <dimension ref="A1:AJ163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -13184,17 +13184,17 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Ricardo Teixeira</t>
+          <t>Emendas Parlamentares - Bombeiro Major Palumbo</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4318.33503900.00.1.500.7061</t>
+          <t>34.10.14.422.4024.4318.33503900.00.1.500.7003</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -13247,11 +13247,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -13260,7 +13260,7 @@
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
@@ -13269,25 +13269,25 @@
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>10919153.01</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>10919153.01</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
@@ -13296,7 +13296,7 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
         <v>5</v>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Ricardo Teixeira</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4318.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33503900.00.1.500.7061</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -13409,25 +13409,25 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
@@ -13436,7 +13436,7 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
         <v>5</v>
@@ -13459,22 +13459,22 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t xml:space="preserve">7066 - Emendas Parlamentares - Gilberto Nascimento </t>
         </is>
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4318.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33503900.00.1.500.7066</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -13540,7 +13540,7 @@
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
@@ -13549,25 +13549,25 @@
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>10919153.01</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>10919153.01</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>378632</v>
+        <v>12675633</v>
       </c>
       <c r="X94" t="n">
-        <v>378632</v>
+        <v>12675633</v>
       </c>
       <c r="Y94" t="n">
         <v>0</v>
@@ -13576,7 +13576,7 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>378632</v>
+        <v>12675633</v>
       </c>
       <c r="AB94" t="n">
         <v>5</v>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH94" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4318.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -13647,17 +13647,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>33804100</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -13689,34 +13689,34 @@
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>8373</v>
+        <v>50000</v>
       </c>
       <c r="X95" t="n">
-        <v>10598</v>
+        <v>50000</v>
       </c>
       <c r="Y95" t="n">
-        <v>2225</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>10598</v>
+        <v>50000</v>
       </c>
       <c r="AB95" t="n">
         <v>5</v>
@@ -13724,12 +13724,12 @@
       <c r="AC95" t="inlineStr"/>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>CPLGBTI - Políticas</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>Taxa Rainbow</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
@@ -13749,12 +13749,12 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4319.33804100.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -13787,12 +13787,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -13802,12 +13802,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -13844,10 +13844,10 @@
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>4000</v>
+        <v>378632</v>
       </c>
       <c r="X96" t="n">
-        <v>4000</v>
+        <v>378632</v>
       </c>
       <c r="Y96" t="n">
         <v>0</v>
@@ -13856,7 +13856,7 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>4000</v>
+        <v>378632</v>
       </c>
       <c r="AB96" t="n">
         <v>5</v>
@@ -13864,17 +13864,17 @@
       <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>CPLGBTI - Políticas</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG96" t="inlineStr">
@@ -13884,17 +13884,17 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4319.33903900.05.1.703.0000</t>
+          <t>34.10.14.422.4024.4318.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33804100</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -13951,7 +13951,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3410465.43</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -13960,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>2363104.83</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -13969,34 +13969,34 @@
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>7383237.78</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>7383237.78</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>7383237.78</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>7383237.78</v>
+        <v>0</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>9813947</v>
+        <v>8373</v>
       </c>
       <c r="X97" t="n">
-        <v>12421782</v>
+        <v>10598</v>
       </c>
       <c r="Y97" t="n">
-        <v>2607835</v>
+        <v>2225</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>12421782</v>
+        <v>10598</v>
       </c>
       <c r="AB97" t="n">
         <v>5</v>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Taxa Rainbow</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4319.33904800.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4319.33804100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -14067,12 +14067,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -14082,12 +14082,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -14124,19 +14124,19 @@
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="X98" t="n">
-        <v>56000</v>
+        <v>4000</v>
       </c>
       <c r="Y98" t="n">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>56000</v>
+        <v>4000</v>
       </c>
       <c r="AB98" t="n">
         <v>5</v>
@@ -14144,17 +14144,17 @@
       <c r="AC98" t="inlineStr"/>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>CPIPTD - Políticas</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG98" t="inlineStr">
@@ -14164,17 +14164,17 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4319.33903900.05.1.703.0000</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -14207,17 +14207,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -14227,11 +14227,11 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3410465.43</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -14240,7 +14240,7 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>2363104.83</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -14249,34 +14249,34 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>7383237.78</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>7383237.78</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>7383237.78</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>7383237.78</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>9813947</v>
       </c>
       <c r="X99" t="n">
-        <v>40000</v>
+        <v>12421782</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>2607835</v>
       </c>
       <c r="Z99" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>12421782</v>
       </c>
       <c r="AB99" t="n">
         <v>5</v>
@@ -14284,12 +14284,12 @@
       <c r="AC99" t="inlineStr"/>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>CPIPTD - Políticas</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -14299,22 +14299,22 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9005</t>
+          <t>34.10.14.422.4024.4319.33904800.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -14367,7 +14367,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -14377,7 +14377,7 @@
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14404,19 +14404,19 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>15000</v>
+        <v>56000</v>
       </c>
       <c r="AB100" t="n">
         <v>5</v>
@@ -14444,17 +14444,17 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9567</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -14517,7 +14517,7 @@
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14544,19 +14544,19 @@
         <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="Y101" t="n">
         <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AA101" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
         <v>5</v>
@@ -14584,17 +14584,17 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
+          <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9570</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9005</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -14647,7 +14647,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="L102" t="n">
@@ -14657,7 +14657,7 @@
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14684,7 +14684,7 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="X102" t="n">
         <v>0</v>
@@ -14696,7 +14696,7 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AB102" t="n">
         <v>5</v>
@@ -14724,17 +14724,17 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9571</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9567</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -14767,12 +14767,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="L103" t="n">
@@ -14797,7 +14797,7 @@
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14824,10 +14824,10 @@
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="X103" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="AB103" t="n">
         <v>5</v>
@@ -14844,12 +14844,12 @@
       <c r="AC103" t="inlineStr"/>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>Drogas</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>CPD - Políticas</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -14864,17 +14864,17 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4325.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9570</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -14907,17 +14907,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -14927,20 +14927,20 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3487177.25</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="O104" t="n">
-        <v>3487177.25</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
@@ -14949,25 +14949,25 @@
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="U104" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>10052704</v>
+        <v>10000</v>
       </c>
       <c r="X104" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="n">
         <v>0</v>
@@ -14976,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>10052704</v>
+        <v>10000</v>
       </c>
       <c r="AB104" t="n">
         <v>5</v>
@@ -14984,12 +14984,12 @@
       <c r="AC104" t="inlineStr"/>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>CPLGBTI - Equipamentos</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -14999,22 +14999,22 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4326.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9571</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -15047,17 +15047,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -15104,10 +15104,10 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>100000</v>
+        <v>1000</v>
       </c>
       <c r="X105" t="n">
-        <v>100000</v>
+        <v>1000</v>
       </c>
       <c r="Y105" t="n">
         <v>0</v>
@@ -15116,7 +15116,7 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>100000</v>
+        <v>1000</v>
       </c>
       <c r="AB105" t="n">
         <v>5</v>
@@ -15124,12 +15124,12 @@
       <c r="AC105" t="inlineStr"/>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Drogas</t>
         </is>
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>CPLGBTI - Equipamentos</t>
+          <t>CPD - Políticas</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -15139,7 +15139,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH105" t="inlineStr">
@@ -15149,12 +15149,12 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4326.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4325.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -15197,7 +15197,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>254250.5</v>
+        <v>3487177.25</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -15220,34 +15220,34 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>204550.5</v>
+        <v>3487177.25</v>
       </c>
       <c r="P106" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>7795800.02</v>
+        <v>10052704</v>
       </c>
       <c r="S106" t="n">
-        <v>821264.08</v>
+        <v>10052704</v>
       </c>
       <c r="T106" t="n">
-        <v>821264.08</v>
+        <v>10052704</v>
       </c>
       <c r="U106" t="n">
-        <v>7745800.02</v>
+        <v>10052704</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>8429440</v>
+        <v>10052704</v>
       </c>
       <c r="X106" t="n">
-        <v>8429440</v>
+        <v>10052704</v>
       </c>
       <c r="Y106" t="n">
         <v>0</v>
@@ -15256,7 +15256,7 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>8429440</v>
+        <v>10052704</v>
       </c>
       <c r="AB106" t="n">
         <v>5</v>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4326.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4326.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -15327,17 +15327,17 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -15351,7 +15351,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3046970.4</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
@@ -15360,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>3046970.4</v>
+        <v>0</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -15369,25 +15369,25 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>5238691</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>5238691</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>8823589.4</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
-        <v>5238691</v>
+        <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>3584898.4</v>
+        <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>5238691</v>
+        <v>100000</v>
       </c>
       <c r="X107" t="n">
-        <v>5238691</v>
+        <v>100000</v>
       </c>
       <c r="Y107" t="n">
         <v>0</v>
@@ -15396,7 +15396,7 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>5238691</v>
+        <v>100000</v>
       </c>
       <c r="AB107" t="n">
         <v>5</v>
@@ -15404,12 +15404,12 @@
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>Ouvidoria</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>ODH - Manutenção</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -15419,7 +15419,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4332.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4326.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -15467,12 +15467,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -15491,7 +15491,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>13052.54</v>
+        <v>254250.5</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
@@ -15500,34 +15500,34 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>13052.54</v>
+        <v>204550.5</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>346118.97</v>
+        <v>7795800.02</v>
       </c>
       <c r="S108" t="n">
-        <v>46118.97</v>
+        <v>821264.08</v>
       </c>
       <c r="T108" t="n">
-        <v>46118.97</v>
+        <v>821264.08</v>
       </c>
       <c r="U108" t="n">
-        <v>346118.97</v>
+        <v>7745800.02</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>867556</v>
+        <v>8429440</v>
       </c>
       <c r="X108" t="n">
-        <v>867556</v>
+        <v>8429440</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>867556</v>
+        <v>8429440</v>
       </c>
       <c r="AB108" t="n">
         <v>5</v>
@@ -15544,12 +15544,12 @@
       <c r="AC108" t="inlineStr"/>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Ouvidoria</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>ODH - Manutenção</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4332.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4326.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -15607,17 +15607,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>57410.34</v>
+        <v>3046970.4</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -15640,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>57410.34</v>
+        <v>3046970.4</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
@@ -15649,25 +15649,25 @@
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>321493</v>
+        <v>5238691</v>
       </c>
       <c r="S109" t="n">
-        <v>202849.86</v>
+        <v>5238691</v>
       </c>
       <c r="T109" t="n">
-        <v>202849.86</v>
+        <v>8823589.4</v>
       </c>
       <c r="U109" t="n">
-        <v>321493</v>
+        <v>5238691</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>3584898.4</v>
       </c>
       <c r="W109" t="n">
-        <v>321493</v>
+        <v>5238691</v>
       </c>
       <c r="X109" t="n">
-        <v>321493</v>
+        <v>5238691</v>
       </c>
       <c r="Y109" t="n">
         <v>0</v>
@@ -15676,7 +15676,7 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>321493</v>
+        <v>5238691</v>
       </c>
       <c r="AB109" t="n">
         <v>5</v>
@@ -15684,12 +15684,12 @@
       <c r="AC109" t="inlineStr"/>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>Centro Público</t>
+          <t>Ouvidoria</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH - Manutenção</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4333.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4332.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -15747,12 +15747,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -15771,43 +15771,43 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>55993.68</v>
+        <v>13052.54</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>55924.58</v>
+        <v>13052.54</v>
       </c>
       <c r="P110" t="n">
-        <v>223266.91</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>507656.93</v>
+        <v>346118.97</v>
       </c>
       <c r="S110" t="n">
-        <v>236304</v>
+        <v>46118.97</v>
       </c>
       <c r="T110" t="n">
-        <v>236304</v>
+        <v>46118.97</v>
       </c>
       <c r="U110" t="n">
-        <v>284390.02</v>
+        <v>346118.97</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>427085</v>
+        <v>867556</v>
       </c>
       <c r="X110" t="n">
-        <v>237085</v>
+        <v>867556</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
@@ -15816,7 +15816,7 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>427085</v>
+        <v>867556</v>
       </c>
       <c r="AB110" t="n">
         <v>5</v>
@@ -15824,12 +15824,12 @@
       <c r="AC110" t="inlineStr"/>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>Centro Público</t>
+          <t>Ouvidoria</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH - Manutenção</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -15849,12 +15849,12 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4333.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4332.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -15897,7 +15897,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -15907,11 +15907,11 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>11293.18</v>
+        <v>57410.34</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -15920,34 +15920,34 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>6804.15</v>
+        <v>57410.34</v>
       </c>
       <c r="P111" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>47920</v>
+        <v>321493</v>
       </c>
       <c r="S111" t="n">
-        <v>45670</v>
+        <v>202849.86</v>
       </c>
       <c r="T111" t="n">
-        <v>47470</v>
+        <v>202849.86</v>
       </c>
       <c r="U111" t="n">
-        <v>45670</v>
+        <v>321493</v>
       </c>
       <c r="V111" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>45670</v>
+        <v>321493</v>
       </c>
       <c r="X111" t="n">
-        <v>45670</v>
+        <v>321493</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
@@ -15956,7 +15956,7 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>45670</v>
+        <v>321493</v>
       </c>
       <c r="AB111" t="n">
         <v>5</v>
@@ -15979,22 +15979,22 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4333.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4024.4333.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -16027,17 +16027,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>CPEF</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -16051,43 +16051,43 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>55993.68</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>55924.58</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>223266.91</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>507656.93</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>236304</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>236304</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>284390.02</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>50000</v>
+        <v>427085</v>
       </c>
       <c r="X112" t="n">
-        <v>50000</v>
+        <v>237085</v>
       </c>
       <c r="Y112" t="n">
         <v>0</v>
@@ -16096,7 +16096,7 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>50000</v>
+        <v>427085</v>
       </c>
       <c r="AB112" t="n">
         <v>5</v>
@@ -16104,12 +16104,12 @@
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Egressos e Familiares</t>
+          <t>Centro Público</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>CPEF - Políticas</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4335.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4333.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -16163,21 +16163,21 @@
         <v>422</v>
       </c>
       <c r="F113" t="n">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -16187,56 +16187,56 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2414424.98</v>
+        <v>11293.18</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2294560.33</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>2414424.98</v>
+        <v>6804.15</v>
       </c>
       <c r="P113" t="n">
-        <v>393733.59</v>
+        <v>2250</v>
       </c>
       <c r="Q113" t="n">
-        <v>261863</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>7837448.92</v>
+        <v>47920</v>
       </c>
       <c r="S113" t="n">
-        <v>7375465.34</v>
+        <v>45670</v>
       </c>
       <c r="T113" t="n">
-        <v>7769198.93</v>
+        <v>47470</v>
       </c>
       <c r="U113" t="n">
-        <v>7443715.33</v>
+        <v>45670</v>
       </c>
       <c r="V113" t="n">
-        <v>393733.59</v>
+        <v>1800</v>
       </c>
       <c r="W113" t="n">
-        <v>7443715.33</v>
+        <v>45670</v>
       </c>
       <c r="X113" t="n">
-        <v>5149155</v>
+        <v>45670</v>
       </c>
       <c r="Y113" t="n">
-        <v>261863</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>7443715.33</v>
+        <v>45670</v>
       </c>
       <c r="AB113" t="n">
         <v>5</v>
@@ -16244,12 +16244,12 @@
       <c r="AC113" t="inlineStr"/>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>Mulheres</t>
+          <t>Centro Público</t>
         </is>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>CPM - Casa da Mulher Brasileira</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -16259,22 +16259,22 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4333.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -16303,16 +16303,16 @@
         <v>422</v>
       </c>
       <c r="F114" t="n">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPEF</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -16322,12 +16322,12 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L114" t="n">
@@ -16364,19 +16364,19 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="X114" t="n">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="Y114" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="AB114" t="n">
         <v>5</v>
@@ -16384,17 +16384,17 @@
       <c r="AC114" t="inlineStr"/>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>Mulheres</t>
+          <t>Egressos e Familiares</t>
         </is>
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>CPM - Casa da Mulher Brasileira</t>
+          <t>CPEF - Políticas</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>02 - Transferências Federais</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG114" t="inlineStr">
@@ -16404,17 +16404,17 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33503900.02.1.700.0000</t>
+          <t>34.10.14.422.4024.4335.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -16471,52 +16471,52 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>21384.72</v>
+        <v>2414424.98</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2294560.33</v>
       </c>
       <c r="O115" t="n">
-        <v>21056.72</v>
+        <v>2414424.98</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>393733.59</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>261863</v>
       </c>
       <c r="R115" t="n">
-        <v>143942.4</v>
+        <v>7837448.92</v>
       </c>
       <c r="S115" t="n">
-        <v>33311.56</v>
+        <v>7375465.34</v>
       </c>
       <c r="T115" t="n">
-        <v>33311.56</v>
+        <v>7769198.93</v>
       </c>
       <c r="U115" t="n">
-        <v>143942.4</v>
+        <v>7443715.33</v>
       </c>
       <c r="V115" t="n">
-        <v>0</v>
+        <v>393733.59</v>
       </c>
       <c r="W115" t="n">
-        <v>150755</v>
+        <v>7443715.33</v>
       </c>
       <c r="X115" t="n">
-        <v>158832</v>
+        <v>5149155</v>
       </c>
       <c r="Y115" t="n">
-        <v>8077</v>
+        <v>261863</v>
       </c>
       <c r="Z115" t="n">
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>158832</v>
+        <v>7443715.33</v>
       </c>
       <c r="AB115" t="n">
         <v>5</v>
@@ -16539,7 +16539,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH115" t="inlineStr">
@@ -16549,12 +16549,12 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -16597,30 +16597,30 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>161974.24</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>564000</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>161974.24</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
@@ -16629,34 +16629,34 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>519437</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>485922.72</v>
+        <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>485922.72</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>519437</v>
+        <v>0</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>1083437</v>
+        <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>547269</v>
+        <v>2000</v>
       </c>
       <c r="Y116" t="n">
-        <v>27832</v>
+        <v>2000</v>
       </c>
       <c r="Z116" t="n">
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1111269</v>
+        <v>2000</v>
       </c>
       <c r="AB116" t="n">
         <v>5</v>
@@ -16674,27 +16674,27 @@
       </c>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>02 - Transferências Federais</t>
         </is>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33503900.02.1.700.0000</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -16751,7 +16751,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>780215.36</v>
+        <v>21384.72</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -16760,43 +16760,43 @@
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>642287.52</v>
+        <v>21056.72</v>
       </c>
       <c r="P117" t="n">
-        <v>2102872.47</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>5725169.27</v>
+        <v>143942.4</v>
       </c>
       <c r="S117" t="n">
-        <v>2708402.82</v>
+        <v>33311.56</v>
       </c>
       <c r="T117" t="n">
-        <v>2708722.82</v>
+        <v>33311.56</v>
       </c>
       <c r="U117" t="n">
-        <v>3622296.8</v>
+        <v>143942.4</v>
       </c>
       <c r="V117" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>4087261</v>
+        <v>150755</v>
       </c>
       <c r="X117" t="n">
-        <v>4953156</v>
+        <v>158832</v>
       </c>
       <c r="Y117" t="n">
-        <v>301895</v>
+        <v>8077</v>
       </c>
       <c r="Z117" t="n">
-        <v>564000</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>4389156</v>
+        <v>158832</v>
       </c>
       <c r="AB117" t="n">
         <v>5</v>
@@ -16819,7 +16819,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH117" t="inlineStr">
@@ -16829,12 +16829,12 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -16887,20 +16887,20 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>22963.84</v>
+        <v>161974.24</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>564000</v>
       </c>
       <c r="O118" t="n">
-        <v>22702.49</v>
+        <v>161974.24</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -16909,34 +16909,34 @@
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>282533</v>
+        <v>519437</v>
       </c>
       <c r="S118" t="n">
-        <v>282533</v>
+        <v>485922.72</v>
       </c>
       <c r="T118" t="n">
-        <v>282533</v>
+        <v>485922.72</v>
       </c>
       <c r="U118" t="n">
-        <v>282533</v>
+        <v>519437</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>282533</v>
+        <v>1083437</v>
       </c>
       <c r="X118" t="n">
-        <v>282533</v>
+        <v>547269</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>27832</v>
       </c>
       <c r="Z118" t="n">
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>282533</v>
+        <v>1111269</v>
       </c>
       <c r="AB118" t="n">
         <v>5</v>
@@ -16959,22 +16959,22 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4025.2053.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -17022,16 +17022,16 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>780215.36</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
@@ -17040,43 +17040,43 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>642287.52</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2102872.47</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>5725169.27</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>2708402.82</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>2708722.82</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>3622296.8</v>
       </c>
       <c r="V119" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="W119" t="n">
-        <v>0</v>
+        <v>4087261</v>
       </c>
       <c r="X119" t="n">
-        <v>0</v>
+        <v>4953156</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>301895</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>564000</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>4389156</v>
       </c>
       <c r="AB119" t="n">
         <v>5</v>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>02 - Transferências Federais</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG119" t="inlineStr">
@@ -17104,17 +17104,17 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903900.02.1.700.0000</t>
+          <t>34.10.14.422.4025.2053.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -17157,21 +17157,21 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>33909300</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>22963.84</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -17180,7 +17180,7 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>22702.49</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -17189,25 +17189,25 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
       </c>
       <c r="W120" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="X120" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="Y120" t="n">
         <v>0</v>
@@ -17216,7 +17216,7 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="AB120" t="n">
         <v>5</v>
@@ -17234,27 +17234,27 @@
       </c>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>02 - Transferências Federais</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>Indenizações e Restituições</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33909300.02.1.700.0000</t>
+          <t>34.10.14.422.4025.2053.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -17297,17 +17297,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -17347,16 +17347,16 @@
         <v>0</v>
       </c>
       <c r="X121" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
         <v>5</v>
@@ -17374,27 +17374,27 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>02 - Transferências Federais</t>
         </is>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.44905200.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33903900.02.1.700.0000</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -17437,17 +17437,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33909300</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -17509,32 +17509,32 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>CPM - Políticas</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>02 - Transferências Federais</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Indenizações e Restituições</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Kenji Ito</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
+          <t>34.10.14.422.4025.2053.33909300.02.1.700.0000</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -17577,7 +17577,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -17591,7 +17591,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3132800</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
@@ -17600,43 +17600,43 @@
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>3132800</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>3169600</v>
+        <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>3949200</v>
+        <v>0</v>
       </c>
       <c r="U123" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="W123" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="X123" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="Y123" t="n">
-        <v>1421600</v>
+        <v>10000</v>
       </c>
       <c r="Z123" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>8705439.67</v>
+        <v>10000</v>
       </c>
       <c r="AB123" t="n">
         <v>5</v>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>CPM - Políticas</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AH123" t="inlineStr">
@@ -17669,12 +17669,12 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.44905200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -17707,7 +17707,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -17727,11 +17727,11 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>19041664.7</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -17740,34 +17740,34 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>16923298.94</v>
+        <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>23851875.51</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>21926109.23</v>
+        <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>22593123.43</v>
+        <v>0</v>
       </c>
       <c r="U124" t="n">
-        <v>22426358</v>
+        <v>0</v>
       </c>
       <c r="V124" t="n">
-        <v>667014.2</v>
+        <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>22426358</v>
+        <v>0</v>
       </c>
       <c r="X124" t="n">
-        <v>22426358</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>22426358</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
         <v>5</v>
@@ -17789,7 +17789,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -17804,17 +17804,17 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Kenji Ito</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -17847,7 +17847,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -17857,7 +17857,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -17871,7 +17871,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>64653</v>
+        <v>3132800</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -17880,43 +17880,43 @@
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>64653</v>
+        <v>3132800</v>
       </c>
       <c r="P125" t="n">
-        <v>2075</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="R125" t="n">
-        <v>190072.94</v>
+        <v>8578400</v>
       </c>
       <c r="S125" t="n">
-        <v>141746.12</v>
+        <v>3169600</v>
       </c>
       <c r="T125" t="n">
-        <v>143540.12</v>
+        <v>3949200</v>
       </c>
       <c r="U125" t="n">
-        <v>187997.94</v>
+        <v>8578400</v>
       </c>
       <c r="V125" t="n">
-        <v>1794</v>
+        <v>779600</v>
       </c>
       <c r="W125" t="n">
-        <v>200000</v>
+        <v>8578400</v>
       </c>
       <c r="X125" t="n">
-        <v>200000</v>
+        <v>10000000</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="AA125" t="n">
-        <v>200000</v>
+        <v>8705439.67</v>
       </c>
       <c r="AB125" t="n">
         <v>5</v>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -17939,7 +17939,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
@@ -17949,12 +17949,12 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>40338.4</v>
+        <v>19041664.7</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -18020,34 +18020,34 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>33338.4</v>
+        <v>16923298.94</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1425517.51</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>95531.96000000001</v>
+        <v>23851875.51</v>
       </c>
       <c r="S126" t="n">
-        <v>95531.96000000001</v>
+        <v>21926109.23</v>
       </c>
       <c r="T126" t="n">
-        <v>95531.96000000001</v>
+        <v>22593123.43</v>
       </c>
       <c r="U126" t="n">
-        <v>95531.96000000001</v>
+        <v>22426358</v>
       </c>
       <c r="V126" t="n">
-        <v>0</v>
+        <v>667014.2</v>
       </c>
       <c r="W126" t="n">
-        <v>250000</v>
+        <v>22426358</v>
       </c>
       <c r="X126" t="n">
-        <v>250000</v>
+        <v>22426358</v>
       </c>
       <c r="Y126" t="n">
         <v>0</v>
@@ -18056,7 +18056,7 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>250000</v>
+        <v>22426358</v>
       </c>
       <c r="AB126" t="n">
         <v>5</v>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -18137,7 +18137,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>246715.46</v>
+        <v>64653</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -18160,34 +18160,34 @@
         <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>246715.46</v>
+        <v>64653</v>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>2075</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>2537927</v>
+        <v>190072.94</v>
       </c>
       <c r="S127" t="n">
-        <v>1074549.58</v>
+        <v>141746.12</v>
       </c>
       <c r="T127" t="n">
-        <v>1131764.02</v>
+        <v>143540.12</v>
       </c>
       <c r="U127" t="n">
-        <v>2537927</v>
+        <v>187997.94</v>
       </c>
       <c r="V127" t="n">
-        <v>57214.44</v>
+        <v>1794</v>
       </c>
       <c r="W127" t="n">
-        <v>2537927</v>
+        <v>200000</v>
       </c>
       <c r="X127" t="n">
-        <v>2537927</v>
+        <v>200000</v>
       </c>
       <c r="Y127" t="n">
         <v>0</v>
@@ -18196,7 +18196,7 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2537927</v>
+        <v>200000</v>
       </c>
       <c r="AB127" t="n">
         <v>5</v>
@@ -18219,7 +18219,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
@@ -18229,12 +18229,12 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -18291,7 +18291,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>903690.76</v>
+        <v>40338.4</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
@@ -18300,34 +18300,34 @@
         <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>876799.9</v>
+        <v>33338.4</v>
       </c>
       <c r="P128" t="n">
-        <v>743505.8100000001</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>3802648.2</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="S128" t="n">
-        <v>2409038.89</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="T128" t="n">
-        <v>2502957.88</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="U128" t="n">
-        <v>3059142.39</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="V128" t="n">
-        <v>93918.99000000001</v>
+        <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>4806049</v>
+        <v>250000</v>
       </c>
       <c r="X128" t="n">
-        <v>4806049</v>
+        <v>250000</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
@@ -18336,7 +18336,7 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>4806049</v>
+        <v>250000</v>
       </c>
       <c r="AB128" t="n">
         <v>5</v>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
@@ -18369,12 +18369,12 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -18417,7 +18417,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -18427,11 +18427,11 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>368.19</v>
+        <v>246715.46</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
@@ -18440,7 +18440,7 @@
         <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>156.13</v>
+        <v>246715.46</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -18449,25 +18449,25 @@
         <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>80100</v>
+        <v>2537927</v>
       </c>
       <c r="S129" t="n">
-        <v>80100</v>
+        <v>1074549.58</v>
       </c>
       <c r="T129" t="n">
-        <v>80100</v>
+        <v>1131764.02</v>
       </c>
       <c r="U129" t="n">
-        <v>80100</v>
+        <v>2537927</v>
       </c>
       <c r="V129" t="n">
-        <v>0</v>
+        <v>57214.44</v>
       </c>
       <c r="W129" t="n">
-        <v>139282</v>
+        <v>2537927</v>
       </c>
       <c r="X129" t="n">
-        <v>139282</v>
+        <v>2537927</v>
       </c>
       <c r="Y129" t="n">
         <v>0</v>
@@ -18476,7 +18476,7 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>139282</v>
+        <v>2537927</v>
       </c>
       <c r="AB129" t="n">
         <v>5</v>
@@ -18499,22 +18499,22 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -18571,7 +18571,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>5903.55</v>
+        <v>903690.76</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
@@ -18580,34 +18580,34 @@
         <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>5903.55</v>
+        <v>876799.9</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>743505.8100000001</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>19678.5</v>
+        <v>3802648.2</v>
       </c>
       <c r="S130" t="n">
-        <v>19678.5</v>
+        <v>2409038.89</v>
       </c>
       <c r="T130" t="n">
-        <v>19678.5</v>
+        <v>2502957.88</v>
       </c>
       <c r="U130" t="n">
-        <v>19678.5</v>
+        <v>3059142.39</v>
       </c>
       <c r="V130" t="n">
-        <v>0</v>
+        <v>93918.99000000001</v>
       </c>
       <c r="W130" t="n">
-        <v>49000</v>
+        <v>4806049</v>
       </c>
       <c r="X130" t="n">
-        <v>49000</v>
+        <v>4806049</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
@@ -18616,7 +18616,7 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>49000</v>
+        <v>4806049</v>
       </c>
       <c r="AB130" t="n">
         <v>5</v>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH130" t="inlineStr">
@@ -18649,12 +18649,12 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -18687,17 +18687,17 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -18707,11 +18707,11 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>368.19</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
@@ -18720,43 +18720,43 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>156.13</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>80100</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>80100</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>80100</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>80100</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>139282</v>
       </c>
       <c r="X131" t="n">
-        <v>110000</v>
+        <v>139282</v>
       </c>
       <c r="Y131" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>110000</v>
+        <v>139282</v>
       </c>
       <c r="AB131" t="n">
         <v>5</v>
@@ -18764,12 +18764,12 @@
       <c r="AC131" t="inlineStr"/>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -18779,22 +18779,22 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -18827,17 +18827,17 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -18851,7 +18851,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>5903.55</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -18860,43 +18860,43 @@
         <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>5903.55</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S132" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T132" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U132" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="X132" t="n">
-        <v>100000</v>
+        <v>49000</v>
       </c>
       <c r="Y132" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>100000</v>
+        <v>49000</v>
       </c>
       <c r="AB132" t="n">
         <v>5</v>
@@ -18904,12 +18904,12 @@
       <c r="AC132" t="inlineStr"/>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -18919,7 +18919,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -19006,7 +19006,7 @@
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>75000</v>
+        <v>220000</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -19027,16 +19027,16 @@
         <v>0</v>
       </c>
       <c r="X133" t="n">
-        <v>75000</v>
+        <v>110000</v>
       </c>
       <c r="Y133" t="n">
-        <v>75000</v>
+        <v>330000</v>
       </c>
       <c r="Z133" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="AB133" t="n">
         <v>5</v>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
+          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -19069,12 +19069,12 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -19103,21 +19103,21 @@
         <v>422</v>
       </c>
       <c r="F134" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -19146,7 +19146,7 @@
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -19164,19 +19164,19 @@
         <v>0</v>
       </c>
       <c r="W134" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="X134" t="n">
-        <v>11949</v>
+        <v>100000</v>
       </c>
       <c r="Y134" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="Z134" t="n">
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>11949</v>
+        <v>100000</v>
       </c>
       <c r="AB134" t="n">
         <v>5</v>
@@ -19184,12 +19184,12 @@
       <c r="AC134" t="inlineStr"/>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH134" t="inlineStr">
@@ -19209,12 +19209,12 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -19243,16 +19243,16 @@
         <v>422</v>
       </c>
       <c r="F135" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -19271,7 +19271,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -19280,43 +19280,43 @@
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>127000</v>
+        <v>75000</v>
       </c>
       <c r="R135" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="U135" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>3596273</v>
+        <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>6455492</v>
+        <v>75000</v>
       </c>
       <c r="Y135" t="n">
-        <v>2986219</v>
+        <v>75000</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA135" t="n">
-        <v>6455492</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
         <v>5</v>
@@ -19324,12 +19324,12 @@
       <c r="AC135" t="inlineStr"/>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -19349,12 +19349,12 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -19387,7 +19387,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -19397,7 +19397,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -19444,19 +19444,19 @@
         <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>5374</v>
+        <v>11949</v>
       </c>
       <c r="X136" t="n">
-        <v>10000</v>
+        <v>11949</v>
       </c>
       <c r="Y136" t="n">
-        <v>4626</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>10000</v>
+        <v>11949</v>
       </c>
       <c r="AB136" t="n">
         <v>5</v>
@@ -19469,7 +19469,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -19479,7 +19479,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH136" t="inlineStr">
@@ -19489,12 +19489,12 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -19551,7 +19551,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -19560,43 +19560,43 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="U137" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>80612</v>
+        <v>3596273</v>
       </c>
       <c r="X137" t="n">
-        <v>150000</v>
+        <v>6455492</v>
       </c>
       <c r="Y137" t="n">
-        <v>69388</v>
+        <v>2986219</v>
       </c>
       <c r="Z137" t="n">
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>150000</v>
+        <v>6455492</v>
       </c>
       <c r="AB137" t="n">
         <v>5</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH137" t="inlineStr">
@@ -19629,12 +19629,12 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -19691,7 +19691,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>110635.26</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -19700,43 +19700,43 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>73756.84</v>
+        <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>551.08</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>5040463.02</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
-        <v>570925.76</v>
+        <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>570925.76</v>
+        <v>0</v>
       </c>
       <c r="U138" t="n">
-        <v>5039911.94</v>
+        <v>0</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
       </c>
       <c r="W138" t="n">
-        <v>5870981</v>
+        <v>5374</v>
       </c>
       <c r="X138" t="n">
-        <v>10925362</v>
+        <v>10000</v>
       </c>
       <c r="Y138" t="n">
-        <v>5054381</v>
+        <v>4626</v>
       </c>
       <c r="Z138" t="n">
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>10925362</v>
+        <v>10000</v>
       </c>
       <c r="AB138" t="n">
         <v>5</v>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AH138" t="inlineStr">
@@ -19769,12 +19769,12 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -19827,11 +19827,11 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>76.61</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -19843,40 +19843,40 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>925</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="U139" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>1000</v>
+        <v>80612</v>
       </c>
       <c r="X139" t="n">
-        <v>1000</v>
+        <v>150000</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>69388</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1000</v>
+        <v>150000</v>
       </c>
       <c r="AB139" t="n">
         <v>5</v>
@@ -19899,22 +19899,22 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -19947,17 +19947,17 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>110635.26</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -19980,43 +19980,43 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>73756.84</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>551.08</v>
       </c>
       <c r="Q140" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>5040463.02</v>
       </c>
       <c r="S140" t="n">
-        <v>0</v>
+        <v>570925.76</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>570925.76</v>
       </c>
       <c r="U140" t="n">
-        <v>0</v>
+        <v>5039911.94</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
       </c>
       <c r="W140" t="n">
-        <v>0</v>
+        <v>5870981</v>
       </c>
       <c r="X140" t="n">
-        <v>75000</v>
+        <v>10925362</v>
       </c>
       <c r="Y140" t="n">
-        <v>75000</v>
+        <v>5054381</v>
       </c>
       <c r="Z140" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>10925362</v>
       </c>
       <c r="AB140" t="n">
         <v>5</v>
@@ -20024,12 +20024,12 @@
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH140" t="inlineStr">
@@ -20049,12 +20049,12 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -20080,24 +20080,24 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F141" t="n">
         <v>4026</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -20107,11 +20107,11 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>76.61</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -20123,40 +20123,40 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>11400</v>
+        <v>925</v>
       </c>
       <c r="Q141" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>21600</v>
+        <v>1900</v>
       </c>
       <c r="S141" t="n">
-        <v>9600</v>
+        <v>975</v>
       </c>
       <c r="T141" t="n">
-        <v>9600</v>
+        <v>975</v>
       </c>
       <c r="U141" t="n">
-        <v>10200</v>
+        <v>975</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>22143</v>
+        <v>1000</v>
       </c>
       <c r="X141" t="n">
-        <v>46881</v>
+        <v>1000</v>
       </c>
       <c r="Y141" t="n">
-        <v>39738</v>
+        <v>0</v>
       </c>
       <c r="Z141" t="n">
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>46881</v>
+        <v>1000</v>
       </c>
       <c r="AB141" t="n">
         <v>5</v>
@@ -20164,12 +20164,12 @@
       <c r="AC141" t="inlineStr"/>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -20179,22 +20179,22 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -20220,24 +20220,24 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F142" t="n">
         <v>4026</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -20266,10 +20266,10 @@
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R142" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -20278,25 +20278,25 @@
         <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="X142" t="n">
-        <v>220966</v>
+        <v>75000</v>
       </c>
       <c r="Y142" t="n">
-        <v>187297</v>
+        <v>75000</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA142" t="n">
-        <v>220966</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
         <v>5</v>
@@ -20304,12 +20304,12 @@
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -20319,7 +20319,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
@@ -20329,12 +20329,12 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -20367,17 +20367,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -20403,40 +20403,40 @@
         <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="Q143" t="n">
-        <v>127873.65</v>
+        <v>15000</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="U143" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>0</v>
+        <v>22143</v>
       </c>
       <c r="X143" t="n">
-        <v>100000</v>
+        <v>46881</v>
       </c>
       <c r="Y143" t="n">
-        <v>155747.3</v>
+        <v>39738</v>
       </c>
       <c r="Z143" t="n">
-        <v>72126.35000000001</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>27873.65</v>
+        <v>46881</v>
       </c>
       <c r="AB143" t="n">
         <v>5</v>
@@ -20444,12 +20444,12 @@
       <c r="AC143" t="inlineStr"/>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -20459,7 +20459,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH143" t="inlineStr">
@@ -20469,12 +20469,12 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -20486,12 +20486,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -20500,24 +20500,24 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F144" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -20527,17 +20527,17 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -20549,34 +20549,34 @@
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>150000</v>
+        <v>33669</v>
       </c>
       <c r="S144" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>150000</v>
+        <v>33669</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
       </c>
       <c r="W144" t="n">
-        <v>150000</v>
+        <v>33669</v>
       </c>
       <c r="X144" t="n">
-        <v>0</v>
+        <v>220966</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>187297</v>
       </c>
       <c r="Z144" t="n">
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>150000</v>
+        <v>220966</v>
       </c>
       <c r="AB144" t="n">
         <v>5</v>
@@ -20584,12 +20584,12 @@
       <c r="AC144" t="inlineStr"/>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -20599,22 +20599,22 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
+          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -20626,12 +20626,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -20640,24 +20640,24 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F145" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -20686,7 +20686,7 @@
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>127873.65</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
@@ -20707,16 +20707,16 @@
         <v>0</v>
       </c>
       <c r="X145" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="Y145" t="n">
-        <v>589773</v>
+        <v>155747.3</v>
       </c>
       <c r="Z145" t="n">
-        <v>0</v>
+        <v>72126.35000000001</v>
       </c>
       <c r="AA145" t="n">
-        <v>589773</v>
+        <v>27873.65</v>
       </c>
       <c r="AB145" t="n">
         <v>5</v>
@@ -20724,12 +20724,12 @@
       <c r="AC145" t="inlineStr"/>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
@@ -20749,50 +20749,50 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F146" t="n">
         <v>4010</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -20807,20 +20807,20 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>12940208.36</v>
+        <v>150000</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O146" t="n">
-        <v>12940208.36</v>
+        <v>0</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -20829,25 +20829,25 @@
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="S146" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="T146" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="U146" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="X146" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="Y146" t="n">
         <v>0</v>
@@ -20856,7 +20856,7 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="AB146" t="n">
         <v>5</v>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -20884,60 +20884,60 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F147" t="n">
         <v>4010</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -20984,19 +20984,19 @@
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>600437</v>
+        <v>0</v>
       </c>
       <c r="X147" t="n">
-        <v>16896102</v>
+        <v>589773</v>
       </c>
       <c r="Y147" t="n">
-        <v>16295665</v>
+        <v>589773</v>
       </c>
       <c r="Z147" t="n">
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>16896102</v>
+        <v>589773</v>
       </c>
       <c r="AB147" t="n">
         <v>5</v>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -21019,7 +21019,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH147" t="inlineStr">
@@ -21029,12 +21029,12 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -21056,28 +21056,28 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F148" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>12940208.36</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -21100,7 +21100,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>0</v>
+        <v>12940208.36</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -21109,25 +21109,25 @@
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="S148" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="T148" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="U148" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>1000</v>
+        <v>40835555</v>
       </c>
       <c r="X148" t="n">
-        <v>1000</v>
+        <v>40835555</v>
       </c>
       <c r="Y148" t="n">
         <v>0</v>
@@ -21136,7 +21136,7 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1000</v>
+        <v>40835555</v>
       </c>
       <c r="AB148" t="n">
         <v>5</v>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
@@ -21169,12 +21169,12 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -21196,28 +21196,28 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F149" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>44906100</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -21237,7 +21237,7 @@
         <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -21258,25 +21258,25 @@
         <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>361510</v>
+        <v>600437</v>
       </c>
       <c r="X149" t="n">
-        <v>0</v>
+        <v>16896102</v>
       </c>
       <c r="Y149" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Z149" t="n">
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>361510</v>
+        <v>16896102</v>
       </c>
       <c r="AB149" t="n">
         <v>5</v>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>Aquisição de Imóveis</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
@@ -21309,12 +21309,12 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -21340,14 +21340,14 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F150" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -21357,7 +21357,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>59869982.53</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -21380,43 +21380,43 @@
         <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>59791184.99</v>
+        <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>21043600.09</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
         <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>158978189.3</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>135266690.42</v>
+        <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>140706402.81</v>
+        <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>137934589.21</v>
+        <v>0</v>
       </c>
       <c r="V150" t="n">
-        <v>5439712.39</v>
+        <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>165715582</v>
+        <v>1000</v>
       </c>
       <c r="X150" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="Y150" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>171451529</v>
+        <v>1000</v>
       </c>
       <c r="AB150" t="n">
         <v>5</v>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr">
@@ -21449,12 +21449,12 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -21480,14 +21480,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F151" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -21497,17 +21497,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>44906100</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -21517,7 +21517,7 @@
         <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -21529,7 +21529,7 @@
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -21538,16 +21538,16 @@
         <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>2000</v>
+        <v>361510</v>
       </c>
       <c r="X151" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y151" t="n">
         <v>0</v>
@@ -21556,7 +21556,7 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>2000</v>
+        <v>361510</v>
       </c>
       <c r="AB151" t="n">
         <v>5</v>
@@ -21569,32 +21569,32 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Aquisição de Imóveis</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
+          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -21637,21 +21637,21 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>59869982.53</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21660,43 +21660,43 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
+        <v>59791184.99</v>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>21043600.09</v>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>158978189.3</v>
       </c>
       <c r="S152" t="n">
-        <v>0</v>
+        <v>135266690.42</v>
       </c>
       <c r="T152" t="n">
-        <v>0</v>
+        <v>140706402.81</v>
       </c>
       <c r="U152" t="n">
-        <v>0</v>
+        <v>137934589.21</v>
       </c>
       <c r="V152" t="n">
-        <v>0</v>
+        <v>5439712.39</v>
       </c>
       <c r="W152" t="n">
-        <v>11298</v>
+        <v>165715582</v>
       </c>
       <c r="X152" t="n">
-        <v>11298</v>
+        <v>171813039</v>
       </c>
       <c r="Y152" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Z152" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="AA152" t="n">
-        <v>11298</v>
+        <v>171451529</v>
       </c>
       <c r="AB152" t="n">
         <v>5</v>
@@ -21714,27 +21714,27 @@
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
+          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -21777,21 +21777,21 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>29431997.31</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -21800,43 +21800,43 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>27984138.6</v>
+        <v>0</v>
       </c>
       <c r="P153" t="n">
-        <v>60670522</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>197559544</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>107626518.4</v>
+        <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>107626518.4</v>
+        <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>136889022</v>
+        <v>0</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>136889022</v>
+        <v>2000</v>
       </c>
       <c r="X153" t="n">
-        <v>141616875</v>
+        <v>2000</v>
       </c>
       <c r="Y153" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Z153" t="n">
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>141616875</v>
+        <v>2000</v>
       </c>
       <c r="AB153" t="n">
         <v>5</v>
@@ -21854,27 +21854,27 @@
       </c>
       <c r="AF153" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -21917,21 +21917,21 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>24164007.34</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -21940,43 +21940,43 @@
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>17924153.08</v>
+        <v>0</v>
       </c>
       <c r="P154" t="n">
-        <v>49898263.91</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>129341289.91</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>79232487.98999999</v>
+        <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>79676487.98999999</v>
+        <v>0</v>
       </c>
       <c r="U154" t="n">
-        <v>79443026</v>
+        <v>0</v>
       </c>
       <c r="V154" t="n">
-        <v>444000</v>
+        <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>79443026</v>
+        <v>11298</v>
       </c>
       <c r="X154" t="n">
-        <v>83642123</v>
+        <v>11298</v>
       </c>
       <c r="Y154" t="n">
-        <v>2792377</v>
+        <v>0</v>
       </c>
       <c r="Z154" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>82235403</v>
+        <v>11298</v>
       </c>
       <c r="AB154" t="n">
         <v>5</v>
@@ -21994,27 +21994,27 @@
       </c>
       <c r="AF154" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -22057,21 +22057,21 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>29431997.31</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
@@ -22080,43 +22080,43 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
+        <v>27984138.6</v>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>60670522</v>
       </c>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>197559544</v>
       </c>
       <c r="S155" t="n">
-        <v>0</v>
+        <v>107626518.4</v>
       </c>
       <c r="T155" t="n">
-        <v>0</v>
+        <v>107626518.4</v>
       </c>
       <c r="U155" t="n">
-        <v>0</v>
+        <v>136889022</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>2000</v>
+        <v>136889022</v>
       </c>
       <c r="X155" t="n">
-        <v>2000</v>
+        <v>141616875</v>
       </c>
       <c r="Y155" t="n">
-        <v>0</v>
+        <v>4727853</v>
       </c>
       <c r="Z155" t="n">
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>2000</v>
+        <v>141616875</v>
       </c>
       <c r="AB155" t="n">
         <v>5</v>
@@ -22134,27 +22134,27 @@
       </c>
       <c r="AF155" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG155" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
+          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -22197,7 +22197,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>33913900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -22211,52 +22211,52 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>336000</v>
+        <v>24164007.34</v>
       </c>
       <c r="M156" t="n">
         <v>0</v>
       </c>
       <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>17924153.08</v>
+      </c>
+      <c r="P156" t="n">
+        <v>49898263.91</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>129341289.91</v>
+      </c>
+      <c r="S156" t="n">
+        <v>79232487.98999999</v>
+      </c>
+      <c r="T156" t="n">
+        <v>79676487.98999999</v>
+      </c>
+      <c r="U156" t="n">
+        <v>79443026</v>
+      </c>
+      <c r="V156" t="n">
+        <v>444000</v>
+      </c>
+      <c r="W156" t="n">
+        <v>79443026</v>
+      </c>
+      <c r="X156" t="n">
+        <v>83642123</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>2792377</v>
+      </c>
+      <c r="Z156" t="n">
         <v>1406720</v>
       </c>
-      <c r="O156" t="n">
-        <v>336000</v>
-      </c>
-      <c r="P156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
-      <c r="R156" t="n">
-        <v>1406720</v>
-      </c>
-      <c r="S156" t="n">
-        <v>1406720</v>
-      </c>
-      <c r="T156" t="n">
-        <v>1406720</v>
-      </c>
-      <c r="U156" t="n">
-        <v>1406720</v>
-      </c>
-      <c r="V156" t="n">
-        <v>0</v>
-      </c>
-      <c r="W156" t="n">
-        <v>1406720</v>
-      </c>
-      <c r="X156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z156" t="n">
-        <v>0</v>
-      </c>
       <c r="AA156" t="n">
-        <v>1406720</v>
+        <v>82235403</v>
       </c>
       <c r="AB156" t="n">
         <v>5</v>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>Transferência entre Órgãos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH156" t="inlineStr">
@@ -22289,24 +22289,24 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -22320,34 +22320,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F157" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L157" t="n">
@@ -22384,10 +22384,10 @@
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="X157" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="Y157" t="n">
         <v>0</v>
@@ -22396,7 +22396,7 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="AB157" t="n">
         <v>5</v>
@@ -22404,49 +22404,49 @@
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -22460,24 +22460,24 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F158" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -22491,16 +22491,16 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>336000</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="O158" t="n">
-        <v>0</v>
+        <v>336000</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -22509,25 +22509,25 @@
         <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S158" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="T158" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U158" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>6245</v>
+        <v>1406720</v>
       </c>
       <c r="X158" t="n">
-        <v>6245</v>
+        <v>0</v>
       </c>
       <c r="Y158" t="n">
         <v>0</v>
@@ -22536,7 +22536,7 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>6245</v>
+        <v>1406720</v>
       </c>
       <c r="AB158" t="n">
         <v>5</v>
@@ -22544,12 +22544,12 @@
       <c r="AC158" t="inlineStr"/>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="AG158" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AH158" t="inlineStr">
@@ -22569,12 +22569,12 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -22600,24 +22600,24 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F159" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>DTIC</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -22664,10 +22664,10 @@
         <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="X159" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="Y159" t="n">
         <v>0</v>
@@ -22676,7 +22676,7 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="AB159" t="n">
         <v>5</v>
@@ -22684,12 +22684,12 @@
       <c r="AC159" t="inlineStr"/>
       <c r="AD159" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>DTIC - Desenvolvimento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="AG159" t="inlineStr">
         <is>
-          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH159" t="inlineStr">
@@ -22709,12 +22709,12 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -22740,24 +22740,24 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F160" t="n">
-        <v>4019</v>
+        <v>4004</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -22767,7 +22767,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -22804,10 +22804,10 @@
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>0</v>
+        <v>6245</v>
       </c>
       <c r="X160" t="n">
-        <v>0</v>
+        <v>6245</v>
       </c>
       <c r="Y160" t="n">
         <v>0</v>
@@ -22816,7 +22816,7 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>6245</v>
       </c>
       <c r="AB160" t="n">
         <v>5</v>
@@ -22824,12 +22824,12 @@
       <c r="AC160" t="inlineStr"/>
       <c r="AD160" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -22839,22 +22839,22 @@
       </c>
       <c r="AG160" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>25/04/2026 07:06:57</t>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>
@@ -22880,38 +22880,38 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F161" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>24479179.14</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
@@ -22920,34 +22920,34 @@
         <v>0</v>
       </c>
       <c r="O161" t="n">
-        <v>24479179.14</v>
+        <v>0</v>
       </c>
       <c r="P161" t="n">
-        <v>3158618.88</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>39837366.69</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>32622739.07</v>
+        <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>34235503.17</v>
+        <v>0</v>
       </c>
       <c r="U161" t="n">
-        <v>36678747.81</v>
+        <v>0</v>
       </c>
       <c r="V161" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>61292510</v>
+        <v>1000</v>
       </c>
       <c r="X161" t="n">
-        <v>61292510</v>
+        <v>1000</v>
       </c>
       <c r="Y161" t="n">
         <v>0</v>
@@ -22956,7 +22956,7 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>61292510</v>
+        <v>1000</v>
       </c>
       <c r="AB161" t="n">
         <v>5</v>
@@ -22964,37 +22964,317 @@
       <c r="AC161" t="inlineStr"/>
       <c r="AD161" t="inlineStr">
         <is>
+          <t>Tecnologia</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>DTIC - Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>26/04/2026 07:05:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>422</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>0004</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC162" t="inlineStr"/>
+      <c r="AD162" t="inlineStr">
+        <is>
           <t>Criança e Adolescente</t>
         </is>
       </c>
-      <c r="AE161" t="inlineStr">
+      <c r="AE162" t="inlineStr">
         <is>
           <t>FUMCAD</t>
         </is>
       </c>
-      <c r="AF161" t="inlineStr">
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>26/04/2026 07:05:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>422</v>
+      </c>
+      <c r="F163" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>24479179.14</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>24479179.14</v>
+      </c>
+      <c r="P163" t="n">
+        <v>3158618.88</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>39837366.69</v>
+      </c>
+      <c r="S163" t="n">
+        <v>32622739.07</v>
+      </c>
+      <c r="T163" t="n">
+        <v>34235503.17</v>
+      </c>
+      <c r="U163" t="n">
+        <v>36678747.81</v>
+      </c>
+      <c r="V163" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="W163" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X163" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC163" t="inlineStr"/>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
         <is>
           <t>08 - Recusos Vinculados</t>
         </is>
       </c>
-      <c r="AG161" t="inlineStr">
+      <c r="AG163" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AH161" t="inlineStr">
+      <c r="AH163" t="inlineStr">
         <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AI161" t="inlineStr">
+      <c r="AI163" t="inlineStr">
         <is>
           <t>90.10.14.422.4019.6160.33503900.08.1.759.0958</t>
         </is>
       </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>25/04/2026 07:06:57</t>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>26/04/2026 07:05:21</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>4600000</v>
+        <v>6900000</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>2300000</v>
       </c>
       <c r="X65" t="n">
         <v>2300000</v>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>26/04/2026 07:05:21</t>
+          <t>27/04/2026 08:18:38</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>490</v>
+        <v>8220.799999999999</v>
       </c>
       <c r="P7" t="n">
         <v>96530.67999999999</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -1792,10 +1792,10 @@
         <v>12796283.42</v>
       </c>
       <c r="S10" t="n">
-        <v>7777663.45</v>
+        <v>7781620.45</v>
       </c>
       <c r="T10" t="n">
-        <v>7883814</v>
+        <v>7887771</v>
       </c>
       <c r="U10" t="n">
         <v>11542338.2</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2775.93</v>
+        <v>19814.29</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5459</v>
       </c>
       <c r="P17" t="n">
         <v>10008.92</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2328209.86</v>
+        <v>2377496.15</v>
       </c>
       <c r="P31" t="n">
         <v>800034.36</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>125614.91</v>
+        <v>126114.07</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>85560.27</v>
+        <v>85625.23</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>19002.37</v>
+        <v>30665.88</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>1377.05</v>
+        <v>4568.87</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>20096</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -8092,10 +8092,10 @@
         <v>20096</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>20096</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>20096</v>
       </c>
       <c r="U55" t="n">
         <v>20096</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -10040,7 +10040,7 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>361150</v>
+        <v>486700</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -19140,7 +19140,7 @@
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>156.13</v>
+        <v>312.26</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -21511,7 +21511,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>12940208.36</v>
+        <v>14955138.28</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -22071,7 +22071,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>59869982.53</v>
+        <v>59919823.77</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
@@ -22080,7 +22080,7 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>59791184.99</v>
+        <v>59803761.71</v>
       </c>
       <c r="P155" t="n">
         <v>21043600.09</v>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -22631,7 +22631,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>24164007.34</v>
+        <v>24434007.34</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>24479179.14</v>
+        <v>26316455.82</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>28/04/2026 08:14:39</t>
+          <t>29/04/2026 08:10:15</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202604.xlsx
+++ b/base_despesas/2026/despesas_202604.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>26713</v>
+        <v>29281</v>
       </c>
       <c r="S6" t="n">
         <v>19513</v>
@@ -1238,7 +1238,7 @@
         <v>19513</v>
       </c>
       <c r="U6" t="n">
-        <v>19513</v>
+        <v>22081</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>12157.8</v>
+        <v>14217.8</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1825007.65</v>
+        <v>1886631.1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1792,10 +1792,10 @@
         <v>12796283.42</v>
       </c>
       <c r="S10" t="n">
-        <v>7781620.45</v>
+        <v>8397693.800000001</v>
       </c>
       <c r="T10" t="n">
-        <v>7887771</v>
+        <v>8503844.35</v>
       </c>
       <c r="U10" t="n">
         <v>11542338.2</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>116000</v>
       </c>
       <c r="O11" t="n">
         <v>19814.29</v>
@@ -1944,7 +1944,7 @@
         <v>450</v>
       </c>
       <c r="W11" t="n">
-        <v>371611</v>
+        <v>487611</v>
       </c>
       <c r="X11" t="n">
         <v>371611</v>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>371611</v>
+        <v>487611</v>
       </c>
       <c r="AB11" t="n">
         <v>5</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>492510.03</v>
+        <v>501019.15</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4443,13 +4443,13 @@
         <v>487833.75</v>
       </c>
       <c r="P29" t="n">
-        <v>315775.36</v>
+        <v>316170.82</v>
       </c>
       <c r="Q29" t="n">
         <v>9180</v>
       </c>
       <c r="R29" t="n">
-        <v>2157447.4</v>
+        <v>2157842.86</v>
       </c>
       <c r="S29" t="n">
         <v>1634951.64</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
         <v>6572.65</v>
       </c>
       <c r="W31" t="n">
-        <v>18269345</v>
+        <v>18159345</v>
       </c>
       <c r="X31" t="n">
         <v>18370086</v>
@@ -4753,10 +4753,10 @@
         <v>100741</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="AA31" t="n">
-        <v>18370086</v>
+        <v>18260086</v>
       </c>
       <c r="AB31" t="n">
         <v>5</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="O32" t="n">
         <v>85625.23</v>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>860517</v>
+        <v>970517</v>
       </c>
       <c r="X32" t="n">
         <v>860517</v>
@@ -4896,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>860517</v>
+        <v>970517</v>
       </c>
       <c r="AB32" t="n">
         <v>5</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>896173.73</v>
+        <v>912895.4300000001</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
         <v>422635.58</v>
       </c>
       <c r="W44" t="n">
-        <v>15225568.73</v>
+        <v>15006568.73</v>
       </c>
       <c r="X44" t="n">
         <v>21072104</v>
@@ -6573,10 +6573,10 @@
         <v>5330872</v>
       </c>
       <c r="Z44" t="n">
-        <v>1795895.27</v>
+        <v>2014895.27</v>
       </c>
       <c r="AA44" t="n">
-        <v>19370094.73</v>
+        <v>19151094.73</v>
       </c>
       <c r="AB44" t="n">
         <v>5</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -6671,13 +6671,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>42304.61</v>
+        <v>55921.64</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>219000</v>
       </c>
       <c r="O45" t="n">
         <v>30665.88</v>
@@ -6704,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>316616</v>
+        <v>535616</v>
       </c>
       <c r="X45" t="n">
         <v>316616</v>
@@ -6716,7 +6716,7 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>316616</v>
+        <v>535616</v>
       </c>
       <c r="AB45" t="n">
         <v>5</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3699664.86</v>
+        <v>4476108.99</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -7246,7 +7246,7 @@
         <v>4140329.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>278000</v>
       </c>
       <c r="R49" t="n">
         <v>13165012.7</v>
@@ -7264,7 +7264,7 @@
         <v>2404922.99</v>
       </c>
       <c r="W49" t="n">
-        <v>9024683</v>
+        <v>9302683</v>
       </c>
       <c r="X49" t="n">
         <v>10590662</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="O52" t="n">
         <v>4568.87</v>
@@ -7684,7 +7684,7 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>48307</v>
+        <v>98307</v>
       </c>
       <c r="X52" t="n">
         <v>48307</v>
@@ -7696,7 +7696,7 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>48307</v>
+        <v>98307</v>
       </c>
       <c r="AB52" t="n">
         <v>5</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
         <v>5495750</v>
       </c>
       <c r="W54" t="n">
-        <v>18568759</v>
+        <v>18518759</v>
       </c>
       <c r="X54" t="n">
         <v>22965724</v>
@@ -7973,10 +7973,10 @@
         <v>4186869</v>
       </c>
       <c r="Z54" t="n">
-        <v>210096</v>
+        <v>260096</v>
       </c>
       <c r="AA54" t="n">
-        <v>22755628</v>
+        <v>22705628</v>
       </c>
       <c r="AB54" t="n">
         <v>5</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11044,7 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>938683</v>
+        <v>848683</v>
       </c>
       <c r="X76" t="n">
         <v>1314953</v>
@@ -11053,10 +11053,10 @@
         <v>376270</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="AA76" t="n">
-        <v>1314953</v>
+        <v>1224953</v>
       </c>
       <c r="AB76" t="n">
         <v>5</v>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -11151,13 +11151,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1731.85</v>
+        <v>2830.87</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="O77" t="n">
         <v>946.3</v>
@@ -11184,7 +11184,7 @@
         <v>450</v>
       </c>
       <c r="W77" t="n">
-        <v>21270</v>
+        <v>61270</v>
       </c>
       <c r="X77" t="n">
         <v>21270</v>
@@ -11196,7 +11196,7 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>21270</v>
+        <v>61270</v>
       </c>
       <c r="AB77" t="n">
         <v>5</v>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -12143,13 +12143,13 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>23843.36</v>
+        <v>24443.36</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>416595.36</v>
+        <v>417195.36</v>
       </c>
       <c r="S84" t="n">
         <v>363452.83</v>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -12444,13 +12444,13 @@
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>50000</v>
+        <v>345.28</v>
       </c>
       <c r="X86" t="n">
         <v>50000</v>
       </c>
       <c r="Y86" t="n">
-        <v>49471</v>
+        <v>99125.72</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -12566,10 +12566,10 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -12578,13 +12578,13 @@
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>1058</v>
+        <v>79058</v>
       </c>
       <c r="X87" t="n">
         <v>100000</v>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -12709,16 +12709,16 @@
         <v>49471</v>
       </c>
       <c r="R88" t="n">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="S88" t="n">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="T88" t="n">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="U88" t="n">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -12864,13 +12864,13 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>13341</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
         <v>1261000</v>
       </c>
       <c r="Y89" t="n">
-        <v>1247659</v>
+        <v>1261000</v>
       </c>
       <c r="Z89" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -15789,7 +15789,7 @@
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>7795800.02</v>
+        <v>7843280.02</v>
       </c>
       <c r="S110" t="n">
         <v>821264.08</v>
@@ -15798,7 +15798,7 @@
         <v>821264.08</v>
       </c>
       <c r="U110" t="n">
-        <v>7745800.02</v>
+        <v>7793280.02</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -16084,13 +16084,13 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>867556</v>
+        <v>589556</v>
       </c>
       <c r="X112" t="n">
         <v>867556</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>278000</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -16331,7 +16331,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>55993.68</v>
+        <v>57142.9</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -16477,10 +16477,10 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="O115" t="n">
-        <v>6804.15</v>
+        <v>6932.88</v>
       </c>
       <c r="P115" t="n">
         <v>2250</v>
@@ -16504,7 +16504,7 @@
         <v>1800</v>
       </c>
       <c r="W115" t="n">
-        <v>45670</v>
+        <v>95670</v>
       </c>
       <c r="X115" t="n">
         <v>45670</v>
@@ -16516,7 +16516,7 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>45670</v>
+        <v>95670</v>
       </c>
       <c r="AB115" t="n">
         <v>5</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -16772,10 +16772,10 @@
         <v>7837448.92</v>
       </c>
       <c r="S117" t="n">
-        <v>7375465.34</v>
+        <v>7443715.32</v>
       </c>
       <c r="T117" t="n">
-        <v>7769198.93</v>
+        <v>7837448.91</v>
       </c>
       <c r="U117" t="n">
         <v>7443715.33</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>780215.36</v>
+        <v>808907.3100000001</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -17344,19 +17344,19 @@
         <v>320</v>
       </c>
       <c r="W121" t="n">
-        <v>4087261</v>
+        <v>3914256.72</v>
       </c>
       <c r="X121" t="n">
         <v>4953156</v>
       </c>
       <c r="Y121" t="n">
-        <v>301895</v>
+        <v>316899.28</v>
       </c>
       <c r="Z121" t="n">
-        <v>564000</v>
+        <v>722000</v>
       </c>
       <c r="AA121" t="n">
-        <v>4389156</v>
+        <v>4231156</v>
       </c>
       <c r="AB121" t="n">
         <v>5</v>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -17457,7 +17457,7 @@
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>158000</v>
       </c>
       <c r="O122" t="n">
         <v>22702.49</v>
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>282533</v>
+        <v>440533</v>
       </c>
       <c r="X122" t="n">
         <v>282533</v>
@@ -17496,7 +17496,7 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>282533</v>
+        <v>440533</v>
       </c>
       <c r="AB122" t="n">
         <v>5</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -18312,10 +18312,10 @@
         <v>8578400</v>
       </c>
       <c r="S128" t="n">
-        <v>3169600</v>
+        <v>3984000</v>
       </c>
       <c r="T128" t="n">
-        <v>3949200</v>
+        <v>4763600</v>
       </c>
       <c r="U128" t="n">
         <v>8578400</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>928928.4399999999</v>
+        <v>929386.36</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
@@ -19024,7 +19024,7 @@
         <v>93918.99000000001</v>
       </c>
       <c r="W133" t="n">
-        <v>4806049</v>
+        <v>4690049</v>
       </c>
       <c r="X133" t="n">
         <v>4806049</v>
@@ -19033,10 +19033,10 @@
         <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>116000</v>
       </c>
       <c r="AA133" t="n">
-        <v>4806049</v>
+        <v>4690049</v>
       </c>
       <c r="AB133" t="n">
         <v>5</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -20391,7 +20391,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>110635.26</v>
+        <v>112772.08</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
         <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>27984138.6</v>
+        <v>29380182.6</v>
       </c>
       <c r="P158" t="n">
         <v>60670522</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -22631,7 +22631,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>24434007.34</v>
+        <v>24794007.34</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -22640,7 +22640,7 @@
         <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>17924153.08</v>
+        <v>22934598.76</v>
       </c>
       <c r="P159" t="n">
         <v>49898263.91</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
@@ -23629,7 +23629,7 @@
         <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>39837366.69</v>
+        <v>40403684.89</v>
       </c>
       <c r="S166" t="n">
         <v>32622739.07</v>
@@ -23638,7 +23638,7 @@
         <v>34235503.17</v>
       </c>
       <c r="U166" t="n">
-        <v>36678747.81</v>
+        <v>37245066.01</v>
       </c>
       <c r="V166" t="n">
         <v>1612764.1</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>29/04/2026 08:10:15</t>
+          <t>30/04/2026 08:06:33</t>
         </is>
       </c>
     </row>
